--- a/src/nodes/HPC/compressor_blade_strength.xlsx
+++ b/src/nodes/HPC/compressor_blade_strength.xlsx
@@ -1183,28 +1183,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>227.3925046610361</v>
+        <v>235.63216491241906</v>
       </c>
       <c r="C3">
-        <v>248.73128419687797</v>
+        <v>230.28755476505043</v>
       </c>
       <c r="D3">
-        <v>31.18164608599049</v>
+        <v>23.982338871449944</v>
       </c>
       <c r="E3">
-        <v>125.36278332125411</v>
+        <v>104.14083772750023</v>
       </c>
       <c r="F3">
-        <v>258.75221041549753</v>
+        <v>241.50206305446437</v>
       </c>
       <c r="G3">
         <v>11.178822012033388</v>
       </c>
       <c r="H3">
-        <v>35.980488306691726</v>
+        <v>27.643139880282742</v>
       </c>
       <c r="I3">
-        <v>139.05383938137263</v>
+        <v>114.46336950773197</v>
       </c>
       <c r="J3">
         <v>299.26418287761362</v>
@@ -1264,19 +1264,19 @@
         <v>1.4617331174998134</v>
       </c>
       <c r="AC3">
-        <v>1.0441082558405503</v>
+        <v>1.0420027363837927</v>
       </c>
       <c r="AD3">
         <v>1.1692051981276797</v>
       </c>
       <c r="AE3">
-        <v>896.48858517932456</v>
+        <v>756.40196267309841</v>
       </c>
       <c r="AF3">
         <v>2.5038677557644964</v>
       </c>
       <c r="AG3">
-        <v>43490.503049824489</v>
+        <v>40591.109554649549</v>
       </c>
       <c r="AH3">
         <v>324.67173109056989</v>
@@ -1297,136 +1297,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-5.5736922462338185</v>
+        <v>-5.5735821459542736</v>
       </c>
       <c r="AO3">
         <v>-2.3232855294726575</v>
       </c>
       <c r="AP3">
-        <v>-2.9959664787008449</v>
+        <v>-2.9961713000971559</v>
       </c>
       <c r="AQ3">
         <v>-1.4146208585337339</v>
       </c>
       <c r="AR3">
-        <v>1482.7381983580797</v>
+        <v>1381.2049989312068</v>
       </c>
       <c r="AS3">
         <v>26.250217892143027</v>
       </c>
       <c r="AT3">
-        <v>-1.6252562958927979</v>
+        <v>-1.3984763476286868</v>
       </c>
       <c r="AU3">
-        <v>-0.76206049591512626</v>
+        <v>-0.53666232106699019</v>
       </c>
       <c r="AV3">
-        <v>-1.3862303399866989</v>
+        <v>-1.1928028506862294</v>
       </c>
       <c r="AW3">
-        <v>0.60725922781417963</v>
+        <v>0.42764734353111244</v>
       </c>
       <c r="AX3">
-        <v>5.4153104838798987</v>
+        <v>4.659685765198982</v>
       </c>
       <c r="AY3">
-        <v>0.0016225132117414997</v>
+        <v>0.0011426149378461264</v>
       </c>
       <c r="AZ3">
-        <v>-13.205620817254589</v>
+        <v>-11.362976052056272</v>
       </c>
       <c r="BA3">
-        <v>0.0020313377798068626</v>
+        <v>0.0014305195632442697</v>
       </c>
       <c r="BB3">
-        <v>-0.017329914459766706</v>
+        <v>-0.019335200224522855</v>
       </c>
       <c r="BC3">
-        <v>-0.010395197590913789</v>
+        <v>-0.011597797617609373</v>
       </c>
       <c r="BD3">
-        <v>-0.47042493117700312</v>
+        <v>-0.46192118681762528</v>
       </c>
       <c r="BE3">
-        <v>0.0057614948161183975</v>
+        <v>0.0040573887286063292</v>
       </c>
       <c r="BF3">
-        <v>-0.3172676954690527</v>
+        <v>-0.33443347452048428</v>
       </c>
       <c r="BG3">
-        <v>0.2194836949465046</v>
+        <v>0.1545659066632262</v>
       </c>
       <c r="BH3">
-        <v>43.680402120481908</v>
+        <v>43.824696406366066</v>
       </c>
       <c r="BI3">
-        <v>38.775741575948885</v>
+        <v>38.895699801144687</v>
       </c>
       <c r="BJ3">
-        <v>-5.2038939572421032</v>
+        <v>-4.50655524166095</v>
       </c>
       <c r="BK3">
-        <v>0.0025370900934805689</v>
+        <v>0.0017875159769749876</v>
       </c>
       <c r="BL3">
-        <v>-13.290353512518259</v>
+        <v>-11.424572466567867</v>
       </c>
       <c r="BM3">
-        <v>0.00056749991674814176</v>
+        <v>0.00039590623772913641</v>
       </c>
       <c r="BN3">
-        <v>3.0135633382711191</v>
+        <v>2.7046860185524357</v>
       </c>
       <c r="BO3">
-        <v>0.098836879454933607</v>
+        <v>0.097865931250574148</v>
       </c>
       <c r="BP3">
-        <v>-2.5097853007076409</v>
+        <v>-2.5469371287826226</v>
       </c>
       <c r="BQ3">
-        <v>4.236903494155337</v>
+        <v>4.0064931143670748</v>
       </c>
       <c r="BR3">
-        <v>29.481406989568505</v>
+        <v>29.509175764571651</v>
       </c>
       <c r="BS3">
-        <v>-5.1961790602729181</v>
+        <v>-5.036087827531901</v>
       </c>
       <c r="BT3">
-        <v>0.20595936139809687</v>
+        <v>0.20594638147026464</v>
       </c>
       <c r="BU3">
-        <v>0.7659454803544522</v>
+        <v>0.7659489704818645</v>
       </c>
       <c r="BV3">
-        <v>12.342337907125346</v>
+        <v>12.34236731200504</v>
       </c>
       <c r="BW3">
-        <v>-1.7352903441024521</v>
+        <v>-1.7350811875955339</v>
       </c>
       <c r="BX3">
-        <v>-25.361144788585943</v>
+        <v>-24.587070000457388</v>
       </c>
       <c r="BY3">
-        <v>0.77574835681301335</v>
+        <v>0.54656130214851961</v>
       </c>
       <c r="BZ3">
-        <v>39.171815715048481</v>
+        <v>38.309934014229214</v>
       </c>
       <c r="CA3">
-        <v>-1.7798882915660839</v>
+        <v>-1.2537281172451249</v>
       </c>
       <c r="CB3">
-        <v>178.2259374876144</v>
+        <v>152.77366957287552</v>
       </c>
       <c r="CC3">
-        <v>0.80620010260819275</v>
+        <v>0.56799637015469606</v>
       </c>
       <c r="CD3">
-        <v>1.1221711206535174</v>
+        <v>1.3091261115816606</v>
       </c>
       <c r="CE3">
-        <v>248.07736857508004</v>
+        <v>352.11492627237953</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -1434,28 +1434,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>227.93499130722384</v>
+        <v>234.22391635587769</v>
       </c>
       <c r="C4">
-        <v>202.49823648819702</v>
+        <v>187.72250285177998</v>
       </c>
       <c r="D4">
-        <v>21.392450477433851</v>
+        <v>16.79538456955304</v>
       </c>
       <c r="E4">
-        <v>105.64265076294009</v>
+        <v>89.46921287755346</v>
       </c>
       <c r="F4">
-        <v>210.23083434961058</v>
+        <v>196.21544539296986</v>
       </c>
       <c r="G4">
         <v>10.99029793601327</v>
       </c>
       <c r="H4">
-        <v>24.620897850869003</v>
+        <v>19.014419659190345</v>
       </c>
       <c r="I4">
-        <v>117.11363809708729</v>
+        <v>96.905825232612429</v>
       </c>
       <c r="J4">
         <v>421.73524183129689</v>
@@ -1509,25 +1509,25 @@
         <v>10.10773353450023</v>
       </c>
       <c r="AA4">
-        <v>2.3816968133135505</v>
+        <v>2.381696813313551</v>
       </c>
       <c r="AB4">
         <v>1.5851733570508129</v>
       </c>
       <c r="AC4">
-        <v>0.89167796210107475</v>
+        <v>0.88988214105754393</v>
       </c>
       <c r="AD4">
         <v>1.27755188511565</v>
       </c>
       <c r="AE4">
-        <v>551.32608330850053</v>
+        <v>461.54472293579528</v>
       </c>
       <c r="AF4">
         <v>2.8233041284324556</v>
       </c>
       <c r="AG4">
-        <v>28706.552227265063</v>
+        <v>26792.769259712084</v>
       </c>
       <c r="AH4">
         <v>313.83823569950476</v>
@@ -1548,136 +1548,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-5.0104135011030548</v>
+        <v>-5.0103412842888817</v>
       </c>
       <c r="AO4">
         <v>-2.3092882668994479</v>
       </c>
       <c r="AP4">
-        <v>-2.3040033240011093</v>
+        <v>-2.3041603642095692</v>
       </c>
       <c r="AQ4">
         <v>-1.5340676355878473</v>
       </c>
       <c r="AR4">
-        <v>1085.8723028249419</v>
+        <v>1011.5123308704367</v>
       </c>
       <c r="AS4">
         <v>25.589123329345522</v>
       </c>
       <c r="AT4">
-        <v>-2.1709494029683514</v>
+        <v>-1.5615600968719723</v>
       </c>
       <c r="AU4">
-        <v>-1.095507044234137</v>
+        <v>-0.62418424613340373</v>
       </c>
       <c r="AV4">
-        <v>-1.5657044196851628</v>
+        <v>-1.1262084422296785</v>
       </c>
       <c r="AW4">
-        <v>0.73051386681601049</v>
+        <v>0.41622301713935478</v>
       </c>
       <c r="AX4">
-        <v>4.4570021808653157</v>
+        <v>3.2059138493943506</v>
       </c>
       <c r="AY4">
-        <v>0.001167692684009129</v>
+        <v>0.00066531327344706182</v>
       </c>
       <c r="AZ4">
-        <v>-11.364875270560901</v>
+        <v>-8.17473484373679</v>
       </c>
       <c r="BA4">
-        <v>0.0017412044697157065</v>
+        <v>0.000992081616465926</v>
       </c>
       <c r="BB4">
-        <v>-0.020109740378982676</v>
+        <v>-0.018664052750750705</v>
       </c>
       <c r="BC4">
-        <v>-0.01080633478415779</v>
+        <v>-0.010029318791238301</v>
       </c>
       <c r="BD4">
-        <v>-0.38948582008367544</v>
+        <v>-0.28014511626728472</v>
       </c>
       <c r="BE4">
-        <v>0.0060242908090891731</v>
+        <v>0.0034324429098657977</v>
       </c>
       <c r="BF4">
-        <v>-0.35868473582981342</v>
+        <v>-0.27695669911034249</v>
       </c>
       <c r="BG4">
-        <v>0.23542388426337904</v>
+        <v>0.13413679185833941</v>
       </c>
       <c r="BH4">
-        <v>49.61233273144714</v>
+        <v>49.810404176997409</v>
       </c>
       <c r="BI4">
-        <v>41.280290836216118</v>
+        <v>41.458815436537577</v>
       </c>
       <c r="BJ4">
-        <v>-5.7684319836928273</v>
+        <v>-4.1759509802967028</v>
       </c>
       <c r="BK4">
-        <v>0.0020262584979956061</v>
+        <v>0.001155445846783711</v>
       </c>
       <c r="BL4">
-        <v>-10.758738346346867</v>
+        <v>-7.7243515446477371</v>
       </c>
       <c r="BM4">
-        <v>0.00053812239216277711</v>
+        <v>0.000303005908696122</v>
       </c>
       <c r="BN4">
-        <v>2.0514836540583161</v>
+        <v>1.825065847400887</v>
       </c>
       <c r="BO4">
-        <v>0.13688625137372817</v>
+        <v>0.13516838904142303</v>
       </c>
       <c r="BP4">
-        <v>-2.0537729413444974</v>
+        <v>-2.0802898250213375</v>
       </c>
       <c r="BQ4">
-        <v>4.0755633879217532</v>
+        <v>3.8501456384362291</v>
       </c>
       <c r="BR4">
-        <v>29.600247653417458</v>
+        <v>29.61661276348952</v>
       </c>
       <c r="BS4">
-        <v>-4.1676189688559768</v>
+        <v>-4.0496860903931289</v>
       </c>
       <c r="BT4">
-        <v>0.20887748257076791</v>
+        <v>0.20885336567499435</v>
       </c>
       <c r="BU4">
-        <v>0.80436653032478689</v>
+        <v>0.80437279260182881</v>
       </c>
       <c r="BV4">
-        <v>12.334482611692774</v>
+        <v>12.334539685262953</v>
       </c>
       <c r="BW4">
-        <v>-1.903756942188638</v>
+        <v>-1.903387124511472</v>
       </c>
       <c r="BX4">
-        <v>-43.411653472615043</v>
+        <v>-35.434983486642473</v>
       </c>
       <c r="BY4">
-        <v>0.576928050513728</v>
+        <v>0.32899038007520204</v>
       </c>
       <c r="BZ4">
-        <v>54.698776103963212</v>
+        <v>45.179097774088909</v>
       </c>
       <c r="CA4">
-        <v>-1.3874575428806166</v>
+        <v>-0.79087580546832947</v>
       </c>
       <c r="CB4">
-        <v>171.81278860531035</v>
+        <v>142.08519293309007</v>
       </c>
       <c r="CC4">
-        <v>0.6231134573664957</v>
+        <v>0.35528488444074474</v>
       </c>
       <c r="CD4">
-        <v>1.1640577027094388</v>
+        <v>1.407606210551319</v>
       </c>
       <c r="CE4">
-        <v>320.96883422366255</v>
+        <v>562.92853639079169</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -1685,28 +1685,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>227.168953466399</v>
+        <v>232.5503088636367</v>
       </c>
       <c r="C5">
-        <v>165.14134193782871</v>
+        <v>154.13191914197302</v>
       </c>
       <c r="D5">
-        <v>14.849584666810578</v>
+        <v>11.736983989613789</v>
       </c>
       <c r="E5">
-        <v>89.920455366052721</v>
+        <v>76.148951203304577</v>
       </c>
       <c r="F5">
-        <v>165.14134193782837</v>
+        <v>154.13191914197319</v>
       </c>
       <c r="G5">
         <v>10.01987104432337</v>
       </c>
       <c r="H5">
-        <v>16.694409450525235</v>
+        <v>12.878316354439914</v>
       </c>
       <c r="I5">
-        <v>101.09164219345067</v>
+        <v>83.55385715127251</v>
       </c>
       <c r="J5">
         <v>587.71920551674089</v>
@@ -1760,25 +1760,25 @@
         <v>9.6511733759009619</v>
       </c>
       <c r="AA5">
-        <v>1.9836126857980152</v>
+        <v>1.9836126857980156</v>
       </c>
       <c r="AB5">
         <v>1.7261053403189999</v>
       </c>
       <c r="AC5">
-        <v>0.83816905918204732</v>
+        <v>0.83648168772412734</v>
       </c>
       <c r="AD5">
         <v>1.454362500605322</v>
       </c>
       <c r="AE5">
-        <v>332.3267762931207</v>
+        <v>277.45098394714086</v>
       </c>
       <c r="AF5">
         <v>2.9521677437943903</v>
       </c>
       <c r="AG5">
-        <v>17712.825989710611</v>
+        <v>16531.963934539435</v>
       </c>
       <c r="AH5">
         <v>260.89987793611488</v>
@@ -1799,43 +1799,43 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-4.436947839206149</v>
+        <v>-4.4368913249324438</v>
       </c>
       <c r="AO5">
         <v>-2.2148830481732484</v>
       </c>
       <c r="AP5">
-        <v>-1.9189130569442252</v>
+        <v>-1.9190437250584922</v>
       </c>
       <c r="AQ5">
         <v>-1.6704281981530393</v>
       </c>
       <c r="AR5">
-        <v>755.98873190415907</v>
+        <v>704.218381138802</v>
       </c>
       <c r="AS5">
         <v>22.275422424764045</v>
       </c>
       <c r="AT5">
-        <v>-2.7314492530746461</v>
+        <v>-1.62503942904441</v>
       </c>
       <c r="AU5">
-        <v>-1.3738280889962038</v>
+        <v>-0.51647672518654286</v>
       </c>
       <c r="AV5">
-        <v>-1.6939991505781744</v>
+        <v>-1.007822279457901</v>
       </c>
       <c r="AW5">
-        <v>0.8678696058155978</v>
+        <v>0.32626676910360825</v>
       </c>
       <c r="AX5">
-        <v>3.7001507952633967</v>
+        <v>2.2013555364225277</v>
       </c>
       <c r="AY5">
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>-9.9066681348828549</v>
+        <v>-5.8938405359429646</v>
       </c>
       <c r="BA5">
         <v>0</v>
@@ -1847,52 +1847,52 @@
         <v>0</v>
       </c>
       <c r="BD5">
-        <v>-0.30188965915488286</v>
+        <v>-0.17959682165339611</v>
       </c>
       <c r="BE5">
         <v>0</v>
       </c>
       <c r="BF5">
-        <v>-0.3993308979546471</v>
+        <v>-0.25503001123453695</v>
       </c>
       <c r="BG5">
         <v>0</v>
       </c>
       <c r="BH5">
-        <v>52.973022335444995</v>
+        <v>53.06744193577466</v>
       </c>
       <c r="BI5">
-        <v>39.086163973472168</v>
+        <v>38.79035547773109</v>
       </c>
       <c r="BJ5">
-        <v>-5.6808114058581332</v>
+        <v>-3.3884636917431585</v>
       </c>
       <c r="BK5">
         <v>0</v>
       </c>
       <c r="BL5">
-        <v>-8.919729324002148</v>
+        <v>-5.3010976477141876</v>
       </c>
       <c r="BM5">
         <v>0</v>
       </c>
       <c r="BN5">
-        <v>1.6873913951085762</v>
+        <v>1.5039993694619136</v>
       </c>
       <c r="BO5">
         <v>90</v>
       </c>
       <c r="BP5">
-        <v>-2.0852573326425214</v>
+        <v>-2.1071085867232013</v>
       </c>
       <c r="BQ5">
-        <v>4.0188974311157732</v>
+        <v>3.7948728042924418</v>
       </c>
       <c r="BR5">
-        <v>29.636857440277812</v>
+        <v>29.648953827983458</v>
       </c>
       <c r="BS5">
-        <v>-3.7926015036242848</v>
+        <v>-3.6968475768887976</v>
       </c>
       <c r="BT5">
         <v>-1.5638802210273644</v>
@@ -1907,25 +1907,25 @@
         <v>-12.327455386870151</v>
       </c>
       <c r="BX5">
-        <v>-69.749326855159012</v>
+        <v>-47.02182376698606</v>
       </c>
       <c r="BY5">
         <v>0</v>
       </c>
       <c r="BZ5">
-        <v>79.7552984586243</v>
+        <v>54.656155903536622</v>
       </c>
       <c r="CA5">
         <v>0</v>
       </c>
       <c r="CB5">
-        <v>180.84738153587182</v>
+        <v>138.21024834981358</v>
       </c>
       <c r="CC5">
         <v>0</v>
       </c>
       <c r="CD5">
-        <v>1.1059048701809884</v>
+        <v>1.4470706940182541</v>
       </c>
       <c r="CE5">
         <v>1E+307</v>
@@ -1936,28 +1936,28 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>223.10189816061211</v>
+        <v>227.86618491185288</v>
       </c>
       <c r="C6">
-        <v>137.83922327259018</v>
+        <v>128.64994172108428</v>
       </c>
       <c r="D6">
-        <v>10.764423524301181</v>
+        <v>8.5085238893902932</v>
       </c>
       <c r="E6">
-        <v>78.094052394749127</v>
+        <v>66.137020938858626</v>
       </c>
       <c r="F6">
-        <v>137.83922327259026</v>
+        <v>128.64994172108425</v>
       </c>
       <c r="G6">
         <v>9.4151145750213665</v>
       </c>
       <c r="H6">
-        <v>12.10986637593966</v>
+        <v>9.3476864478934925</v>
       </c>
       <c r="I6">
-        <v>87.855010267949936</v>
+        <v>72.659857617032358</v>
       </c>
       <c r="J6">
         <v>807.93911464931659</v>
@@ -2011,25 +2011,25 @@
         <v>9.35538912409344</v>
       </c>
       <c r="AA6">
-        <v>1.6006930222828681</v>
+        <v>1.6006930222828686</v>
       </c>
       <c r="AB6">
         <v>1.6801900894488955</v>
       </c>
       <c r="AC6">
-        <v>0.74196531251140241</v>
+        <v>0.74047261927202557</v>
       </c>
       <c r="AD6">
         <v>1.4603397275626393</v>
       </c>
       <c r="AE6">
-        <v>222.43043639616374</v>
+        <v>184.80481267068026</v>
       </c>
       <c r="AF6">
         <v>2.6257329219647314</v>
       </c>
       <c r="AG6">
-        <v>12339.631513745719</v>
+        <v>11516.985597147761</v>
       </c>
       <c r="AH6">
         <v>230.35788692654094</v>
@@ -2050,43 +2050,43 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>-4.0479293427221243</v>
+        <v>-4.0478890016717912</v>
       </c>
       <c r="AO6">
         <v>-2.147349376293195</v>
       </c>
       <c r="AP6">
-        <v>-1.5484046929863335</v>
+        <v>-1.5485101507828181</v>
       </c>
       <c r="AQ6">
         <v>-1.6259930541192122</v>
       </c>
       <c r="AR6">
-        <v>576.48379786518512</v>
+        <v>537.00519899110543</v>
       </c>
       <c r="AS6">
         <v>20.289462983161943</v>
       </c>
       <c r="AT6">
-        <v>-3.2720907585362862</v>
+        <v>-1.8429016915894025</v>
       </c>
       <c r="AU6">
-        <v>-1.5742253103314798</v>
+        <v>-0.57875930526892638</v>
       </c>
       <c r="AV6">
-        <v>-1.8277445052541788</v>
+        <v>-1.0294193190512042</v>
       </c>
       <c r="AW6">
-        <v>0.97602145388777073</v>
+        <v>0.35883141687050391</v>
       </c>
       <c r="AX6">
-        <v>3.1186845658781492</v>
+        <v>1.7565005026210268</v>
       </c>
       <c r="AY6">
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>-8.6813715712078316</v>
+        <v>-4.8895081263124567</v>
       </c>
       <c r="BA6">
         <v>0</v>
@@ -2098,52 +2098,52 @@
         <v>0</v>
       </c>
       <c r="BD6">
-        <v>-0.26151331918794318</v>
+        <v>-0.14728232878657627</v>
       </c>
       <c r="BE6">
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>-0.45363515879608451</v>
+        <v>-0.27426611336963191</v>
       </c>
       <c r="BG6">
         <v>0</v>
       </c>
       <c r="BH6">
-        <v>56.245634483742236</v>
+        <v>56.308574416468247</v>
       </c>
       <c r="BI6">
-        <v>39.626891438527338</v>
+        <v>39.42129917029834</v>
       </c>
       <c r="BJ6">
-        <v>-5.4850832676310759</v>
+        <v>-3.0938865736958827</v>
       </c>
       <c r="BK6">
         <v>0</v>
       </c>
       <c r="BL6">
-        <v>-7.4166210180900922</v>
+        <v>-4.1737812115739636</v>
       </c>
       <c r="BM6">
         <v>0</v>
       </c>
       <c r="BN6">
-        <v>1.3962125624885724</v>
+        <v>1.2400938534729333</v>
       </c>
       <c r="BO6">
         <v>90</v>
       </c>
       <c r="BP6">
-        <v>-2.1152136763824037</v>
+        <v>-1.5902005433073589</v>
       </c>
       <c r="BQ6">
-        <v>3.9288534337784311</v>
+        <v>3.7065248012213963</v>
       </c>
       <c r="BR6">
-        <v>28.585055657085686</v>
+        <v>29.138048013286262</v>
       </c>
       <c r="BS6">
-        <v>-3.325905946190193</v>
+        <v>-3.2284041426901791</v>
       </c>
       <c r="BT6">
         <v>-1.570421558155559</v>
@@ -2158,25 +2158,25 @@
         <v>-12.32703842153494</v>
       </c>
       <c r="BX6">
-        <v>-98.155949210414164</v>
+        <v>-62.6286119138999</v>
       </c>
       <c r="BY6">
         <v>0</v>
       </c>
       <c r="BZ6">
-        <v>99.196856110755235</v>
+        <v>64.607616156344008</v>
       </c>
       <c r="CA6">
         <v>0</v>
       </c>
       <c r="CB6">
-        <v>187.05241645221872</v>
+        <v>137.26774777064537</v>
       </c>
       <c r="CC6">
         <v>0</v>
       </c>
       <c r="CD6">
-        <v>1.0692190124744452</v>
+        <v>1.4570064945931158</v>
       </c>
       <c r="CE6">
         <v>1E+307</v>
@@ -2187,28 +2187,28 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>219.96846721960262</v>
+        <v>224.2498532157588</v>
       </c>
       <c r="C7">
-        <v>119.4628881403286</v>
+        <v>111.49869559763987</v>
       </c>
       <c r="D7">
-        <v>8.2582321164244927</v>
+        <v>6.5278183931213913</v>
       </c>
       <c r="E7">
-        <v>69.128013268219789</v>
+        <v>58.546141352882046</v>
       </c>
       <c r="F7">
-        <v>119.4628881403285</v>
+        <v>111.49869559763994</v>
       </c>
       <c r="G7">
         <v>9.3471062037915491</v>
       </c>
       <c r="H7">
-        <v>9.29394760218482</v>
+        <v>7.1774231723472193</v>
       </c>
       <c r="I7">
-        <v>77.797780941538718</v>
+        <v>64.372261342393159</v>
       </c>
       <c r="J7">
         <v>1070.8013292006924</v>
@@ -2262,25 +2262,25 @@
         <v>9.3215394088520238</v>
       </c>
       <c r="AA7">
-        <v>1.3718023362564786</v>
+        <v>1.3718023362564789</v>
       </c>
       <c r="AB7">
         <v>1.7245067896635398</v>
       </c>
       <c r="AC7">
-        <v>0.68321485575599816</v>
+        <v>0.68183727518687742</v>
       </c>
       <c r="AD7">
         <v>1.5035805315702051</v>
       </c>
       <c r="AE7">
-        <v>163.38645004560189</v>
+        <v>135.32521397544198</v>
       </c>
       <c r="AF7">
         <v>2.7267117614324992</v>
       </c>
       <c r="AG7">
-        <v>9268.548428521055</v>
+        <v>8650.6427634106749</v>
       </c>
       <c r="AH7">
         <v>227.05067869090993</v>
@@ -2301,43 +2301,43 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>-3.765560677589018</v>
+        <v>-3.7655287711184138</v>
       </c>
       <c r="AO7">
         <v>-2.1421242656031856</v>
       </c>
       <c r="AP7">
-        <v>-1.3269958833756363</v>
+        <v>-1.3270864195597807</v>
       </c>
       <c r="AQ7">
         <v>-1.6688733081955107</v>
       </c>
       <c r="AR7">
-        <v>465.13145273417166</v>
+        <v>433.275897428434</v>
       </c>
       <c r="AS7">
         <v>20.069786171461484</v>
       </c>
       <c r="AT7">
-        <v>-3.8295773603398482</v>
+        <v>-2.1000908105089491</v>
       </c>
       <c r="AU7">
-        <v>-1.8529736830045203</v>
+        <v>-0.55363238089769207</v>
       </c>
       <c r="AV7">
-        <v>-1.9849475658556999</v>
+        <v>-1.0885196328886095</v>
       </c>
       <c r="AW7">
-        <v>1.0990050783030176</v>
+        <v>0.32836127339541388</v>
       </c>
       <c r="AX7">
-        <v>2.7285379350920538</v>
+        <v>1.4962949966633843</v>
       </c>
       <c r="AY7">
         <v>0</v>
       </c>
       <c r="AZ7">
-        <v>-7.8139897381680381</v>
+        <v>-4.2850911467373116</v>
       </c>
       <c r="BA7">
         <v>0</v>
@@ -2349,52 +2349,52 @@
         <v>0</v>
       </c>
       <c r="BD7">
-        <v>-0.23414882550694149</v>
+        <v>-0.12839822733106118</v>
       </c>
       <c r="BE7">
         <v>0</v>
       </c>
       <c r="BF7">
-        <v>-0.503403552115321</v>
+        <v>-0.29634288012124937</v>
       </c>
       <c r="BG7">
         <v>0</v>
       </c>
       <c r="BH7">
-        <v>58.660892618044208</v>
+        <v>58.713164682157384</v>
       </c>
       <c r="BI7">
-        <v>39.502893420827654</v>
+        <v>38.792182807243449</v>
       </c>
       <c r="BJ7">
-        <v>-5.2548415480420427</v>
+        <v>-2.8848853110343389</v>
       </c>
       <c r="BK7">
         <v>0</v>
       </c>
       <c r="BL7">
-        <v>-6.3945285358971482</v>
+        <v>-3.504046460174961</v>
       </c>
       <c r="BM7">
         <v>0</v>
       </c>
       <c r="BN7">
-        <v>1.228879357594548</v>
+        <v>1.0885340642489656</v>
       </c>
       <c r="BO7">
         <v>90</v>
       </c>
       <c r="BP7">
-        <v>-2.1322332022926767</v>
+        <v>-1.6052535037712894</v>
       </c>
       <c r="BQ7">
-        <v>3.8745526447089471</v>
+        <v>3.6532377330812325</v>
       </c>
       <c r="BR7">
-        <v>27.516147713550986</v>
+        <v>28.067903195391025</v>
       </c>
       <c r="BS7">
-        <v>-3.0709370385796544</v>
+        <v>-2.9702063165834431</v>
       </c>
       <c r="BT7">
         <v>-1.6177891770057946</v>
@@ -2409,25 +2409,25 @@
         <v>-12.323969454424388</v>
       </c>
       <c r="BX7">
-        <v>-126.08458108711041</v>
+        <v>-78.530553848441144</v>
       </c>
       <c r="BY7">
         <v>0</v>
       </c>
       <c r="BZ7">
-        <v>117.75145631887767</v>
+        <v>74.688590254849942</v>
       </c>
       <c r="CA7">
         <v>0</v>
       </c>
       <c r="CB7">
-        <v>195.54988521670603</v>
+        <v>139.06116735470425</v>
       </c>
       <c r="CC7">
         <v>0</v>
       </c>
       <c r="CD7">
-        <v>1.0227569286392697</v>
+        <v>1.438216029712009</v>
       </c>
       <c r="CE7">
         <v>1E+307</v>
@@ -2438,28 +2438,28 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>217.49227741305941</v>
+        <v>221.38721110996937</v>
       </c>
       <c r="C8">
-        <v>106.27633537609465</v>
+        <v>99.191246351021576</v>
       </c>
       <c r="D8">
-        <v>6.5886259439306345</v>
+        <v>5.20812659911914</v>
       </c>
       <c r="E8">
-        <v>61.995230834922559</v>
+        <v>52.505909449795929</v>
       </c>
       <c r="F8">
-        <v>106.27633537609447</v>
+        <v>99.1912463510215</v>
       </c>
       <c r="G8">
         <v>9.6991219736553038</v>
       </c>
       <c r="H8">
-        <v>7.4199261596953328</v>
+        <v>5.7329970010426052</v>
       </c>
       <c r="I8">
-        <v>69.817294070570227</v>
+        <v>57.797408661994936</v>
       </c>
       <c r="J8">
         <v>1382.2001602781577</v>
@@ -2519,19 +2519,19 @@
         <v>1.7200608283329932</v>
       </c>
       <c r="AC8">
-        <v>0.60811252527876913</v>
+        <v>0.6068898669454259</v>
       </c>
       <c r="AD8">
         <v>1.472743141682521</v>
       </c>
       <c r="AE8">
-        <v>125.87048067291018</v>
+        <v>103.92395235655846</v>
       </c>
       <c r="AF8">
         <v>2.8289924027063811</v>
       </c>
       <c r="AG8">
-        <v>7335.1037857593947</v>
+        <v>6846.0953427056211</v>
       </c>
       <c r="AH8">
         <v>244.46766155159241</v>
@@ -2552,43 +2552,43 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-3.5485033758396356</v>
+        <v>-3.5484796095473148</v>
       </c>
       <c r="AO8">
         <v>-2.1802316745603507</v>
       </c>
       <c r="AP8">
-        <v>-1.1136896677919845</v>
+        <v>-1.1137653905194065</v>
       </c>
       <c r="AQ8">
         <v>-1.6645757194346198</v>
       </c>
       <c r="AR8">
-        <v>390.27949978318128</v>
+        <v>363.55172355491413</v>
       </c>
       <c r="AS8">
         <v>21.214335002704665</v>
       </c>
       <c r="AT8">
-        <v>-4.2750859759416677</v>
+        <v>-2.4363393196226713</v>
       </c>
       <c r="AU8">
-        <v>-2.0738610816682042</v>
+        <v>-0.37143780567191709</v>
       </c>
       <c r="AV8">
-        <v>-2.0674995787182389</v>
+        <v>-1.1782524480867382</v>
       </c>
       <c r="AW8">
-        <v>1.1478511652414873</v>
+        <v>0.20558528332683351</v>
       </c>
       <c r="AX8">
-        <v>2.347595203278539</v>
+        <v>1.3378768362770168</v>
       </c>
       <c r="AY8">
         <v>0</v>
       </c>
       <c r="AZ8">
-        <v>-6.9451182771809634</v>
+        <v>-3.9579706310816243</v>
       </c>
       <c r="BA8">
         <v>0</v>
@@ -2600,52 +2600,52 @@
         <v>0</v>
       </c>
       <c r="BD8">
-        <v>-0.21362271413742515</v>
+        <v>-0.12173668659415023</v>
       </c>
       <c r="BE8">
         <v>0</v>
       </c>
       <c r="BF8">
-        <v>-0.54735827594352926</v>
+        <v>-0.334853828786104</v>
       </c>
       <c r="BG8">
         <v>0</v>
       </c>
       <c r="BH8">
-        <v>61.183145390915328</v>
+        <v>61.23604142764129</v>
       </c>
       <c r="BI8">
-        <v>40.363874296845914</v>
+        <v>36.427618803166183</v>
       </c>
       <c r="BJ8">
-        <v>-4.9535013045536793</v>
+        <v>-2.8258053812142556</v>
       </c>
       <c r="BK8">
         <v>0</v>
       </c>
       <c r="BL8">
-        <v>-5.4045070032588987</v>
+        <v>-3.0773803621021285</v>
       </c>
       <c r="BM8">
         <v>0</v>
       </c>
       <c r="BN8">
-        <v>1.0725889679910743</v>
+        <v>0.94709755761312175</v>
       </c>
       <c r="BO8">
         <v>90</v>
       </c>
       <c r="BP8">
-        <v>-1.6063742127274443</v>
+        <v>-1.6206879724752104</v>
       </c>
       <c r="BQ8">
-        <v>3.8073133876976271</v>
+        <v>3.5863620095457702</v>
       </c>
       <c r="BR8">
-        <v>-14.295501400246511</v>
+        <v>26.997303235536581</v>
       </c>
       <c r="BS8">
-        <v>-2.8496789534822136</v>
+        <v>-2.6897511748923679</v>
       </c>
       <c r="BT8">
         <v>-1.5840004319127954</v>
@@ -2660,25 +2660,25 @@
         <v>-12.326167548416786</v>
       </c>
       <c r="BX8">
-        <v>-151.01641899284408</v>
+        <v>-98.245600203662292</v>
       </c>
       <c r="BY8">
         <v>0</v>
       </c>
       <c r="BZ8">
-        <v>101.61320856709382</v>
+        <v>85.272788526482245</v>
       </c>
       <c r="CA8">
         <v>0</v>
       </c>
       <c r="CB8">
-        <v>171.43137646208288</v>
+        <v>143.07058904833096</v>
       </c>
       <c r="CC8">
         <v>0</v>
       </c>
       <c r="CD8">
-        <v>0.87498568287571865</v>
+        <v>1.0484335110225078</v>
       </c>
       <c r="CE8">
         <v>1E+307</v>
@@ -2689,28 +2689,28 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>215.63047275898356</v>
+        <v>219.2319142121199</v>
       </c>
       <c r="C9">
-        <v>98.026347774387517</v>
+        <v>91.491257922761775</v>
       </c>
       <c r="D9">
-        <v>5.5678083888790075</v>
+        <v>4.4012439464684556</v>
       </c>
       <c r="E9">
-        <v>56.79910060194829</v>
+        <v>48.105622836490546</v>
       </c>
       <c r="F9">
-        <v>98.026347774387474</v>
+        <v>91.491257922761662</v>
       </c>
       <c r="G9">
         <v>10.774453553069906</v>
       </c>
       <c r="H9">
-        <v>6.2795509008696149</v>
+        <v>4.8551018671320749</v>
       </c>
       <c r="I9">
-        <v>64.0598272142334</v>
+        <v>53.066292642197865</v>
       </c>
       <c r="J9">
         <v>1733.6095261481089</v>
@@ -2764,25 +2764,25 @@
         <v>10.007985743262324</v>
       </c>
       <c r="AA9">
-        <v>0.87090477911883868</v>
+        <v>0.87090477911883857</v>
       </c>
       <c r="AB9">
         <v>1.5176573654883232</v>
       </c>
       <c r="AC9">
-        <v>0.47919506017180769</v>
+        <v>0.47823219629660391</v>
       </c>
       <c r="AD9">
         <v>1.2357974253789732</v>
       </c>
       <c r="AE9">
-        <v>102.8490968323906</v>
+        <v>84.459664034039548</v>
       </c>
       <c r="AF9">
         <v>2.5603807269452385</v>
       </c>
       <c r="AG9">
-        <v>6240.2294751407344</v>
+        <v>5824.2133716757426</v>
       </c>
       <c r="AH9">
         <v>301.62252444184361</v>
@@ -2803,43 +2803,43 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>-3.403611355538553</v>
+        <v>-3.4035971972550261</v>
       </c>
       <c r="AO9">
         <v>-2.284272867993022</v>
       </c>
       <c r="AP9">
-        <v>-0.84246836458719854</v>
+        <v>-0.84252556265014755</v>
       </c>
       <c r="AQ9">
         <v>-1.4687339335024379</v>
       </c>
       <c r="AR9">
-        <v>345.72145485741544</v>
+        <v>322.04473190798467</v>
       </c>
       <c r="AS9">
         <v>24.838979525820641</v>
       </c>
       <c r="AT9">
-        <v>-3.9392012531629952</v>
+        <v>-3.3683025208205319</v>
       </c>
       <c r="AU9">
-        <v>-2.1890935320711487</v>
+        <v>-0.46032340627664342</v>
       </c>
       <c r="AV9">
-        <v>-1.7954750178514323</v>
+        <v>-1.535261247148326</v>
       </c>
       <c r="AW9">
-        <v>1.1791368711930625</v>
+        <v>0.24794934207330752</v>
       </c>
       <c r="AX9">
-        <v>1.7405060132337926</v>
+        <v>1.4882587649390404</v>
       </c>
       <c r="AY9">
         <v>0</v>
       </c>
       <c r="AZ9">
-        <v>-5.3143702853284189</v>
+        <v>-4.5441716932518368</v>
       </c>
       <c r="BA9">
         <v>0</v>
@@ -2851,52 +2851,52 @@
         <v>0</v>
       </c>
       <c r="BD9">
-        <v>-0.18475836595076761</v>
+        <v>-0.15797666138584476</v>
       </c>
       <c r="BE9">
         <v>0</v>
       </c>
       <c r="BF9">
-        <v>-0.5344139432334819</v>
+        <v>-0.49054260397273691</v>
       </c>
       <c r="BG9">
         <v>0</v>
       </c>
       <c r="BH9">
-        <v>64.505685732689741</v>
+        <v>64.5508249972046</v>
       </c>
       <c r="BI9">
-        <v>44.926590155176719</v>
+        <v>42.036039503590892</v>
       </c>
       <c r="BJ9">
-        <v>-4.0477481745226287</v>
+        <v>-3.4637161766895233</v>
       </c>
       <c r="BK9">
         <v>0</v>
       </c>
       <c r="BL9">
-        <v>-3.858448836946446</v>
+        <v>-3.2965255613309679</v>
       </c>
       <c r="BM9">
         <v>0</v>
       </c>
       <c r="BN9">
-        <v>0.90009030932000944</v>
+        <v>0.79071737478103044</v>
       </c>
       <c r="BO9">
         <v>90</v>
       </c>
       <c r="BP9">
-        <v>-2.1720292065261364</v>
+        <v>-1.640828990342506</v>
       </c>
       <c r="BQ9">
-        <v>3.694317327481325</v>
+        <v>3.4735400609035092</v>
       </c>
       <c r="BR9">
-        <v>-9.9341744287742255</v>
+        <v>-12.639604606913037</v>
       </c>
       <c r="BS9">
-        <v>-2.8799822053248469</v>
+        <v>-2.6938984592094961</v>
       </c>
       <c r="BT9">
         <v>-1.3256586975254614</v>
@@ -2911,25 +2911,25 @@
         <v>-12.34149785689093</v>
       </c>
       <c r="BX9">
-        <v>-146.7372451815524</v>
+        <v>-143.37963571516096</v>
       </c>
       <c r="BY9">
         <v>0</v>
       </c>
       <c r="BZ9">
-        <v>107.20263201112725</v>
+        <v>103.32352318407924</v>
       </c>
       <c r="CA9">
         <v>0</v>
       </c>
       <c r="CB9">
-        <v>171.26329302620871</v>
+        <v>156.39058515851642</v>
       </c>
       <c r="CC9">
         <v>0</v>
       </c>
       <c r="CD9">
-        <v>0.87584442264020479</v>
+        <v>0.9591370212469057</v>
       </c>
       <c r="CE9">
         <v>1E+307</v>
@@ -2940,28 +2940,28 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>214.37176091245323</v>
+        <v>217.7733157987233</v>
       </c>
       <c r="C10">
-        <v>94.6453312276236</v>
+        <v>88.335642479115336</v>
       </c>
       <c r="D10">
-        <v>5.0456652589973343</v>
+        <v>3.9885287066266866</v>
       </c>
       <c r="E10">
-        <v>53.311295903888016</v>
+        <v>45.151974839257782</v>
       </c>
       <c r="F10">
-        <v>94.645331227623529</v>
+        <v>88.3356424791153</v>
       </c>
       <c r="G10">
         <v>12.835509347879874</v>
       </c>
       <c r="H10">
-        <v>5.6972035577669686</v>
+        <v>4.4070668114709619</v>
       </c>
       <c r="I10">
-        <v>60.19529419856012</v>
+        <v>49.890018205424838</v>
       </c>
       <c r="J10">
         <v>2088.0588484221753</v>
@@ -3015,25 +3015,25 @@
         <v>10.923343855945044</v>
       </c>
       <c r="AA10">
-        <v>0.7076817133842016</v>
+        <v>0.70768171338420172</v>
       </c>
       <c r="AB10">
         <v>1.4317343978517629</v>
       </c>
       <c r="AC10">
-        <v>0.39637088337338222</v>
+        <v>0.39557469644678528</v>
       </c>
       <c r="AD10">
         <v>1.0695974996141742</v>
       </c>
       <c r="AE10">
-        <v>93.827884124670859</v>
+        <v>76.82146380562051</v>
       </c>
       <c r="AF10">
         <v>2.8358005488297913</v>
       </c>
       <c r="AG10">
-        <v>5817.06449123661</v>
+        <v>5429.2596783013969</v>
       </c>
       <c r="AH10">
         <v>428.00564304346545</v>
@@ -3054,43 +3054,43 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>-3.342175012787906</v>
+        <v>-3.34216549952355</v>
       </c>
       <c r="AO10">
         <v>-2.4843431793879445</v>
       </c>
       <c r="AP10">
-        <v>-0.68457718934661715</v>
+        <v>-0.68462363242300206</v>
       </c>
       <c r="AQ10">
         <v>-1.3856008078067854</v>
       </c>
       <c r="AR10">
-        <v>327.98639573070392</v>
+        <v>305.52403828704433</v>
       </c>
       <c r="AS10">
         <v>32.296292736522858</v>
       </c>
       <c r="AT10">
-        <v>-4.2537855333001406</v>
+        <v>-4.4143057421039194</v>
       </c>
       <c r="AU10">
-        <v>-2.409351549020462</v>
+        <v>-0.545764715523972</v>
       </c>
       <c r="AV10">
-        <v>-1.866175570311575</v>
+        <v>-1.936597289945974</v>
       </c>
       <c r="AW10">
-        <v>1.2516327111299592</v>
+        <v>0.28351901191341622</v>
       </c>
       <c r="AX10">
-        <v>1.6126816775748927</v>
+        <v>1.6735375899362093</v>
       </c>
       <c r="AY10">
         <v>0</v>
       </c>
       <c r="AZ10">
-        <v>-5.0339253243577433</v>
+        <v>-5.2238847705599234</v>
       </c>
       <c r="BA10">
         <v>0</v>
@@ -3102,52 +3102,52 @@
         <v>0</v>
       </c>
       <c r="BD10">
-        <v>-0.19296288387353164</v>
+        <v>-0.20023932649312895</v>
       </c>
       <c r="BE10">
         <v>0</v>
       </c>
       <c r="BF10">
-        <v>-0.58832587688169091</v>
+        <v>-0.655396307327547</v>
       </c>
       <c r="BG10">
         <v>0</v>
       </c>
       <c r="BH10">
-        <v>66.810665158869313</v>
+        <v>66.7844761499119</v>
       </c>
       <c r="BI10">
-        <v>48.477528756631479</v>
+        <v>45.847999102542111</v>
       </c>
       <c r="BJ10">
-        <v>-3.9922007390823651</v>
+        <v>-4.141206015269896</v>
       </c>
       <c r="BK10">
         <v>0</v>
       </c>
       <c r="BL10">
-        <v>-3.4646038190919031</v>
+        <v>-3.5972368423707977</v>
       </c>
       <c r="BM10">
         <v>0</v>
       </c>
       <c r="BN10">
-        <v>0.80197997040207158</v>
+        <v>0.704182009239085</v>
       </c>
       <c r="BO10">
         <v>90</v>
       </c>
       <c r="BP10">
-        <v>-2.1850510873117774</v>
+        <v>-1.6523744805413707</v>
       </c>
       <c r="BQ10">
-        <v>3.6221171651458106</v>
+        <v>3.4011998565379509</v>
       </c>
       <c r="BR10">
-        <v>-9.3821714985705515</v>
+        <v>-9.3730525585833018</v>
       </c>
       <c r="BS10">
-        <v>-2.9225696120667712</v>
+        <v>-2.7263866448264844</v>
       </c>
       <c r="BT10">
         <v>-1.1456216295590764</v>
@@ -3162,25 +3162,25 @@
         <v>-12.350618387356004</v>
       </c>
       <c r="BX10">
-        <v>-155.41570298749997</v>
+        <v>-184.442903715739</v>
       </c>
       <c r="BY10">
         <v>0</v>
       </c>
       <c r="BZ10">
-        <v>118.76190614187716</v>
+        <v>140.76076290037739</v>
       </c>
       <c r="CA10">
         <v>0</v>
       </c>
       <c r="CB10">
-        <v>178.95816740519226</v>
+        <v>190.65190762374283</v>
       </c>
       <c r="CC10">
         <v>0</v>
       </c>
       <c r="CD10">
-        <v>0.83818471196329392</v>
+        <v>0.78677418898965024</v>
       </c>
       <c r="CE10">
         <v>1E+307</v>
@@ -3191,28 +3191,28 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>213.29647024618566</v>
+        <v>216.52630919808175</v>
       </c>
       <c r="C11">
-        <v>92.6856176422915</v>
+        <v>86.506576466138782</v>
       </c>
       <c r="D11">
-        <v>8.1923336535798033</v>
+        <v>6.4735412282366624</v>
       </c>
       <c r="E11">
-        <v>88.388402235145961</v>
+        <v>74.832937479274733</v>
       </c>
       <c r="F11">
-        <v>92.685617642291348</v>
+        <v>86.506576466138611</v>
       </c>
       <c r="G11">
         <v>15.355359401901744</v>
       </c>
       <c r="H11">
-        <v>9.2224735466543031</v>
+        <v>7.1286651876240885</v>
       </c>
       <c r="I11">
-        <v>99.502746825805218</v>
+        <v>82.406049098642484</v>
       </c>
       <c r="J11">
         <v>2444.19558326151</v>
@@ -3260,31 +3260,31 @@
         <v>46.879455309907051</v>
       </c>
       <c r="Y11">
-        <v>14.676592290009902</v>
+        <v>14.676592290009896</v>
       </c>
       <c r="Z11">
         <v>11.947555160219878</v>
       </c>
       <c r="AA11">
-        <v>0.62944000590753268</v>
+        <v>0.6294400059075328</v>
       </c>
       <c r="AB11">
         <v>1.4624531791287747</v>
       </c>
       <c r="AC11">
-        <v>0.35628959871558818</v>
+        <v>0.35557401829824742</v>
       </c>
       <c r="AD11">
         <v>0.99939722577395429</v>
       </c>
       <c r="AE11">
-        <v>89.164164558795662</v>
+        <v>72.90918189412973</v>
       </c>
       <c r="AF11">
         <v>3.6230559924562384</v>
       </c>
       <c r="AG11">
-        <v>5578.6133301037116</v>
+        <v>5206.7053768511023</v>
       </c>
       <c r="AH11">
         <v>612.52561686014462</v>
@@ -3305,43 +3305,43 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>-3.3064772459638587</v>
+        <v>-3.3064696411257768</v>
       </c>
       <c r="AO11">
         <v>-2.7136193947537377</v>
       </c>
       <c r="AP11">
-        <v>-0.608890824909625</v>
+        <v>-0.60893212023131893</v>
       </c>
       <c r="AQ11">
         <v>-1.4153378375591239</v>
       </c>
       <c r="AR11">
-        <v>317.85083027466692</v>
+        <v>296.08252487112094</v>
       </c>
       <c r="AS11">
         <v>42.258812489328747</v>
       </c>
       <c r="AT11">
-        <v>-4.3426527935241177</v>
+        <v>-4.8744061968127834</v>
       </c>
       <c r="AU11">
-        <v>-2.7590515485943041</v>
+        <v>-0.84367691981809312</v>
       </c>
       <c r="AV11">
-        <v>-1.8186106709563168</v>
+        <v>-2.041297691889743</v>
       </c>
       <c r="AW11">
-        <v>1.4322015499192922</v>
+        <v>0.43794592848771741</v>
       </c>
       <c r="AX11">
-        <v>1.4132797634614316</v>
+        <v>1.586334428375076</v>
       </c>
       <c r="AY11">
         <v>0</v>
       </c>
       <c r="AZ11">
-        <v>-4.57292063238861</v>
+        <v>-5.1328700975790511</v>
       </c>
       <c r="BA11">
         <v>0</v>
@@ -3353,52 +3353,52 @@
         <v>0</v>
       </c>
       <c r="BD11">
-        <v>-0.17923826981904414</v>
+        <v>-0.20118093276862695</v>
       </c>
       <c r="BE11">
         <v>0</v>
       </c>
       <c r="BF11">
-        <v>-0.5639068794130806</v>
+        <v>-0.67947587537021015</v>
       </c>
       <c r="BG11">
         <v>0</v>
       </c>
       <c r="BH11">
-        <v>68.290907782799991</v>
+        <v>68.205827117669941</v>
       </c>
       <c r="BI11">
-        <v>50.047640315103564</v>
+        <v>48.994799514473613</v>
       </c>
       <c r="BJ11">
-        <v>-3.7258171563162716</v>
+        <v>-4.1770271917822415</v>
       </c>
       <c r="BK11">
         <v>0</v>
       </c>
       <c r="BL11">
-        <v>-3.0045381205160924</v>
+        <v>-3.3786470955666577</v>
       </c>
       <c r="BM11">
         <v>0</v>
       </c>
       <c r="BN11">
-        <v>0.73844618241656168</v>
+        <v>0.648931434599893</v>
       </c>
       <c r="BO11">
         <v>90</v>
       </c>
       <c r="BP11">
-        <v>-2.1922027677413016</v>
+        <v>-1.6585999278280263</v>
       </c>
       <c r="BQ11">
-        <v>3.5865029047856227</v>
+        <v>3.3657445978428986</v>
       </c>
       <c r="BR11">
-        <v>-8.8339583894407046</v>
+        <v>-9.3686269065799372</v>
       </c>
       <c r="BS11">
-        <v>-2.9479807421437831</v>
+        <v>-2.7487961571545529</v>
       </c>
       <c r="BT11">
         <v>-1.0698209940408361</v>
@@ -3413,25 +3413,25 @@
         <v>-12.354069675318431</v>
       </c>
       <c r="BX11">
-        <v>-151.04642610448587</v>
+        <v>-193.90255583966743</v>
       </c>
       <c r="BY11">
         <v>0</v>
       </c>
       <c r="BZ11">
-        <v>118.42662805822344</v>
+        <v>151.40146926778272</v>
       </c>
       <c r="CA11">
         <v>0</v>
       </c>
       <c r="CB11">
-        <v>217.93010445625026</v>
+        <v>233.8085056881624</v>
       </c>
       <c r="CC11">
         <v>0</v>
       </c>
       <c r="CD11">
-        <v>0.56440114277416131</v>
+        <v>0.52607153720938138</v>
       </c>
       <c r="CE11">
         <v>1E+307</v>
@@ -4286,28 +4286,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>227.3925046610361</v>
+        <v>235.63216491241906</v>
       </c>
       <c r="C3">
-        <v>109.32280890054773</v>
+        <v>78.7380092777086</v>
       </c>
       <c r="D3">
-        <v>12.753757611958344</v>
+        <v>8.1994120021517425</v>
       </c>
       <c r="E3">
-        <v>116.66145189848341</v>
+        <v>104.13537346661197</v>
       </c>
       <c r="F3">
-        <v>146.21232630334995</v>
+        <v>105.85772424362537</v>
       </c>
       <c r="G3">
-        <v>22.943114979886023</v>
+        <v>27.531737975863223</v>
       </c>
       <c r="H3">
-        <v>14.29024408409536</v>
+        <v>9.4690177625296688</v>
       </c>
       <c r="I3">
-        <v>97.736247315066109</v>
+        <v>89.45041875959167</v>
       </c>
       <c r="J3">
         <v>300.50920160679021</v>
@@ -4355,37 +4355,37 @@
         <v>35.946915467752305</v>
       </c>
       <c r="Y3">
-        <v>28.557268840417869</v>
+        <v>28.557268840417873</v>
       </c>
       <c r="Z3">
-        <v>11.312298784599479</v>
+        <v>11.312298784599481</v>
       </c>
       <c r="AA3">
-        <v>1.0791544037582388</v>
+        <v>1.0791544037582392</v>
       </c>
       <c r="AB3">
-        <v>1.5731425907814127</v>
+        <v>1.5731425907814125</v>
       </c>
       <c r="AC3">
-        <v>0.31001639408022291</v>
+        <v>0.30962217086022292</v>
       </c>
       <c r="AD3">
-        <v>1.136209995352254</v>
+        <v>1.1375564628100969</v>
       </c>
       <c r="AE3">
-        <v>104.86082238185412</v>
+        <v>45.308055881979115</v>
       </c>
       <c r="AF3">
-        <v>7.4064870149948909</v>
+        <v>10.042586514942441</v>
       </c>
       <c r="AG3">
-        <v>33312.315775493167</v>
+        <v>24118.115726380929</v>
       </c>
       <c r="AH3">
-        <v>820.53705027201931</v>
+        <v>984.64491511324263</v>
       </c>
       <c r="AI3">
-        <v>820.53705027201931</v>
+        <v>984.64491511324263</v>
       </c>
       <c r="AJ3">
         <v>22.131117236363469</v>
@@ -4400,136 +4400,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-6.4318966031159714</v>
+        <v>-6.4318894171960626</v>
       </c>
       <c r="AO3">
-        <v>-2.5762645203794174</v>
+        <v>-2.57630029548506</v>
       </c>
       <c r="AP3">
-        <v>-1.0443681114755408</v>
+        <v>-1.0444123660715117</v>
       </c>
       <c r="AQ3">
-        <v>-1.5223563797775503</v>
+        <v>-1.5222958363927817</v>
       </c>
       <c r="AR3">
-        <v>963.27299396499529</v>
+        <v>696.52723362228858</v>
       </c>
       <c r="AS3">
-        <v>59.886164215822049</v>
+        <v>71.946958196113656</v>
       </c>
       <c r="AT3">
-        <v>-2.9505193528069102</v>
+        <v>-2.5388189779966437</v>
       </c>
       <c r="AU3">
-        <v>-0.65993606681700745</v>
+        <v>-0.46474370902606166</v>
       </c>
       <c r="AV3">
-        <v>-1.3346251411363874</v>
+        <v>-1.1483983772568915</v>
       </c>
       <c r="AW3">
-        <v>0.58059874553593172</v>
+        <v>0.40887235601121957</v>
       </c>
       <c r="AX3">
-        <v>1.140220393512118</v>
+        <v>0.98111987348717145</v>
       </c>
       <c r="AY3">
-        <v>0.64397720355320576</v>
+        <v>0.45350507292479275</v>
       </c>
       <c r="AZ3">
-        <v>-3.179591658857452</v>
+        <v>-2.7359277064587375</v>
       </c>
       <c r="BA3">
-        <v>0.78270142238207263</v>
+        <v>0.55119818477610738</v>
       </c>
       <c r="BB3">
-        <v>-0.43718107231023029</v>
+        <v>-0.5297204520242812</v>
       </c>
       <c r="BC3">
-        <v>-0.24245490734612477</v>
+        <v>-0.29135826813007082</v>
       </c>
       <c r="BD3">
-        <v>-0.27601350562670829</v>
+        <v>-0.310942316137982</v>
       </c>
       <c r="BE3">
-        <v>-0.11621594213664806</v>
+        <v>-0.081841629186138617</v>
       </c>
       <c r="BF3">
-        <v>-0.28653715754096848</v>
+        <v>-0.44641803095182231</v>
       </c>
       <c r="BG3">
-        <v>-1.9406142246449567</v>
+        <v>-1.1375273011967229</v>
       </c>
       <c r="BH3">
-        <v>65.1332635085885</v>
+        <v>65.085792298812379</v>
       </c>
       <c r="BI3">
-        <v>37.828768526746678</v>
+        <v>38.074464850833088</v>
       </c>
       <c r="BJ3">
-        <v>-2.4053331917450245</v>
+        <v>-2.0680138640895183</v>
       </c>
       <c r="BK3">
-        <v>0.98867726307179138</v>
+        <v>0.69691940804436814</v>
       </c>
       <c r="BL3">
-        <v>-2.3715560080981657</v>
+        <v>-2.04235532634593</v>
       </c>
       <c r="BM3">
-        <v>0.22326088949925477</v>
+        <v>0.15423886916106733</v>
       </c>
       <c r="BN3">
-        <v>0.17782295141342264</v>
+        <v>0.10629970107469862</v>
       </c>
       <c r="BO3">
-        <v>0.11678691997361775</v>
+        <v>0.12932994935416645</v>
       </c>
       <c r="BP3">
-        <v>-1.3514763519939486</v>
+        <v>-0.72469066125427206</v>
       </c>
       <c r="BQ3">
-        <v>1.9007031683863109</v>
+        <v>1.4631644443707086</v>
       </c>
       <c r="BR3">
-        <v>-19.718404734284046</v>
+        <v>34.665747355781754</v>
       </c>
       <c r="BS3">
-        <v>-1.5113455510331597</v>
+        <v>-1.3308330628627341</v>
       </c>
       <c r="BT3">
-        <v>-0.017070204556956365</v>
+        <v>-0.014050038681906673</v>
       </c>
       <c r="BU3">
-        <v>1.0849653514407158</v>
+        <v>1.2096431137820558</v>
       </c>
       <c r="BV3">
-        <v>13.697811170325119</v>
+        <v>13.697356690149816</v>
       </c>
       <c r="BW3">
-        <v>-1.8731229664636473</v>
+        <v>-1.8764434998649049</v>
       </c>
       <c r="BX3">
-        <v>-43.695189150989435</v>
+        <v>-66.845172528390563</v>
       </c>
       <c r="BY3">
-        <v>144.83451771036604</v>
+        <v>83.947085129763849</v>
       </c>
       <c r="BZ3">
-        <v>33.263973878945094</v>
+        <v>63.679293447196471</v>
       </c>
       <c r="CA3">
-        <v>-253.76652353758803</v>
+        <v>-132.36404522829506</v>
       </c>
       <c r="CB3">
-        <v>131.00053456540746</v>
+        <v>153.13036292516296</v>
       </c>
       <c r="CC3">
-        <v>144.84751811461331</v>
+        <v>83.954791823604609</v>
       </c>
       <c r="CD3">
-        <v>1.5267113272743302</v>
+        <v>1.3060767060138354</v>
       </c>
       <c r="CE3">
-        <v>1.3807623534270448</v>
+        <v>2.3822344818651349</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -4537,28 +4537,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>227.93499130722384</v>
+        <v>234.22391635587769</v>
       </c>
       <c r="C4">
-        <v>88.8225275127105</v>
+        <v>65.367803385166141</v>
       </c>
       <c r="D4">
-        <v>8.7327014823962035</v>
+        <v>5.8487529619814831</v>
       </c>
       <c r="E4">
-        <v>98.316291226305779</v>
+        <v>89.47452199852772</v>
       </c>
       <c r="F4">
-        <v>118.31283477433323</v>
+        <v>85.658492376617275</v>
       </c>
       <c r="G4">
-        <v>22.492189172918533</v>
+        <v>26.99062700750223</v>
       </c>
       <c r="H4">
-        <v>9.7405530402555485</v>
+        <v>6.5535940054302158</v>
       </c>
       <c r="I4">
-        <v>82.328794325944614</v>
+        <v>76.508397750170886</v>
       </c>
       <c r="J4">
         <v>422.81391004163669</v>
@@ -4606,7 +4606,7 @@
         <v>31.4243636924555</v>
       </c>
       <c r="Y4">
-        <v>25.688610072706254</v>
+        <v>25.688610072706247</v>
       </c>
       <c r="Z4">
         <v>11.200580721556491</v>
@@ -4615,28 +4615,28 @@
         <v>1.0154478267180622</v>
       </c>
       <c r="AB4">
-        <v>1.7281251002563176</v>
+        <v>1.7281251002563185</v>
       </c>
       <c r="AC4">
-        <v>0.32428117114824051</v>
+        <v>0.32386879177481265</v>
       </c>
       <c r="AD4">
-        <v>1.2592723677859543</v>
+        <v>1.2607665999180948</v>
       </c>
       <c r="AE4">
-        <v>69.645914971916341</v>
+        <v>30.380093758169771</v>
       </c>
       <c r="AF4">
-        <v>8.2425865152456659</v>
+        <v>11.000859057671194</v>
       </c>
       <c r="AG4">
-        <v>21812.315138881117</v>
+        <v>15792.115519296898</v>
       </c>
       <c r="AH4">
-        <v>788.6698553753273</v>
+        <v>946.40436332930744</v>
       </c>
       <c r="AI4">
-        <v>788.6698553753273</v>
+        <v>946.40436332930744</v>
       </c>
       <c r="AJ4">
         <v>19.907983649810767</v>
@@ -4651,136 +4651,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-5.7862810122799333</v>
+        <v>-5.7862739391610738</v>
       </c>
       <c r="AO4">
-        <v>-2.5578008700849435</v>
+        <v>-2.5578444820230941</v>
       </c>
       <c r="AP4">
-        <v>-0.98271469755601815</v>
+        <v>-0.98275634358126152</v>
       </c>
       <c r="AQ4">
-        <v>-1.6723170220624173</v>
+        <v>-1.6722503159129676</v>
       </c>
       <c r="AR4">
-        <v>701.16808515477032</v>
+        <v>507.0034136370092</v>
       </c>
       <c r="AS4">
-        <v>58.1297428989283</v>
+        <v>69.8366802950334</v>
       </c>
       <c r="AT4">
-        <v>-3.6231198494125545</v>
+        <v>-2.6061037513318377</v>
       </c>
       <c r="AU4">
-        <v>-0.91047484257842137</v>
+        <v>-0.51875892193421691</v>
       </c>
       <c r="AV4">
-        <v>-1.5521252952578308</v>
+        <v>-1.1164410018521243</v>
       </c>
       <c r="AW4">
-        <v>0.75042999144090006</v>
+        <v>0.42757057651865243</v>
       </c>
       <c r="AX4">
-        <v>0.97730158155928748</v>
+        <v>0.70297131305141736</v>
       </c>
       <c r="AY4">
-        <v>0.54814389810815478</v>
+        <v>0.31231454659650676</v>
       </c>
       <c r="AZ4">
-        <v>-2.7873408397582353</v>
+        <v>-2.0049293759664497</v>
       </c>
       <c r="BA4">
-        <v>0.76342726444343145</v>
+        <v>0.43497599950846677</v>
       </c>
       <c r="BB4">
-        <v>-0.54750283997061489</v>
+        <v>-0.54990826059300979</v>
       </c>
       <c r="BC4">
-        <v>-0.27529095096088785</v>
+        <v>-0.27477403425208335</v>
       </c>
       <c r="BD4">
-        <v>-0.22793244091646578</v>
+        <v>-0.16394909511116848</v>
       </c>
       <c r="BE4">
-        <v>-0.13163776201911345</v>
+        <v>-0.0750023175139001</v>
       </c>
       <c r="BF4">
-        <v>-0.32507532179841547</v>
+        <v>-0.32336881902840275</v>
       </c>
       <c r="BG4">
-        <v>-2.2645509072351384</v>
+        <v>-1.0739673935966578</v>
       </c>
       <c r="BH4">
-        <v>65.981635663288969</v>
+        <v>65.801103834125158</v>
       </c>
       <c r="BI4">
-        <v>37.547372726010863</v>
+        <v>37.862108483434262</v>
       </c>
       <c r="BJ4">
-        <v>-2.1482085507313773</v>
+        <v>-1.5406004683483874</v>
       </c>
       <c r="BK4">
-        <v>0.899841432177181</v>
+        <v>0.51354153075582532</v>
       </c>
       <c r="BL4">
-        <v>-2.0272117207798064</v>
+        <v>-1.4630313279322424</v>
       </c>
       <c r="BM4">
-        <v>0.27123480246108511</v>
+        <v>0.15172208920633498</v>
       </c>
       <c r="BN4">
-        <v>0.17263858604421381</v>
+        <v>0.10467297001672557</v>
       </c>
       <c r="BO4">
-        <v>0.18049654625208644</v>
+        <v>0.1967632714921661</v>
       </c>
       <c r="BP4">
-        <v>-1.3510525385013317</v>
+        <v>-0.72426015096882124</v>
       </c>
       <c r="BQ4">
-        <v>1.915049207248875</v>
+        <v>1.4777924561896667</v>
       </c>
       <c r="BR4">
-        <v>-20.351153792613747</v>
+        <v>34.665081744198218</v>
       </c>
       <c r="BS4">
-        <v>-1.5276329339640091</v>
+        <v>-1.3881560141651013</v>
       </c>
       <c r="BT4">
-        <v>-0.012317523461321729</v>
+        <v>-0.0087942181642024757</v>
       </c>
       <c r="BU4">
-        <v>1.1333896059896842</v>
+        <v>1.2580571617601084</v>
       </c>
       <c r="BV4">
-        <v>13.687305227983124</v>
+        <v>13.686656718897893</v>
       </c>
       <c r="BW4">
-        <v>-2.0899298663566923</v>
+        <v>-2.0941726550862674</v>
       </c>
       <c r="BX4">
-        <v>-59.1947164859123</v>
+        <v>-75.00721373525073</v>
       </c>
       <c r="BY4">
-        <v>123.73614051791172</v>
+        <v>58.729968875559287</v>
       </c>
       <c r="BZ4">
-        <v>45.227992768106652</v>
+        <v>73.606057929592311</v>
       </c>
       <c r="CA4">
-        <v>-232.86446223697558</v>
+        <v>-99.954224907527134</v>
       </c>
       <c r="CB4">
-        <v>127.55720131659352</v>
+        <v>150.11480397157607</v>
       </c>
       <c r="CC4">
-        <v>123.75686106668938</v>
+        <v>58.7397876237791</v>
       </c>
       <c r="CD4">
-        <v>1.567924021032771</v>
+        <v>1.3323136340228616</v>
       </c>
       <c r="CE4">
-        <v>1.6160720163403721</v>
+        <v>3.4048471758354775</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -4788,28 +4788,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>227.168953466399</v>
+        <v>232.5503088636367</v>
       </c>
       <c r="C5">
-        <v>69.7722169687325</v>
+        <v>53.432785309065871</v>
       </c>
       <c r="D5">
-        <v>6.0502882681749695</v>
+        <v>4.0696096399767185</v>
       </c>
       <c r="E5">
-        <v>86.714863466160566</v>
+        <v>76.1631574404607</v>
       </c>
       <c r="F5">
-        <v>92.681334890838187</v>
+        <v>67.101286460966847</v>
       </c>
       <c r="G5">
-        <v>20.466626125882186</v>
+        <v>24.559951351058618</v>
       </c>
       <c r="H5">
-        <v>6.7048308141983783</v>
+        <v>4.5047531502437614</v>
       </c>
       <c r="I5">
-        <v>72.342838200328615</v>
+        <v>67.133633166097326</v>
       </c>
       <c r="J5">
         <v>588.53643886798193</v>
@@ -4857,37 +4857,37 @@
         <v>29.786781935589474</v>
       </c>
       <c r="Y5">
-        <v>22.736353696435014</v>
+        <v>22.736353696435007</v>
       </c>
       <c r="Z5">
-        <v>10.684342578811469</v>
+        <v>10.684342578811473</v>
       </c>
       <c r="AA5">
-        <v>0.96548436518024061</v>
+        <v>0.9654843651802405</v>
       </c>
       <c r="AB5">
-        <v>1.8858467704533009</v>
+        <v>1.8858467704533015</v>
       </c>
       <c r="AC5">
-        <v>0.34834200909608232</v>
+        <v>0.34789900000829616</v>
       </c>
       <c r="AD5">
-        <v>1.4380737810100561</v>
+        <v>1.4397837589304969</v>
       </c>
       <c r="AE5">
-        <v>43.819142698173238</v>
+        <v>19.425393343901067</v>
       </c>
       <c r="AF5">
-        <v>8.3345323958669066</v>
+        <v>10.920178333952272</v>
       </c>
       <c r="AG5">
-        <v>13385.196057583715</v>
+        <v>9690.8814916258889</v>
       </c>
       <c r="AH5">
-        <v>653.11072391031792</v>
+        <v>783.73344839889421</v>
       </c>
       <c r="AI5">
-        <v>653.11072391031792</v>
+        <v>783.73344839889421</v>
       </c>
       <c r="AJ5">
         <v>17.620064159324073</v>
@@ -4902,136 +4902,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-5.1220648144637124</v>
+        <v>-5.12205758986098</v>
       </c>
       <c r="AO5">
-        <v>-2.4508345794288746</v>
+        <v>-2.4508890424366023</v>
       </c>
       <c r="AP5">
-        <v>-0.93436113114320152</v>
+        <v>-0.93440073475240348</v>
       </c>
       <c r="AQ5">
-        <v>-1.8249142185715128</v>
+        <v>-1.8248410732261025</v>
       </c>
       <c r="AR5">
-        <v>486.14345973983194</v>
+        <v>351.52258849894173</v>
       </c>
       <c r="AS5">
-        <v>50.455881113368548</v>
+        <v>60.617184165244929</v>
       </c>
       <c r="AT5">
-        <v>-4.1487691507630036</v>
+        <v>-2.4682550643779897</v>
       </c>
       <c r="AU5">
-        <v>-1.17778943305299</v>
+        <v>-0.44277798235074817</v>
       </c>
       <c r="AV5">
-        <v>-1.6884668909502651</v>
+        <v>-1.0045309351223097</v>
       </c>
       <c r="AW5">
-        <v>0.89249876294608177</v>
+        <v>0.33552585073160973</v>
       </c>
       <c r="AX5">
-        <v>0.85752099868599174</v>
+        <v>0.51017072073723557</v>
       </c>
       <c r="AY5">
-        <v>0.51717836831245889</v>
+        <v>0.19442795801220261</v>
       </c>
       <c r="AZ5">
-        <v>-2.5269904750527332</v>
+        <v>-1.5033993965503598</v>
       </c>
       <c r="BA5">
-        <v>0.77186209970393915</v>
+        <v>0.29017372169321021</v>
       </c>
       <c r="BB5">
-        <v>-0.66663724679240755</v>
+        <v>-0.55621106453360381</v>
       </c>
       <c r="BC5">
-        <v>-0.30648299367062443</v>
+        <v>-0.25449326500119834</v>
       </c>
       <c r="BD5">
-        <v>-0.18356605145049343</v>
+        <v>-0.10920825205466581</v>
       </c>
       <c r="BE5">
-        <v>-0.14724587302277351</v>
+        <v>-0.055355368796494137</v>
       </c>
       <c r="BF5">
-        <v>-0.37759646411520581</v>
+        <v>-0.31067207521713663</v>
       </c>
       <c r="BG5">
-        <v>-2.918309417527146</v>
+        <v>-0.91319597831521049</v>
       </c>
       <c r="BH5">
-        <v>66.52270955358955</v>
+        <v>66.067192281323258</v>
       </c>
       <c r="BI5">
-        <v>36.100100100879246</v>
+        <v>35.981348935645713</v>
       </c>
       <c r="BJ5">
-        <v>-1.9761772947772316</v>
+        <v>-1.1671814349248002</v>
       </c>
       <c r="BK5">
-        <v>0.87265378450258324</v>
+        <v>0.32781612219702616</v>
       </c>
       <c r="BL5">
-        <v>-1.7932502401509949</v>
+        <v>-1.0761837240046055</v>
       </c>
       <c r="BM5">
-        <v>0.31893563300928007</v>
+        <v>0.12058030372240677</v>
       </c>
       <c r="BN5">
-        <v>0.17020624360181472</v>
+        <v>0.10589530980997555</v>
       </c>
       <c r="BO5">
-        <v>0.26722370097022025</v>
+        <v>0.29364745642978862</v>
       </c>
       <c r="BP5">
-        <v>-1.3501138782258675</v>
+        <v>-0.72341554165659072</v>
       </c>
       <c r="BQ5">
-        <v>1.9393867294953353</v>
+        <v>1.5025064152806364</v>
       </c>
       <c r="BR5">
-        <v>-20.984397591183253</v>
+        <v>34.663802677939785</v>
       </c>
       <c r="BS5">
-        <v>-1.5558654066178419</v>
+        <v>-1.4872539078788321</v>
       </c>
       <c r="BT5">
-        <v>-0.0049969078380937993</v>
+        <v>-0.00063402022975030548</v>
       </c>
       <c r="BU5">
-        <v>1.2028954604834348</v>
+        <v>1.3275448414918467</v>
       </c>
       <c r="BV5">
-        <v>13.669993793620479</v>
+        <v>13.668811448342837</v>
       </c>
       <c r="BW5">
-        <v>-2.40455025094344</v>
+        <v>-2.4112622869746776</v>
       </c>
       <c r="BX5">
-        <v>-87.64429694215012</v>
+        <v>-90.358950465224865</v>
       </c>
       <c r="BY5">
-        <v>125.94967103739727</v>
+        <v>39.852065954930062</v>
       </c>
       <c r="BZ5">
-        <v>67.355849517456662</v>
+        <v>93.211618004038712</v>
       </c>
       <c r="CA5">
-        <v>-258.4400708700216</v>
+        <v>-74.487406224158519</v>
       </c>
       <c r="CB5">
-        <v>139.69919802619128</v>
+        <v>160.34555213647909</v>
       </c>
       <c r="CC5">
-        <v>125.98347575886695</v>
+        <v>39.862527363062505</v>
       </c>
       <c r="CD5">
-        <v>1.4316474455530037</v>
+        <v>1.2473061917537245</v>
       </c>
       <c r="CE5">
-        <v>1.5875097809081016</v>
+        <v>5.0172433418088884</v>
       </c>
     </row>
     <row r="6" spans="1:83">
@@ -5039,28 +5039,28 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>223.10189816061211</v>
+        <v>227.86618491185288</v>
       </c>
       <c r="C6">
-        <v>58.237071832669386</v>
+        <v>44.351880627331859</v>
       </c>
       <c r="D6">
-        <v>4.3644370545903168</v>
+        <v>2.9335429185863111</v>
       </c>
       <c r="E6">
-        <v>74.942590986210746</v>
+        <v>66.142469656146091</v>
       </c>
       <c r="F6">
-        <v>77.2212578862158</v>
+        <v>55.90819070962025</v>
       </c>
       <c r="G6">
-        <v>19.207461175032439</v>
+        <v>23.048953410038919</v>
       </c>
       <c r="H6">
-        <v>4.83126207778886</v>
+        <v>3.2427492303833705</v>
       </c>
       <c r="I6">
-        <v>62.563887328896428</v>
+        <v>58.001326625391634</v>
       </c>
       <c r="J6">
         <v>808.72882967128078</v>
@@ -5108,37 +5108,37 @@
         <v>27.181807144137792</v>
       </c>
       <c r="Y6">
-        <v>20.753584250711576</v>
+        <v>20.753584250711569</v>
       </c>
       <c r="Z6">
-        <v>10.350460171809656</v>
+        <v>10.350460171809658</v>
       </c>
       <c r="AA6">
-        <v>0.85290174942292629</v>
+        <v>0.85290174942292607</v>
       </c>
       <c r="AB6">
         <v>1.8450740910254295</v>
       </c>
       <c r="AC6">
-        <v>0.33713076331141451</v>
+        <v>0.33670202709441616</v>
       </c>
       <c r="AD6">
-        <v>1.4521500453923895</v>
+        <v>1.4538770650105544</v>
       </c>
       <c r="AE6">
-        <v>30.063282745123537</v>
+        <v>13.227278710399924</v>
       </c>
       <c r="AF6">
-        <v>7.4520512130334522</v>
+        <v>9.7516214359854843</v>
       </c>
       <c r="AG6">
-        <v>9292.0792872686416</v>
+        <v>6727.4651087308266</v>
       </c>
       <c r="AH6">
-        <v>575.227302332162</v>
+        <v>690.27328341103248</v>
       </c>
       <c r="AI6">
-        <v>575.227302332162</v>
+        <v>690.27328341103248</v>
       </c>
       <c r="AJ6">
         <v>16.083471031276794</v>
@@ -5153,136 +5153,136 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>-4.6750508560706425</v>
+        <v>-4.6750446795283764</v>
       </c>
       <c r="AO6">
-        <v>-2.375141211423228</v>
+        <v>-2.3751950278922935</v>
       </c>
       <c r="AP6">
-        <v>-0.8254080019368335</v>
+        <v>-0.825442984658271</v>
       </c>
       <c r="AQ6">
-        <v>-1.7854564789023928</v>
+        <v>-1.7853848861607584</v>
       </c>
       <c r="AR6">
-        <v>369.72646678132236</v>
+        <v>267.3433023954193</v>
       </c>
       <c r="AS6">
-        <v>45.871812957749974</v>
+        <v>55.109918183188924</v>
       </c>
       <c r="AT6">
-        <v>-4.6950135469691547</v>
+        <v>-2.6443179747297538</v>
       </c>
       <c r="AU6">
-        <v>-1.3715489926722086</v>
+        <v>-0.50424595318831211</v>
       </c>
       <c r="AV6">
-        <v>-1.8232802454885866</v>
+        <v>-1.0269049658498934</v>
       </c>
       <c r="AW6">
-        <v>0.99744849457401052</v>
+        <v>0.36670900535809209</v>
       </c>
       <c r="AX6">
-        <v>0.72640867584966085</v>
+        <v>0.40912672547854456</v>
       </c>
       <c r="AY6">
-        <v>0.45070568321493887</v>
+        <v>0.16570061882902165</v>
       </c>
       <c r="AZ6">
-        <v>-2.2045086631372763</v>
+        <v>-1.2416198217669721</v>
       </c>
       <c r="BA6">
-        <v>0.69026252341673711</v>
+        <v>0.25377298655027103</v>
       </c>
       <c r="BB6">
-        <v>-0.80915851653702964</v>
+        <v>-0.63924145156214329</v>
       </c>
       <c r="BC6">
-        <v>-0.34998931964125091</v>
+        <v>-0.27530687086336963</v>
       </c>
       <c r="BD6">
-        <v>-0.1573810150697729</v>
+        <v>-0.088638217291158047</v>
       </c>
       <c r="BE6">
-        <v>-0.1436682518973422</v>
+        <v>-0.052818985609339252</v>
       </c>
       <c r="BF6">
-        <v>-0.42566878276219572</v>
+        <v>-0.3315520400060592</v>
       </c>
       <c r="BG6">
-        <v>-3.1319505952308271</v>
+        <v>-0.95842975911823225</v>
       </c>
       <c r="BH6">
-        <v>67.552396921286629</v>
+        <v>67.040517659843388</v>
       </c>
       <c r="BI6">
-        <v>36.977651246273943</v>
+        <v>36.887096787616656</v>
       </c>
       <c r="BJ6">
-        <v>-1.7601003628280334</v>
+        <v>-0.98366767467491045</v>
       </c>
       <c r="BK6">
-        <v>0.7752506336921865</v>
+        <v>0.28485537238451031</v>
       </c>
       <c r="BL6">
-        <v>-1.5131340730317273</v>
+        <v>-0.86104724905495067</v>
       </c>
       <c r="BM6">
-        <v>0.28032912634214385</v>
+        <v>0.10351251425140223</v>
       </c>
       <c r="BN6">
-        <v>0.1593620784984231</v>
+        <v>0.0986097454977269</v>
       </c>
       <c r="BO6">
-        <v>0.26839961535544676</v>
+        <v>0.29413250983602468</v>
       </c>
       <c r="BP6">
-        <v>-1.3509565239001145</v>
+        <v>-0.72398653610750052</v>
       </c>
       <c r="BQ6">
-        <v>1.9277656785170165</v>
+        <v>1.4909075520596828</v>
       </c>
       <c r="BR6">
-        <v>-20.983646700653392</v>
+        <v>34.664577387630679</v>
       </c>
       <c r="BS6">
-        <v>-1.5465846307144475</v>
+        <v>-1.4370140090341916</v>
       </c>
       <c r="BT6">
-        <v>-0.0045137521564393036</v>
+        <v>-0.00013069558149072952</v>
       </c>
       <c r="BU6">
-        <v>1.2083212868742084</v>
+        <v>1.332969419953727</v>
       </c>
       <c r="BV6">
-        <v>13.668757316478574</v>
+        <v>13.667592076052104</v>
       </c>
       <c r="BW6">
-        <v>-2.4280271358392955</v>
+        <v>-2.4345778261941518</v>
       </c>
       <c r="BX6">
-        <v>-113.08394912584917</v>
+        <v>-110.96638056859632</v>
       </c>
       <c r="BY6">
-        <v>125.70609204944621</v>
+        <v>38.937493022277607</v>
       </c>
       <c r="BZ6">
-        <v>87.1301327491259</v>
+        <v>111.30255242463619</v>
       </c>
       <c r="CA6">
-        <v>-259.253422831471</v>
+        <v>-73.166217210964462</v>
       </c>
       <c r="CB6">
-        <v>149.69462529106372</v>
+        <v>169.3042036930616</v>
       </c>
       <c r="CC6">
-        <v>125.74510206316114</v>
+        <v>38.949286905707027</v>
       </c>
       <c r="CD6">
-        <v>1.3360533126097436</v>
+        <v>1.18130557681006</v>
       </c>
       <c r="CE6">
-        <v>1.5905192068597709</v>
+        <v>5.1348821991063218</v>
       </c>
     </row>
     <row r="7" spans="1:83">
@@ -5290,28 +5290,28 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>219.96846721960262</v>
+        <v>224.2498532157588</v>
       </c>
       <c r="C7">
-        <v>50.473070239288788</v>
+        <v>38.286097578595395</v>
       </c>
       <c r="D7">
-        <v>3.3365305011186877</v>
+        <v>2.2415763405457692</v>
       </c>
       <c r="E7">
-        <v>66.1051623232045</v>
+        <v>58.548049613679275</v>
       </c>
       <c r="F7">
-        <v>66.8297146615733</v>
+        <v>48.384713414979068</v>
       </c>
       <c r="G7">
-        <v>19.049481833608858</v>
+        <v>22.859378200330625</v>
       </c>
       <c r="H7">
-        <v>3.6895537747752081</v>
+        <v>2.4743977094581768</v>
       </c>
       <c r="I7">
-        <v>55.208282624864765</v>
+        <v>51.140071622128204</v>
       </c>
       <c r="J7">
         <v>1071.5064729451767</v>
@@ -5359,37 +5359,37 @@
         <v>27.336868536882193</v>
       </c>
       <c r="Y7">
-        <v>19.306763646234344</v>
+        <v>19.306763646234348</v>
       </c>
       <c r="Z7">
-        <v>10.307806563992024</v>
+        <v>10.307806563992026</v>
       </c>
       <c r="AA7">
-        <v>0.78273159475183307</v>
+        <v>0.78273159475183329</v>
       </c>
       <c r="AB7">
-        <v>1.898339550922574</v>
+        <v>1.8983395509225747</v>
       </c>
       <c r="AC7">
-        <v>0.3325831636576404</v>
+        <v>0.33216021650596544</v>
       </c>
       <c r="AD7">
-        <v>1.4994773543842783</v>
+        <v>1.5012617358456368</v>
       </c>
       <c r="AE7">
-        <v>22.410784875231375</v>
+        <v>9.8302780904895037</v>
       </c>
       <c r="AF7">
-        <v>7.7057873307608631</v>
+        <v>10.042815089711226</v>
       </c>
       <c r="AG7">
-        <v>6959.4989832591637</v>
+        <v>5038.6770486699861</v>
       </c>
       <c r="AH7">
-        <v>565.82736096028793</v>
+        <v>678.99337915144463</v>
       </c>
       <c r="AI7">
-        <v>565.82736096028793</v>
+        <v>678.99337915144463</v>
       </c>
       <c r="AJ7">
         <v>14.962223877124806</v>
@@ -5404,136 +5404,136 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>-4.349010050465</v>
+        <v>-4.3490044586181469</v>
       </c>
       <c r="AO7">
-        <v>-2.3684141412403341</v>
+        <v>-2.3684713501535635</v>
       </c>
       <c r="AP7">
-        <v>-0.75749992458845972</v>
+        <v>-0.75753202817875165</v>
       </c>
       <c r="AQ7">
-        <v>-1.8369923462114106</v>
+        <v>-1.8369185850135714</v>
       </c>
       <c r="AR7">
-        <v>297.66606572793438</v>
+        <v>215.23757305116112</v>
       </c>
       <c r="AS7">
-        <v>45.30643038521908</v>
+        <v>54.430629616269805</v>
       </c>
       <c r="AT7">
-        <v>-5.2800586984172933</v>
+        <v>-2.8955160604223864</v>
       </c>
       <c r="AU7">
-        <v>-1.6360557441681851</v>
+        <v>-0.48882153331854311</v>
       </c>
       <c r="AV7">
-        <v>-1.9813701494084068</v>
+        <v>-1.0865578238691265</v>
       </c>
       <c r="AW7">
-        <v>1.1187880513282582</v>
+        <v>0.33427203972612596</v>
       </c>
       <c r="AX7">
-        <v>0.6386700546525973</v>
+        <v>0.35023841706755349</v>
       </c>
       <c r="AY7">
-        <v>0.40606459943754997</v>
+        <v>0.12132417910024361</v>
       </c>
       <c r="AZ7">
-        <v>-1.9797356175412011</v>
+        <v>-1.0856614676838843</v>
       </c>
       <c r="BA7">
-        <v>0.65365502763944794</v>
+        <v>0.19529936801422532</v>
       </c>
       <c r="BB7">
-        <v>-0.95208027243679894</v>
+        <v>-0.732479405490545</v>
       </c>
       <c r="BC7">
-        <v>-0.39337173560604471</v>
+        <v>-0.30145454218793333</v>
       </c>
       <c r="BD7">
-        <v>-0.14014585162081453</v>
+        <v>-0.076852641041575964</v>
       </c>
       <c r="BE7">
-        <v>-0.15066910558150856</v>
+        <v>-0.045016782728534849</v>
       </c>
       <c r="BF7">
-        <v>-0.47081568158631587</v>
+        <v>-0.35705959676152077</v>
       </c>
       <c r="BG7">
-        <v>-3.3255567543159024</v>
+        <v>-0.82704872322621326</v>
       </c>
       <c r="BH7">
-        <v>68.438446230148742</v>
+        <v>67.909197176703884</v>
       </c>
       <c r="BI7">
-        <v>37.19885184158246</v>
+        <v>36.5669278818605</v>
       </c>
       <c r="BJ7">
-        <v>-1.6064886244410266</v>
+        <v>-0.87424588677630433</v>
       </c>
       <c r="BK7">
-        <v>0.71863633933396642</v>
+        <v>0.21379472891605683</v>
       </c>
       <c r="BL7">
-        <v>-1.321532010059828</v>
+        <v>-0.73281778134692188</v>
       </c>
       <c r="BM7">
-        <v>0.27516388909771855</v>
+        <v>0.084576672131348216</v>
       </c>
       <c r="BN7">
-        <v>0.15177517419808637</v>
+        <v>0.093698777946565948</v>
       </c>
       <c r="BO7">
-        <v>0.29876796940406</v>
+        <v>0.33524414562265459</v>
       </c>
       <c r="BP7">
-        <v>-1.3514028428953564</v>
+        <v>-0.72426677110367765</v>
       </c>
       <c r="BQ7">
-        <v>1.9229758325978819</v>
+        <v>1.4861771882513915</v>
       </c>
       <c r="BR7">
-        <v>-20.983259152206614</v>
+        <v>34.664931748870806</v>
       </c>
       <c r="BS7">
-        <v>-1.5439867488229428</v>
+        <v>-1.4154527741111582</v>
       </c>
       <c r="BT7">
-        <v>-0.0023041674390328563</v>
+        <v>0.0025113328450566681</v>
       </c>
       <c r="BU7">
-        <v>1.2265149177199475</v>
+        <v>1.3511562674065769</v>
       </c>
       <c r="BV7">
-        <v>13.663356024433874</v>
+        <v>13.66167464633582</v>
       </c>
       <c r="BW7">
-        <v>-2.5133280013161272</v>
+        <v>-2.5224514564800158</v>
       </c>
       <c r="BX7">
-        <v>-138.10269448619053</v>
+        <v>-132.27700853887498</v>
       </c>
       <c r="BY7">
-        <v>114.38504429224535</v>
+        <v>28.76354326720886</v>
       </c>
       <c r="BZ7">
-        <v>106.69423810609716</v>
+        <v>130.92348436857915</v>
       </c>
       <c r="CA7">
-        <v>-241.03575170897668</v>
+        <v>-55.400494247293551</v>
       </c>
       <c r="CB7">
-        <v>161.90320530009765</v>
+        <v>182.063906119629</v>
       </c>
       <c r="CC7">
-        <v>114.43337662354068</v>
+        <v>28.775431028486544</v>
       </c>
       <c r="CD7">
-        <v>1.2353059942778004</v>
+        <v>1.0985153744234495</v>
       </c>
       <c r="CE7">
-        <v>1.7477418380998553</v>
+        <v>6.9503737338289691</v>
       </c>
     </row>
     <row r="8" spans="1:83">
@@ -5541,28 +5541,28 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>217.49227741305941</v>
+        <v>221.38721110996937</v>
       </c>
       <c r="C8">
-        <v>44.90175169639992</v>
+        <v>33.903312137508514</v>
       </c>
       <c r="D8">
-        <v>2.6510746433249786</v>
+        <v>1.7800888326833</v>
       </c>
       <c r="E8">
-        <v>59.041675283628926</v>
+        <v>52.50486517256585</v>
       </c>
       <c r="F8">
-        <v>59.383182541497831</v>
+        <v>42.993424160044427</v>
       </c>
       <c r="G8">
-        <v>19.750695205474937</v>
+        <v>23.700834246569915</v>
       </c>
       <c r="H8">
-        <v>2.92968848923152</v>
+        <v>1.9634362264068106</v>
       </c>
       <c r="I8">
-        <v>49.335322962594852</v>
+        <v>45.668291483317425</v>
       </c>
       <c r="J8">
         <v>1382.9628636146674</v>
@@ -5613,34 +5613,34 @@
         <v>18.199372375093496</v>
       </c>
       <c r="Z8">
-        <v>10.495807818544396</v>
+        <v>10.4958078185444</v>
       </c>
       <c r="AA8">
         <v>0.69688353407589643</v>
       </c>
       <c r="AB8">
-        <v>1.902975588701</v>
+        <v>1.9029755887010003</v>
       </c>
       <c r="AC8">
-        <v>0.31413609182285829</v>
+        <v>0.31373662529371849</v>
       </c>
       <c r="AD8">
-        <v>1.4765888396669071</v>
+        <v>1.4783454672535046</v>
       </c>
       <c r="AE8">
-        <v>17.367586860893496</v>
+        <v>7.5247455226534381</v>
       </c>
       <c r="AF8">
-        <v>8.086690843134809</v>
+        <v>10.559587607147265</v>
       </c>
       <c r="AG8">
-        <v>5494.9548447719653</v>
+        <v>3978.3471560198009</v>
       </c>
       <c r="AH8">
-        <v>608.2380525573767</v>
+        <v>729.88623222648107</v>
       </c>
       <c r="AI8">
-        <v>608.2380525573767</v>
+        <v>729.88623222648107</v>
       </c>
       <c r="AJ8">
         <v>14.104025350329518</v>
@@ -5655,136 +5655,136 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-4.099106262202258</v>
+        <v>-4.0991015600451757</v>
       </c>
       <c r="AO8">
-        <v>-2.4100908521792683</v>
+        <v>-2.4101473089448</v>
       </c>
       <c r="AP8">
-        <v>-0.674419575993695</v>
+        <v>-0.67444815497151633</v>
       </c>
       <c r="AQ8">
-        <v>-1.8414826877524659</v>
+        <v>-1.8414087960679439</v>
       </c>
       <c r="AR8">
-        <v>249.32675076867676</v>
+        <v>180.28417287218974</v>
       </c>
       <c r="AS8">
-        <v>47.831247190275555</v>
+        <v>57.463938319369959</v>
       </c>
       <c r="AT8">
-        <v>-5.7137816162381023</v>
+        <v>-3.2562411361356927</v>
       </c>
       <c r="AU8">
-        <v>-1.8501212191238619</v>
+        <v>-0.33136499446994544</v>
       </c>
       <c r="AV8">
-        <v>-2.0645686679590138</v>
+        <v>-1.1765821441056747</v>
       </c>
       <c r="AW8">
-        <v>1.1645774931326829</v>
+        <v>0.20858104354615217</v>
       </c>
       <c r="AX8">
-        <v>0.55029841193007278</v>
+        <v>0.313610922927891</v>
       </c>
       <c r="AY8">
-        <v>0.3492552400227939</v>
+        <v>0.062553177317515307</v>
       </c>
       <c r="AZ8">
-        <v>-1.7518038058737824</v>
+        <v>-0.99833980334742445</v>
       </c>
       <c r="BA8">
-        <v>0.60509777615194371</v>
+        <v>0.10837572110184068</v>
       </c>
       <c r="BB8">
-        <v>-1.0641793391353369</v>
+        <v>-0.85090686882579869</v>
       </c>
       <c r="BC8">
-        <v>-0.41963316408094409</v>
+        <v>-0.33432340512302849</v>
       </c>
       <c r="BD8">
-        <v>-0.12583841987287089</v>
+        <v>-0.0717129460925606</v>
       </c>
       <c r="BE8">
-        <v>-0.14993261100962871</v>
+        <v>-0.026853463227403632</v>
       </c>
       <c r="BF8">
-        <v>-0.50471286969773532</v>
+        <v>-0.39777726990710721</v>
       </c>
       <c r="BG8">
-        <v>-3.1346163819059085</v>
+        <v>-0.46730982965627782</v>
       </c>
       <c r="BH8">
-        <v>69.509448362170758</v>
+        <v>69.045147369312048</v>
       </c>
       <c r="BI8">
-        <v>38.238017152190871</v>
+        <v>34.3720048053326</v>
       </c>
       <c r="BJ8">
-        <v>-1.4483334890538431</v>
+        <v>-0.82015475868312537</v>
       </c>
       <c r="BK8">
-        <v>0.64883424957015867</v>
+        <v>0.11281573907872408</v>
       </c>
       <c r="BL8">
-        <v>-1.1287050194500559</v>
+        <v>-0.64990795174153848</v>
       </c>
       <c r="BM8">
-        <v>0.25910742554418659</v>
+        <v>0.054136918391996726</v>
       </c>
       <c r="BN8">
-        <v>0.14112663598140574</v>
+        <v>0.085875146001744548</v>
       </c>
       <c r="BO8">
-        <v>0.30420188264747267</v>
+        <v>0.39776931665591003</v>
       </c>
       <c r="BP8">
-        <v>-1.3525243813981038</v>
+        <v>-0.72507799688498964</v>
       </c>
       <c r="BQ8">
-        <v>1.9040161849750603</v>
+        <v>1.4671370287762635</v>
       </c>
       <c r="BR8">
-        <v>-20.349923930744559</v>
+        <v>34.6660247102103</v>
       </c>
       <c r="BS8">
-        <v>-1.5281054459620844</v>
+        <v>-1.3353143494810154</v>
       </c>
       <c r="BT8">
-        <v>-0.0029510066182683245</v>
+        <v>0.0031575821234480113</v>
       </c>
       <c r="BU8">
-        <v>1.2177271680129613</v>
+        <v>1.3423676842734591</v>
       </c>
       <c r="BV8">
-        <v>13.665125417435259</v>
+        <v>13.660985706943746</v>
       </c>
       <c r="BW8">
-        <v>-2.4768610578352765</v>
+        <v>-2.4995925445429372</v>
       </c>
       <c r="BX8">
-        <v>-159.05925598330569</v>
+        <v>-160.0280987417753</v>
       </c>
       <c r="BY8">
-        <v>97.705387098344247</v>
+        <v>14.341254124727243</v>
       </c>
       <c r="BZ8">
-        <v>123.25312215522682</v>
+        <v>151.20480837487241</v>
       </c>
       <c r="CA8">
-        <v>-204.55181999904698</v>
+        <v>-27.718220309575369</v>
       </c>
       <c r="CB8">
-        <v>172.58918310041389</v>
+        <v>196.87350170738887</v>
       </c>
       <c r="CC8">
-        <v>97.755657063409913</v>
+        <v>14.348865751232728</v>
       </c>
       <c r="CD8">
-        <v>0.86911588145549479</v>
+        <v>0.76191056032997018</v>
       </c>
       <c r="CE8">
-        <v>1.5344380520372483</v>
+        <v>10.453787957916696</v>
       </c>
     </row>
     <row r="9" spans="1:83">
@@ -5792,28 +5792,28 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>215.63047275898356</v>
+        <v>219.2319142121199</v>
       </c>
       <c r="C9">
-        <v>41.41613193467871</v>
+        <v>31.055766052526305</v>
       </c>
       <c r="D9">
-        <v>2.2265348276393047</v>
+        <v>1.4937968441774596</v>
       </c>
       <c r="E9">
-        <v>53.760086314940828</v>
+        <v>48.100466807063135</v>
       </c>
       <c r="F9">
-        <v>54.725271217524529</v>
+        <v>39.621096361487751</v>
       </c>
       <c r="G9">
-        <v>21.92696761324386</v>
+        <v>26.312361135892626</v>
       </c>
       <c r="H9">
-        <v>2.4607704963977897</v>
+        <v>1.6482853250799288</v>
       </c>
       <c r="I9">
-        <v>44.965889462961364</v>
+        <v>41.60120431907292</v>
       </c>
       <c r="J9">
         <v>1734.9265462127746</v>
@@ -5861,37 +5861,37 @@
         <v>40.105980772653396</v>
       </c>
       <c r="Y9">
-        <v>17.471035165150283</v>
+        <v>17.471035165150287</v>
       </c>
       <c r="Z9">
-        <v>11.058951772214726</v>
+        <v>11.058951772214728</v>
       </c>
       <c r="AA9">
-        <v>0.55748530989039835</v>
+        <v>0.55748530989039846</v>
       </c>
       <c r="AB9">
         <v>1.7011608307607355</v>
       </c>
       <c r="AC9">
-        <v>0.26180173902028248</v>
+        <v>0.26146864714207851</v>
       </c>
       <c r="AD9">
-        <v>1.2555415310972371</v>
+        <v>1.2570312751909709</v>
       </c>
       <c r="AE9">
-        <v>14.05142648073285</v>
+        <v>5.8820265140453616</v>
       </c>
       <c r="AF9">
-        <v>7.7996260691798645</v>
+        <v>10.414234759882783</v>
       </c>
       <c r="AG9">
-        <v>4666.6911690333991</v>
+        <v>3378.6843168988785</v>
       </c>
       <c r="AH9">
-        <v>749.52775204845591</v>
+        <v>899.43380967450889</v>
       </c>
       <c r="AI9">
-        <v>749.52775204845591</v>
+        <v>899.43380967450889</v>
       </c>
       <c r="AJ9">
         <v>13.539583551958181</v>
@@ -5906,136 +5906,136 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>-3.9339578818737007</v>
+        <v>-3.9339547453065395</v>
       </c>
       <c r="AO9">
-        <v>-2.525238479888845</v>
+        <v>-2.5252812824084923</v>
       </c>
       <c r="AP9">
-        <v>-0.539515561645954</v>
+        <v>-0.53953843189762718</v>
       </c>
       <c r="AQ9">
-        <v>-1.6462241039030039</v>
+        <v>-1.6461584447737405</v>
       </c>
       <c r="AR9">
-        <v>220.57319532370767</v>
+        <v>159.49277233640859</v>
       </c>
       <c r="AS9">
-        <v>55.95239431483045</v>
+        <v>67.22083212586945</v>
       </c>
       <c r="AT9">
-        <v>-5.1473375458857689</v>
+        <v>-4.4013465972066728</v>
       </c>
       <c r="AU9">
-        <v>-1.9663567015060202</v>
+        <v>-0.41348622227930332</v>
       </c>
       <c r="AV9">
-        <v>-1.7932949683551449</v>
+        <v>-1.5333971468543994</v>
       </c>
       <c r="AW9">
-        <v>1.1920824682087055</v>
+        <v>0.25067154705323247</v>
       </c>
       <c r="AX9">
-        <v>0.40587120534886645</v>
+        <v>0.34704929153019021</v>
       </c>
       <c r="AY9">
-        <v>0.30731620437758278</v>
+        <v>0.06462256634108049</v>
       </c>
       <c r="AZ9">
-        <v>-1.327634855418004</v>
+        <v>-1.1352240068066988</v>
       </c>
       <c r="BA9">
-        <v>0.54895645566278117</v>
+        <v>0.11543476871413624</v>
       </c>
       <c r="BB9">
-        <v>-0.968258145185789</v>
+        <v>-1.161519067071489</v>
       </c>
       <c r="BC9">
-        <v>-0.36588837002789709</v>
+        <v>-0.43743127447951363</v>
       </c>
       <c r="BD9">
-        <v>-0.10451632954985642</v>
+        <v>-0.0893675982664041</v>
       </c>
       <c r="BE9">
-        <v>-0.13869720245010547</v>
+        <v>-0.029165009203172085</v>
       </c>
       <c r="BF9">
-        <v>-0.47383966758277618</v>
+        <v>-0.56032381252929975</v>
       </c>
       <c r="BG9">
-        <v>-2.4788430262642596</v>
+        <v>-0.43386861305973246</v>
       </c>
       <c r="BH9">
-        <v>71.057206079384159</v>
+        <v>70.971200746125845</v>
       </c>
       <c r="BI9">
-        <v>42.6293821019453</v>
+        <v>39.763937154911957</v>
       </c>
       <c r="BJ9">
-        <v>-1.1239788350807924</v>
+        <v>-0.96003635680290378</v>
       </c>
       <c r="BK9">
-        <v>0.59789046517411537</v>
+        <v>0.12350955898703425</v>
       </c>
       <c r="BL9">
-        <v>-0.81487258080177849</v>
+        <v>-0.698216979167988</v>
       </c>
       <c r="BM9">
-        <v>0.19576371303376733</v>
+        <v>0.047398847532632946</v>
       </c>
       <c r="BN9">
-        <v>0.12507337472127139</v>
+        <v>0.072544499337529919</v>
       </c>
       <c r="BO9">
-        <v>0.19521697659828513</v>
+        <v>0.25459222707044449</v>
       </c>
       <c r="BP9">
-        <v>-1.3551463069223009</v>
+        <v>-0.727066882972355</v>
       </c>
       <c r="BQ9">
-        <v>1.8505256694747381</v>
+        <v>1.4131952658608538</v>
       </c>
       <c r="BR9">
-        <v>-18.450663368953972</v>
+        <v>-21.60889400966844</v>
       </c>
       <c r="BS9">
-        <v>-1.489306695155618</v>
+        <v>-1.15822334150383</v>
       </c>
       <c r="BT9">
-        <v>-0.012137111996997843</v>
+        <v>-0.0076449967207965893</v>
       </c>
       <c r="BU9">
-        <v>1.131931859176387</v>
+        <v>1.2566048553852336</v>
       </c>
       <c r="BV9">
-        <v>13.68703652052668</v>
+        <v>13.684811441950872</v>
       </c>
       <c r="BW9">
-        <v>-2.0873271742586597</v>
+        <v>-2.1018656581428194</v>
       </c>
       <c r="BX9">
-        <v>-148.26086557092756</v>
+        <v>-230.80525243619977</v>
       </c>
       <c r="BY9">
-        <v>86.772876631867788</v>
+        <v>14.903342470827152</v>
       </c>
       <c r="BZ9">
-        <v>115.90844109365119</v>
+        <v>184.57414438867917</v>
       </c>
       <c r="CA9">
-        <v>-163.58159293193614</v>
+        <v>-25.648637256418837</v>
       </c>
       <c r="CB9">
-        <v>160.87502837938777</v>
+        <v>226.17604277608214</v>
       </c>
       <c r="CC9">
-        <v>86.80827599784601</v>
+        <v>14.909656561308136</v>
       </c>
       <c r="CD9">
-        <v>0.93240076791942228</v>
+        <v>0.66320021412923191</v>
       </c>
       <c r="CE9">
-        <v>1.7279458470494447</v>
+        <v>10.06059390994043</v>
       </c>
     </row>
     <row r="10" spans="1:83">
@@ -6043,28 +6043,28 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>214.37176091245323</v>
+        <v>217.7733157987233</v>
       </c>
       <c r="C10">
-        <v>39.98765244367096</v>
+        <v>29.827055102493709</v>
       </c>
       <c r="D10">
-        <v>2.0082250152717327</v>
+        <v>1.3466656167011675</v>
       </c>
       <c r="E10">
-        <v>50.221128086992373</v>
+        <v>45.149130950865434</v>
       </c>
       <c r="F10">
-        <v>52.805699323592314</v>
+        <v>38.231326310280842</v>
       </c>
       <c r="G10">
-        <v>26.110333901864664</v>
+        <v>31.332400682237591</v>
       </c>
       <c r="H10">
-        <v>2.2197995995109965</v>
+        <v>1.486331254973557</v>
       </c>
       <c r="I10">
-        <v>42.037121521828674</v>
+        <v>38.87731340813739</v>
       </c>
       <c r="J10">
         <v>2089.9227444025614</v>
@@ -6115,34 +6115,34 @@
         <v>17.161888490036898</v>
       </c>
       <c r="Z10">
-        <v>12.067877398384612</v>
+        <v>12.06787739838461</v>
       </c>
       <c r="AA10">
         <v>0.46916425536893</v>
       </c>
       <c r="AB10">
-        <v>1.6203243026796825</v>
+        <v>1.6203243026796821</v>
       </c>
       <c r="AC10">
-        <v>0.2243074504748592</v>
+        <v>0.2240221081906571</v>
       </c>
       <c r="AD10">
-        <v>1.09735062532441</v>
+        <v>1.0986505459103202</v>
       </c>
       <c r="AE10">
-        <v>12.686864224798686</v>
+        <v>5.1901306418213471</v>
       </c>
       <c r="AF10">
-        <v>9.1444407641223151</v>
+        <v>12.469010511864669</v>
       </c>
       <c r="AG10">
-        <v>4345.0263011671086</v>
+        <v>3145.7989808905731</v>
       </c>
       <c r="AH10">
-        <v>1062.6909227348253</v>
+        <v>1275.22965670274</v>
       </c>
       <c r="AI10">
-        <v>1062.6909227348253</v>
+        <v>1275.22965670274</v>
       </c>
       <c r="AJ10">
         <v>13.30000317232177</v>
@@ -6157,136 +6157,136 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>-3.8636924513345603</v>
+        <v>-3.863690190084816</v>
       </c>
       <c r="AO10">
-        <v>-2.7461292916418003</v>
+        <v>-2.7461648660110125</v>
       </c>
       <c r="AP10">
-        <v>-0.45404179014699858</v>
+        <v>-0.45406103195706343</v>
       </c>
       <c r="AQ10">
-        <v>-1.5680201791727335</v>
+        <v>-1.5679578748782423</v>
       </c>
       <c r="AR10">
-        <v>209.06919511920546</v>
+        <v>151.17441932831113</v>
       </c>
       <c r="AS10">
-        <v>72.70504539111613</v>
+        <v>87.347547242976816</v>
       </c>
       <c r="AT10">
-        <v>-5.4876942691416533</v>
+        <v>-5.6947770717507726</v>
       </c>
       <c r="AU10">
-        <v>-2.1753450278790885</v>
+        <v>-0.492757713497473</v>
       </c>
       <c r="AV10">
-        <v>-1.8645542469376537</v>
+        <v>-1.9349147845579429</v>
       </c>
       <c r="AW10">
-        <v>1.2629195934644373</v>
+        <v>0.28607570901680618</v>
       </c>
       <c r="AX10">
-        <v>0.37438257255051771</v>
+        <v>0.38851021679770703</v>
       </c>
       <c r="AY10">
-        <v>0.29170424621945817</v>
+        <v>0.06607665245855128</v>
       </c>
       <c r="AZ10">
-        <v>-1.2486774144072024</v>
+        <v>-1.2957973168376629</v>
       </c>
       <c r="BA10">
-        <v>0.54151616189737251</v>
+        <v>0.1226638819767529</v>
       </c>
       <c r="BB10">
-        <v>-1.0156813868953452</v>
+        <v>-1.4785591853558824</v>
       </c>
       <c r="BC10">
-        <v>-0.37264097274668451</v>
+        <v>-0.54070484401565377</v>
       </c>
       <c r="BD10">
-        <v>-0.10656479258729443</v>
+        <v>-0.11058461956632087</v>
       </c>
       <c r="BE10">
-        <v>-0.1438263708782675</v>
+        <v>-0.032579122621533452</v>
       </c>
       <c r="BF10">
-        <v>-0.50971063683740747</v>
+        <v>-0.73150351797389834</v>
       </c>
       <c r="BG10">
-        <v>-1.9782171939313815</v>
+        <v>-0.37298268411484187</v>
       </c>
       <c r="BH10">
-        <v>72.368360078341652</v>
+        <v>72.37290119180534</v>
       </c>
       <c r="BI10">
-        <v>46.131524459693317</v>
+        <v>43.511209316746232</v>
       </c>
       <c r="BJ10">
-        <v>-1.0766199144960935</v>
+        <v>-1.1173075312575687</v>
       </c>
       <c r="BK10">
-        <v>0.59254918966279435</v>
+        <v>0.13237506107537972</v>
       </c>
       <c r="BL10">
-        <v>-0.73501507167582925</v>
+        <v>-0.762662937001009</v>
       </c>
       <c r="BM10">
-        <v>0.16497447890049391</v>
+        <v>0.043467173211797737</v>
       </c>
       <c r="BN10">
-        <v>0.11421358806122454</v>
+        <v>0.064525248609714883</v>
       </c>
       <c r="BO10">
-        <v>0.13726642983280904</v>
+        <v>0.18395853882250032</v>
       </c>
       <c r="BP10">
-        <v>-1.3569272951083209</v>
+        <v>-1.3607054005339885</v>
       </c>
       <c r="BQ10">
-        <v>1.8121896793619454</v>
+        <v>1.3745564050861616</v>
       </c>
       <c r="BR10">
-        <v>-17.18454469805814</v>
+        <v>-20.343021104779208</v>
       </c>
       <c r="BS10">
-        <v>-1.4713869068482941</v>
+        <v>-1.1166524150741448</v>
       </c>
       <c r="BT10">
-        <v>-0.01774937032497869</v>
+        <v>-0.014062087951013122</v>
       </c>
       <c r="BU10">
-        <v>1.0695955941563629</v>
+        <v>1.194282980961257</v>
       </c>
       <c r="BV10">
-        <v>13.699580625951615</v>
+        <v>13.698055983022671</v>
       </c>
       <c r="BW10">
-        <v>-1.8144733848210848</v>
+        <v>-1.8259477750335069</v>
       </c>
       <c r="BX10">
-        <v>-154.01375938848307</v>
+        <v>-296.23808889709119</v>
       </c>
       <c r="BY10">
-        <v>69.311313397367627</v>
+        <v>12.679374919438088</v>
       </c>
       <c r="BZ10">
-        <v>121.95637732514592</v>
+        <v>235.45588030781795</v>
       </c>
       <c r="CA10">
-        <v>-119.70253069377175</v>
+        <v>-19.851762656943766</v>
       </c>
       <c r="CB10">
-        <v>163.99429096467341</v>
+        <v>274.33416898336361</v>
       </c>
       <c r="CC10">
-        <v>69.339537841944676</v>
+        <v>12.684859653552541</v>
       </c>
       <c r="CD10">
-        <v>0.91466598695385082</v>
+        <v>0.5467784073557983</v>
       </c>
       <c r="CE10">
-        <v>2.1632679517119944</v>
+        <v>11.82512097861412</v>
       </c>
     </row>
     <row r="11" spans="1:83">
@@ -6294,28 +6294,28 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>213.29647024618566</v>
+        <v>216.52630919808175</v>
       </c>
       <c r="C11">
-        <v>39.1596734538681</v>
+        <v>29.487145447899987</v>
       </c>
       <c r="D11">
-        <v>3.2883801472552356</v>
+        <v>2.2072795924454462</v>
       </c>
       <c r="E11">
-        <v>83.973635559783176</v>
+        <v>74.855655198819662</v>
       </c>
       <c r="F11">
-        <v>51.678360279737774</v>
+        <v>37.415132842530141</v>
       </c>
       <c r="G11">
-        <v>31.221958795995924</v>
+        <v>37.4663505551951</v>
       </c>
       <c r="H11">
-        <v>3.6258553590946345</v>
+        <v>2.4269421278472274</v>
       </c>
       <c r="I11">
-        <v>70.161966042801708</v>
+        <v>64.86525487057736</v>
       </c>
       <c r="J11">
         <v>2446.5600911094334</v>
@@ -6366,34 +6366,34 @@
         <v>16.977707192530932</v>
       </c>
       <c r="Z11">
-        <v>13.19637807881103</v>
+        <v>13.196378078811032</v>
       </c>
       <c r="AA11">
-        <v>0.4383394607053715</v>
+        <v>0.43833946070537155</v>
       </c>
       <c r="AB11">
-        <v>1.6558782540609873</v>
+        <v>1.6558782540609878</v>
       </c>
       <c r="AC11">
-        <v>0.21184741613854261</v>
+        <v>0.21157804075144279</v>
       </c>
       <c r="AD11">
-        <v>1.02607332450198</v>
+        <v>1.0272879989547392</v>
       </c>
       <c r="AE11">
-        <v>12.037800288867087</v>
+        <v>4.8905266522696085</v>
       </c>
       <c r="AF11">
-        <v>11.955042856772828</v>
+        <v>16.484774919531283</v>
       </c>
       <c r="AG11">
-        <v>4161.4774592251224</v>
+        <v>3012.9096282555111</v>
       </c>
       <c r="AH11">
-        <v>1519.4368747436915</v>
+        <v>1823.3249365599143</v>
       </c>
       <c r="AI11">
-        <v>1519.4368747436915</v>
+        <v>1823.3249365599143</v>
       </c>
       <c r="AJ11">
         <v>13.157267607845068</v>
@@ -6408,136 +6408,136 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>-3.8220341979905563</v>
+        <v>-3.8220322035271841</v>
       </c>
       <c r="AO11">
-        <v>-2.9987153998764282</v>
+        <v>-2.9987493709557338</v>
       </c>
       <c r="AP11">
-        <v>-0.42421066987626527</v>
+        <v>-0.42422863911731096</v>
       </c>
       <c r="AQ11">
-        <v>-1.6024360070972781</v>
+        <v>-1.6023724337651706</v>
       </c>
       <c r="AR11">
-        <v>202.40970700618144</v>
+        <v>146.35912586293617</v>
       </c>
       <c r="AS11">
-        <v>95.0673420544445</v>
+        <v>114.21362300929796</v>
       </c>
       <c r="AT11">
-        <v>-5.533377853774029</v>
+        <v>-6.2109343256647263</v>
       </c>
       <c r="AU11">
-        <v>-2.49929545129312</v>
+        <v>-0.76424736940368121</v>
       </c>
       <c r="AV11">
-        <v>-1.8146026363761159</v>
+        <v>-2.0367988775650283</v>
       </c>
       <c r="AW11">
-        <v>1.4411014466180829</v>
+        <v>0.44066738450305015</v>
       </c>
       <c r="AX11">
-        <v>0.33537467272810062</v>
+        <v>0.37644095918460263</v>
       </c>
       <c r="AY11">
-        <v>0.2941165247159937</v>
+        <v>0.089936457971006328</v>
       </c>
       <c r="AZ11">
-        <v>-1.1566673706970263</v>
+        <v>-1.2983001099660498</v>
       </c>
       <c r="BA11">
-        <v>0.54748419975755047</v>
+        <v>0.16741252389280467</v>
       </c>
       <c r="BB11">
-        <v>-0.56473652980982647</v>
+        <v>-0.88979209622036626</v>
       </c>
       <c r="BC11">
-        <v>-0.19870076920188781</v>
+        <v>-0.31210902579773586</v>
       </c>
       <c r="BD11">
-        <v>-0.098859833907865541</v>
+        <v>-0.11096365665206903</v>
       </c>
       <c r="BE11">
-        <v>-0.16333733200670045</v>
+        <v>-0.049945623403468552</v>
       </c>
       <c r="BF11">
-        <v>-0.48841449044163893</v>
+        <v>-0.758160148865506</v>
       </c>
       <c r="BG11">
-        <v>-1.7181224222421</v>
+        <v>-0.43730005307162484</v>
       </c>
       <c r="BH11">
-        <v>73.14920904667467</v>
+        <v>73.153215262182968</v>
       </c>
       <c r="BI11">
-        <v>47.819604925971554</v>
+        <v>46.733721586809828</v>
       </c>
       <c r="BJ11">
-        <v>-1.009784915613402</v>
+        <v>-1.133483551705506</v>
       </c>
       <c r="BK11">
-        <v>0.6031941838813426</v>
+        <v>0.18354736758108398</v>
       </c>
       <c r="BL11">
-        <v>-0.65626976293463879</v>
+        <v>-0.73655007250203419</v>
       </c>
       <c r="BM11">
-        <v>0.14966714945805656</v>
+        <v>0.049253258598634053</v>
       </c>
       <c r="BN11">
-        <v>0.10771476152225815</v>
+        <v>0.060433681358118933</v>
       </c>
       <c r="BO11">
-        <v>0.11185615791964139</v>
+        <v>0.13900407719143568</v>
       </c>
       <c r="BP11">
-        <v>-1.3575958231691265</v>
+        <v>-1.3611607403812929</v>
       </c>
       <c r="BQ11">
-        <v>1.7993767883692535</v>
+        <v>1.3617998016182586</v>
       </c>
       <c r="BR11">
-        <v>-16.551681297139957</v>
+        <v>-19.710295481482486</v>
       </c>
       <c r="BS11">
-        <v>-1.468446269756633</v>
+        <v>-1.1061469816705212</v>
       </c>
       <c r="BT11">
-        <v>-0.020116150330924384</v>
+        <v>-0.017062436718488679</v>
       </c>
       <c r="BU11">
-        <v>1.0412783872107567</v>
+        <v>1.1659665222264919</v>
       </c>
       <c r="BV11">
-        <v>13.70459728935489</v>
+        <v>13.703758054151763</v>
       </c>
       <c r="BW11">
-        <v>-1.6919619847538756</v>
+        <v>-1.6987458357612866</v>
       </c>
       <c r="BX11">
-        <v>-151.15392518295315</v>
+        <v>-315.95881929410638</v>
       </c>
       <c r="BY11">
-        <v>52.539899949840482</v>
+        <v>12.982748312399096</v>
       </c>
       <c r="BZ11">
-        <v>120.56966899994397</v>
+        <v>251.55461426514114</v>
       </c>
       <c r="CA11">
-        <v>-86.718221708875618</v>
+        <v>-19.284620418010654</v>
       </c>
       <c r="CB11">
-        <v>190.73226039344681</v>
+        <v>316.42077743200832</v>
       </c>
       <c r="CC11">
-        <v>52.567984851971062</v>
+        <v>12.990111049545266</v>
       </c>
       <c r="CD11">
-        <v>0.64488304047921852</v>
+        <v>0.38872289297257012</v>
       </c>
       <c r="CE11">
-        <v>2.33982718467071</v>
+        <v>9.4687412240641109</v>
       </c>
     </row>
   </sheetData>
@@ -7389,28 +7389,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>227.3925046610361</v>
+        <v>235.63216491241906</v>
       </c>
       <c r="C3">
-        <v>109.32280890054773</v>
+        <v>69.814217961473943</v>
       </c>
       <c r="D3">
-        <v>0.53603857730649818</v>
+        <v>0.34231753143004695</v>
       </c>
       <c r="E3">
-        <v>4.9032638540612226</v>
+        <v>4.9032638540612217</v>
       </c>
       <c r="F3">
-        <v>109.32280890054773</v>
+        <v>69.814217961473943</v>
       </c>
       <c r="G3">
-        <v>37.560841960432178</v>
+        <v>48.292511091984224</v>
       </c>
       <c r="H3">
-        <v>0.53494166395377718</v>
+        <v>0.34222056481212354</v>
       </c>
       <c r="I3">
-        <v>4.8932301441359778</v>
+        <v>4.90187493041852</v>
       </c>
       <c r="J3">
         <v>301.22432772946655</v>
@@ -7458,37 +7458,37 @@
         <v>31.146463255638665</v>
       </c>
       <c r="Y3">
-        <v>31.878981833936816</v>
+        <v>35.29336527669517</v>
       </c>
       <c r="Z3">
-        <v>12.232868807108174</v>
+        <v>12.232868807108176</v>
       </c>
       <c r="AA3">
-        <v>0.48857577491856258</v>
+        <v>0.50105290867266339</v>
       </c>
       <c r="AB3">
-        <v>1.6665517917131332</v>
+        <v>1.6666594422619077</v>
       </c>
       <c r="AC3">
-        <v>0.1255502938646294</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.1159912849093541</v>
+        <v>1.1180165935167421</v>
       </c>
       <c r="AE3">
-        <v>32.270644646107591</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="AF3">
-        <v>17.805745227229156</v>
+        <v>29.769093119297569</v>
       </c>
       <c r="AG3">
-        <v>31038.203210478991</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AH3">
-        <v>1571.0926173190044</v>
+        <v>2019.9763563475462</v>
       </c>
       <c r="AI3">
-        <v>1571.0926173190044</v>
+        <v>2019.9763563475462</v>
       </c>
       <c r="AJ3">
         <v>24.705355693686609</v>
@@ -7503,136 +7503,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-7.174679516277509</v>
+        <v>-10.588009583008557</v>
       </c>
       <c r="AO3">
-        <v>-2.7846600873521687</v>
+        <v>-2.7847191895336247</v>
       </c>
       <c r="AP3">
-        <v>-0.47285529142251032</v>
+        <v>-0.50105290867266339</v>
       </c>
       <c r="AQ3">
-        <v>-1.6126222751706361</v>
+        <v>-1.6126314712079848</v>
       </c>
       <c r="AR3">
-        <v>802.62996732164311</v>
+        <v>537.10763923259378</v>
       </c>
       <c r="AS3">
-        <v>106.30598317008956</v>
+        <v>137.13906149937242</v>
       </c>
       <c r="AT3">
-        <v>-3.972356807073302</v>
+        <v>-3.4180744619002827</v>
       </c>
       <c r="AU3">
-        <v>-0.59511839591629911</v>
+        <v>-0.4190974619128866</v>
       </c>
       <c r="AV3">
-        <v>-1.3055328824654839</v>
+        <v>-1.1233655035168118</v>
       </c>
       <c r="AW3">
-        <v>0.56295143507413414</v>
+        <v>0.39644467258741839</v>
       </c>
       <c r="AX3">
-        <v>0.0017160661923017846</v>
+        <v>0.0014766150957015358</v>
       </c>
       <c r="AY3">
-        <v>2.2087507554436212</v>
+        <v>1.555458278481423</v>
       </c>
       <c r="AZ3">
-        <v>-0.0052615554846178175</v>
+        <v>-0.0045273849518804483</v>
       </c>
       <c r="BA3">
-        <v>2.6140284503042839</v>
+        <v>1.8408651058480874</v>
       </c>
       <c r="BB3">
-        <v>-0.88703999514217335</v>
+        <v>-1.1317624713645493</v>
       </c>
       <c r="BC3">
-        <v>-0.46276562179460562</v>
+        <v>-0.58016811240683219</v>
       </c>
       <c r="BD3">
-        <v>-0.012198544007905265</v>
+        <v>-0.016703754245654335</v>
       </c>
       <c r="BE3">
-        <v>-0.21678386989950171</v>
+        <v>-0.15266429921633087</v>
       </c>
       <c r="BF3">
-        <v>-0.015198216493973571</v>
+        <v>-0.031099453862768085</v>
       </c>
       <c r="BG3">
-        <v>-2.0392442968393185</v>
+        <v>-1.1132079915613942</v>
       </c>
       <c r="BH3">
-        <v>72.587691378763239</v>
+        <v>72.461113406556407</v>
       </c>
       <c r="BI3">
-        <v>36.946400223752349</v>
+        <v>37.26449528592012</v>
       </c>
       <c r="BJ3">
-        <v>-0.0045069247389963084</v>
+        <v>-0.0038719363743517</v>
       </c>
       <c r="BK3">
-        <v>3.3364374439902837</v>
+        <v>2.3525449327798649</v>
       </c>
       <c r="BL3">
-        <v>-0.003211927566290379</v>
+        <v>-0.0027723122761224789</v>
       </c>
       <c r="BM3">
-        <v>0.76151810287908872</v>
+        <v>0.52322761134831619</v>
       </c>
       <c r="BN3">
-        <v>0.042454043316593054</v>
+        <v>0.020688087853250131</v>
       </c>
       <c r="BO3">
-        <v>0.14820992116157147</v>
+        <v>0.18779893398767233</v>
       </c>
       <c r="BP3">
-        <v>-1.5231663735241126</v>
+        <v>0.000305264002156285</v>
       </c>
       <c r="BQ3">
-        <v>1.2031378731635203</v>
+        <v>0.84543039089892924</v>
       </c>
       <c r="BR3">
-        <v>-18.470486073187498</v>
+        <v>23.293412314639106</v>
       </c>
       <c r="BS3">
-        <v>-0.99025160184295513</v>
+        <v>-0.5823894827299132</v>
       </c>
       <c r="BT3">
-        <v>-0.012495575207137405</v>
+        <v>-0.27623835607432828</v>
       </c>
       <c r="BU3">
-        <v>1.4331086856460393</v>
+        <v>1.7028284307059776</v>
       </c>
       <c r="BV3">
-        <v>14.812876148690803</v>
+        <v>14.811421642263355</v>
       </c>
       <c r="BW3">
-        <v>-1.9938489091957923</v>
+        <v>-2.00471469946858</v>
       </c>
       <c r="BX3">
-        <v>-0.16818809987555633</v>
+        <v>-0.34256501177293674</v>
       </c>
       <c r="BY3">
-        <v>268.54171295806822</v>
+        <v>134.63999223521878</v>
       </c>
       <c r="BZ3">
-        <v>0.13638735639364677</v>
+        <v>0.23938989130145416</v>
       </c>
       <c r="CA3">
-        <v>-380.78695258987591</v>
+        <v>-162.26198321617792</v>
       </c>
       <c r="CB3">
-        <v>5.0296404630369418</v>
+        <v>5.1413588809852477</v>
       </c>
       <c r="CC3">
-        <v>268.54945562364435</v>
+        <v>134.64459417716051</v>
       </c>
       <c r="CD3">
-        <v>39.764273703022937</v>
+        <v>38.900221639784391</v>
       </c>
       <c r="CE3">
-        <v>0.74474178149252246</v>
+        <v>1.4853919774665976</v>
       </c>
     </row>
     <row r="4" spans="1:83">
@@ -7640,28 +7640,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>227.93499130722384</v>
+        <v>234.22391635587769</v>
       </c>
       <c r="C4">
-        <v>88.8225275127105</v>
+        <v>59.215018341806989</v>
       </c>
       <c r="D4">
-        <v>0.34903357789144707</v>
+        <v>0.23268905192763134</v>
       </c>
       <c r="E4">
         <v>3.9295614261990051</v>
       </c>
       <c r="F4">
-        <v>88.8225275127105</v>
+        <v>59.215018341806989</v>
       </c>
       <c r="G4">
-        <v>36.927401065004595</v>
+        <v>47.478087083577321</v>
       </c>
       <c r="H4">
-        <v>0.34853131677035715</v>
+        <v>0.23309950778263311</v>
       </c>
       <c r="I4">
-        <v>3.9239067670133827</v>
+        <v>3.9364930436584897</v>
       </c>
       <c r="J4">
         <v>423.3462934690229</v>
@@ -7712,34 +7712,34 @@
         <v>28.734961193392547</v>
       </c>
       <c r="Z4">
-        <v>12.129280241400279</v>
+        <v>12.129280241400281</v>
       </c>
       <c r="AA4">
         <v>0.61646592200840677</v>
       </c>
       <c r="AB4">
-        <v>1.8267866815750018</v>
+        <v>1.8269044365883842</v>
       </c>
       <c r="AC4">
-        <v>0.17573851509306887</v>
+        <v>0.17564464381670725</v>
       </c>
       <c r="AD4">
-        <v>1.2325487418079597</v>
+        <v>1.2347883954903314</v>
       </c>
       <c r="AE4">
-        <v>22.859006548711257</v>
+        <v>7.9473881770507271</v>
       </c>
       <c r="AF4">
-        <v>19.213244217584567</v>
+        <v>31.34506311307711</v>
       </c>
       <c r="AG4">
-        <v>20489.117879602942</v>
+        <v>13659.411851170204</v>
       </c>
       <c r="AH4">
-        <v>1518.6726797922415</v>
+        <v>1952.5793194635558</v>
       </c>
       <c r="AI4">
-        <v>1518.6726797922415</v>
+        <v>1952.5793194635558</v>
       </c>
       <c r="AJ4">
         <v>22.268824042909408</v>
@@ -7754,136 +7754,136 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-6.4679975654014195</v>
+        <v>-6.4679965878962884</v>
       </c>
       <c r="AO4">
-        <v>-2.7680767985166415</v>
+        <v>-2.7681484303430159</v>
       </c>
       <c r="AP4">
-        <v>-0.59663001585337783</v>
+        <v>-0.59664061277947322</v>
       </c>
       <c r="AQ4">
-        <v>-1.7676533032913322</v>
+        <v>-1.7676628273397954</v>
       </c>
       <c r="AR4">
-        <v>587.8082179034426</v>
+        <v>391.66317915221271</v>
       </c>
       <c r="AS4">
-        <v>103.62870921633811</v>
+        <v>133.68437731548397</v>
       </c>
       <c r="AT4">
-        <v>-4.7553649078610736</v>
+        <v>-3.4205256354790179</v>
       </c>
       <c r="AU4">
-        <v>-0.79629100143621134</v>
+        <v>-0.45370068686481807</v>
       </c>
       <c r="AV4">
-        <v>-1.5449338915670532</v>
+        <v>-1.1112682377938454</v>
       </c>
       <c r="AW4">
-        <v>0.76102437163163539</v>
+        <v>0.43360690941802477</v>
       </c>
       <c r="AX4">
-        <v>0.0013642134289491262</v>
+        <v>0.00098127632608621348</v>
       </c>
       <c r="AY4">
-        <v>1.9682059274794828</v>
+        <v>1.1214196563545891</v>
       </c>
       <c r="AZ4">
-        <v>-0.004226007387870879</v>
+        <v>-0.0030397597000474748</v>
       </c>
       <c r="BA4">
-        <v>2.5896485453855234</v>
+        <v>1.4754974270219841</v>
       </c>
       <c r="BB4">
-        <v>-1.1283549701320053</v>
+        <v>-1.181560533493466</v>
       </c>
       <c r="BC4">
-        <v>-0.53797584687982658</v>
+        <v>-0.5567355985078406</v>
       </c>
       <c r="BD4">
-        <v>-0.0095445044887308914</v>
+        <v>-0.0068652966641230967</v>
       </c>
       <c r="BE4">
-        <v>-0.25057629728725905</v>
+        <v>-0.1427698652202781</v>
       </c>
       <c r="BF4">
-        <v>-0.016237446497045633</v>
+        <v>-0.017528573094319457</v>
       </c>
       <c r="BG4">
-        <v>-2.418020056238944</v>
+        <v>-1.0679622263067667</v>
       </c>
       <c r="BH4">
-        <v>71.850191240319546</v>
+        <v>71.53621272584131</v>
       </c>
       <c r="BI4">
-        <v>34.851928109217333</v>
+        <v>35.233143630950188</v>
       </c>
       <c r="BJ4">
-        <v>-0.0035907875703715094</v>
+        <v>-0.0025725097294631068</v>
       </c>
       <c r="BK4">
-        <v>3.0950462524023781</v>
+        <v>1.7672099747399308</v>
       </c>
       <c r="BL4">
-        <v>-0.0026127497673006988</v>
+        <v>-0.0018934719311327597</v>
       </c>
       <c r="BM4">
-        <v>1.0004013479962539</v>
+        <v>0.55825048856819848</v>
       </c>
       <c r="BN4">
-        <v>0.0465119698097451</v>
+        <v>0.024536740931889157</v>
       </c>
       <c r="BO4">
-        <v>0.2342954524313233</v>
+        <v>0.29054963268952588</v>
       </c>
       <c r="BP4">
-        <v>-1.5218104139463076</v>
+        <v>-0.81765462300736946</v>
       </c>
       <c r="BQ4">
-        <v>1.2603093391385782</v>
+        <v>0.90753401412831725</v>
       </c>
       <c r="BR4">
-        <v>-22.00098205297947</v>
+        <v>38.705122992455834</v>
       </c>
       <c r="BS4">
-        <v>-1.0252599205353514</v>
+        <v>-0.81914983846424516</v>
       </c>
       <c r="BT4">
-        <v>-0.00615890649103432</v>
+        <v>-0.26841839636864212</v>
       </c>
       <c r="BU4">
-        <v>1.4826619238851573</v>
+        <v>1.7524594487931124</v>
       </c>
       <c r="BV4">
-        <v>14.801230557803164</v>
+        <v>14.798951216417008</v>
       </c>
       <c r="BW4">
-        <v>-2.2220050297309646</v>
+        <v>-2.2372333119636187</v>
       </c>
       <c r="BX4">
-        <v>-0.19816867848460917</v>
+        <v>-0.2938752725088663</v>
       </c>
       <c r="BY4">
-        <v>238.8448889122065</v>
+        <v>98.879025625817349</v>
       </c>
       <c r="BZ4">
-        <v>0.15824654018665468</v>
+        <v>0.27051795283489072</v>
       </c>
       <c r="CA4">
-        <v>-367.69109958151586</v>
+        <v>-130.36453360407484</v>
       </c>
       <c r="CB4">
-        <v>4.0821856006498463</v>
+        <v>4.2070475128634977</v>
       </c>
       <c r="CC4">
-        <v>238.85712838531038</v>
+        <v>98.8847928249226</v>
       </c>
       <c r="CD4">
-        <v>48.993362763359372</v>
+        <v>47.539277697358678</v>
       </c>
       <c r="CE4">
-        <v>0.83732062489410686</v>
+        <v>2.0225556861316765</v>
       </c>
     </row>
     <row r="5" spans="1:83">
@@ -7891,28 +7891,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>227.168953466399</v>
+        <v>232.5503088636367</v>
       </c>
       <c r="C5">
-        <v>69.7722169687325</v>
+        <v>46.514811312488327</v>
       </c>
       <c r="D5">
-        <v>0.4212015069120858</v>
+        <v>0.28080100460805724</v>
       </c>
       <c r="E5">
-        <v>6.0368084204754693</v>
+        <v>6.03680842047547</v>
       </c>
       <c r="F5">
-        <v>69.7722169687325</v>
+        <v>46.514811312488327</v>
       </c>
       <c r="G5">
-        <v>33.666766708926517</v>
+        <v>43.285842911476941</v>
       </c>
       <c r="H5">
-        <v>0.42047012743342083</v>
+        <v>0.28210886335792945</v>
       </c>
       <c r="I5">
-        <v>6.0263260320630057</v>
+        <v>6.0649254591771005</v>
       </c>
       <c r="J5">
         <v>588.98399302146879</v>
@@ -7963,7 +7963,7 @@
         <v>25.467734439046545</v>
       </c>
       <c r="Z5">
-        <v>11.581408051081152</v>
+        <v>11.58140805108115</v>
       </c>
       <c r="AA5">
         <v>0.62018720238767078</v>
@@ -7972,25 +7972,25 @@
         <v>2.0045499898604895</v>
       </c>
       <c r="AC5">
-        <v>0.19947477922290915</v>
+        <v>0.19936829209814289</v>
       </c>
       <c r="AD5">
-        <v>1.41160428996194</v>
+        <v>1.4165085019227341</v>
       </c>
       <c r="AE5">
-        <v>14.665728822568124</v>
+        <v>5.2805225902439483</v>
       </c>
       <c r="AF5">
-        <v>18.849809741603625</v>
+        <v>29.770302994238737</v>
       </c>
       <c r="AG5">
-        <v>12642.798860980411</v>
+        <v>8428.53251951291</v>
       </c>
       <c r="AH5">
-        <v>1262.4981910480231</v>
+        <v>1623.2153325420291</v>
       </c>
       <c r="AI5">
-        <v>1262.4981910480231</v>
+        <v>1623.2153325420291</v>
       </c>
       <c r="AJ5">
         <v>19.736810959225576</v>
@@ -8005,136 +8005,136 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-5.7330479204309448</v>
+        <v>-5.7330468048605567</v>
       </c>
       <c r="AO5">
-        <v>-2.6547179924569448</v>
+        <v>-2.6548840141427354</v>
       </c>
       <c r="AP5">
-        <v>-0.60023132175117466</v>
+        <v>-0.60024197691172887</v>
       </c>
       <c r="AQ5">
-        <v>-1.9397406112106572</v>
+        <v>-1.9395133744586219</v>
       </c>
       <c r="AR5">
-        <v>409.23767750384673</v>
+        <v>272.67973276673973</v>
       </c>
       <c r="AS5">
-        <v>90.207792954583979</v>
+        <v>116.37134164603774</v>
       </c>
       <c r="AT5">
-        <v>-5.2952185701160808</v>
+        <v>-3.1503199088032381</v>
       </c>
       <c r="AU5">
-        <v>-1.0471077660306634</v>
+        <v>-0.39364953610175307</v>
       </c>
       <c r="AV5">
-        <v>-1.6854583446928368</v>
+        <v>-1.00274104051346</v>
       </c>
       <c r="AW5">
-        <v>0.90657873604476058</v>
+        <v>0.34081907370103781</v>
       </c>
       <c r="AX5">
-        <v>0.003687933943378519</v>
+        <v>0.0021940872827694987</v>
       </c>
       <c r="AY5">
-        <v>1.8177141107892789</v>
+        <v>0.68335116946965391</v>
       </c>
       <c r="AZ5">
-        <v>-0.011708412392768614</v>
+        <v>-0.0069657643349382891</v>
       </c>
       <c r="BA5">
-        <v>2.5801528588707789</v>
+        <v>0.96998227777096979</v>
       </c>
       <c r="BB5">
-        <v>-1.4082333422240578</v>
+        <v>-1.2230908749753775</v>
       </c>
       <c r="BC5">
-        <v>-0.61874149638816023</v>
+        <v>-0.53252015054369561</v>
       </c>
       <c r="BD5">
-        <v>-0.013671337025470836</v>
+        <v>-0.00813351089304566</v>
       </c>
       <c r="BE5">
-        <v>-0.27795615277785446</v>
+        <v>-0.10449387142979144</v>
       </c>
       <c r="BF5">
-        <v>-0.033406838561051914</v>
+        <v>-0.029828072700963673</v>
       </c>
       <c r="BG5">
-        <v>-3.0812875880667461</v>
+        <v>-0.89793474881149393</v>
       </c>
       <c r="BH5">
-        <v>71.884802494415666</v>
+        <v>71.2118646520448</v>
       </c>
       <c r="BI5">
-        <v>33.875786804861342</v>
+        <v>33.846528798966268</v>
       </c>
       <c r="BJ5">
-        <v>-0.0099813810232326529</v>
+        <v>-0.0058879514224398008</v>
       </c>
       <c r="BK5">
-        <v>2.9473158351848809</v>
+        <v>1.1077965930053031</v>
       </c>
       <c r="BL5">
-        <v>-0.0071456147670380457</v>
+        <v>-0.0043206388209729163</v>
       </c>
       <c r="BM5">
-        <v>1.1289830518524002</v>
+        <v>0.42499546883601635</v>
       </c>
       <c r="BN5">
-        <v>0.047580819616232367</v>
+        <v>0.02634094097192918</v>
       </c>
       <c r="BO5">
-        <v>0.32768370754901638</v>
+        <v>0.40313161544974274</v>
       </c>
       <c r="BP5">
-        <v>-0.81527606233986594</v>
+        <v>-0.81714392586738638</v>
       </c>
       <c r="BQ5">
-        <v>1.2875718617747065</v>
+        <v>0.93487416903001108</v>
       </c>
       <c r="BR5">
-        <v>-23.413330630259725</v>
+        <v>38.704390198056274</v>
       </c>
       <c r="BS5">
-        <v>-1.0526177257195506</v>
+        <v>-0.92879082468944529</v>
       </c>
       <c r="BT5">
-        <v>0.0032005512165276151</v>
+        <v>-0.25703811251608355</v>
       </c>
       <c r="BU5">
-        <v>1.5587241071825166</v>
+        <v>1.8285789628047953</v>
       </c>
       <c r="BV5">
-        <v>14.782153300241998</v>
+        <v>14.778538567264988</v>
       </c>
       <c r="BW5">
-        <v>-2.5671523900101882</v>
+        <v>-2.5878804843446166</v>
       </c>
       <c r="BX5">
-        <v>-0.87677218725657091</v>
+        <v>-1.042833456279687</v>
       </c>
       <c r="BY5">
-        <v>243.71589724969292</v>
+        <v>68.111400934015634</v>
       </c>
       <c r="BZ5">
-        <v>0.70317040266427644</v>
+        <v>1.0554721132780605</v>
       </c>
       <c r="CA5">
-        <v>-414.61331431008983</v>
+        <v>-100.1681890987534</v>
       </c>
       <c r="CB5">
-        <v>6.7295793540064475</v>
+        <v>7.1204600486026468</v>
       </c>
       <c r="CC5">
-        <v>243.73537475184691</v>
+        <v>68.1173195597665</v>
       </c>
       <c r="CD5">
-        <v>29.719539584733511</v>
+        <v>28.0880727698555</v>
       </c>
       <c r="CE5">
-        <v>0.82056205507150948</v>
+        <v>2.9361108348445644</v>
       </c>
     </row>
     <row r="6" spans="1:83">
@@ -8142,28 +8142,28 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>223.10189816061211</v>
+        <v>227.86618491185288</v>
       </c>
       <c r="C6">
-        <v>58.237071832669386</v>
+        <v>38.824714555112919</v>
       </c>
       <c r="D6">
-        <v>0.26252963657692041</v>
+        <v>0.17501975771794689</v>
       </c>
       <c r="E6">
         <v>4.5079470570092859</v>
       </c>
       <c r="F6">
-        <v>58.237071832669386</v>
+        <v>38.824714555112919</v>
       </c>
       <c r="G6">
-        <v>31.634784972071781</v>
+        <v>40.673294964092285</v>
       </c>
       <c r="H6">
-        <v>0.26222440906464844</v>
+        <v>0.17580842431149518</v>
       </c>
       <c r="I6">
-        <v>4.50270593648817</v>
+        <v>4.5282605764410579</v>
       </c>
       <c r="J6">
         <v>809.18955657148092</v>
@@ -8214,7 +8214,7 @@
         <v>23.267451461230138</v>
       </c>
       <c r="Z6">
-        <v>11.226466948912126</v>
+        <v>11.226466948912124</v>
       </c>
       <c r="AA6">
         <v>0.5705678558440741</v>
@@ -8223,25 +8223,25 @@
         <v>1.9738667955030851</v>
       </c>
       <c r="AC6">
-        <v>0.20086912366835222</v>
+        <v>0.20076189192008617</v>
       </c>
       <c r="AD6">
-        <v>1.4336145814080854</v>
+        <v>1.4385966152171854</v>
       </c>
       <c r="AE6">
-        <v>10.241999545672483</v>
+        <v>3.6952832192721137</v>
       </c>
       <c r="AF6">
-        <v>16.975162558557741</v>
+        <v>26.711993486847092</v>
       </c>
       <c r="AG6">
-        <v>8808.00024538548</v>
+        <v>5872.0001251068807</v>
       </c>
       <c r="AH6">
-        <v>1114.7200192737764</v>
+        <v>1433.2145247159835</v>
       </c>
       <c r="AI6">
-        <v>1114.7200192737764</v>
+        <v>1433.2145247159835</v>
       </c>
       <c r="AJ6">
         <v>18.031650679111152</v>
@@ -8256,136 +8256,136 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>-5.2377689144152484</v>
+        <v>-5.23776788092174</v>
       </c>
       <c r="AO6">
-        <v>-2.5748490296579809</v>
+        <v>-2.575015103892389</v>
       </c>
       <c r="AP6">
-        <v>-0.55220857232172915</v>
+        <v>-0.5522183750518268</v>
       </c>
       <c r="AQ6">
-        <v>-1.9100453367781285</v>
+        <v>-1.9098214389844359</v>
       </c>
       <c r="AR6">
-        <v>312.06940018941623</v>
+        <v>207.93540150544663</v>
       </c>
       <c r="AS6">
-        <v>82.1649834353701</v>
+        <v>105.99571343122054</v>
       </c>
       <c r="AT6">
-        <v>-5.87015665114485</v>
+        <v>-3.3061801828287085</v>
       </c>
       <c r="AU6">
-        <v>-1.2311819420910577</v>
+        <v>-0.45264041988641829</v>
       </c>
       <c r="AV6">
-        <v>-1.8206553382552486</v>
+        <v>-1.0254265698219216</v>
       </c>
       <c r="AW6">
-        <v>1.0103925175564017</v>
+        <v>0.37146783733691241</v>
       </c>
       <c r="AX6">
-        <v>0.0023554936710573644</v>
+        <v>0.001326657354963343</v>
       </c>
       <c r="AY6">
-        <v>1.602356822535657</v>
+        <v>0.58910177299105038</v>
       </c>
       <c r="AZ6">
-        <v>-0.0076580543773947371</v>
+        <v>-0.0043131570631303687</v>
       </c>
       <c r="BA6">
-        <v>2.3465929604950464</v>
+        <v>0.86271800018200229</v>
       </c>
       <c r="BB6">
-        <v>-1.7165586478634487</v>
+        <v>-1.4127335813501663</v>
       </c>
       <c r="BC6">
-        <v>-0.71252245909813128</v>
+        <v>-0.58158986810411661</v>
       </c>
       <c r="BD6">
-        <v>-0.010196221464815134</v>
+        <v>-0.0057426478589016608</v>
       </c>
       <c r="BE6">
-        <v>-0.2737888552440001</v>
+        <v>-0.10065669968928685</v>
       </c>
       <c r="BF6">
-        <v>-0.032672929350414846</v>
+        <v>-0.027617461083226075</v>
       </c>
       <c r="BG6">
-        <v>-3.332184147026072</v>
+        <v>-0.94962990889817334</v>
       </c>
       <c r="BH6">
-        <v>72.38444116183814</v>
+        <v>71.6272658323713</v>
       </c>
       <c r="BI6">
-        <v>34.949214192145767</v>
+        <v>34.914258266381218</v>
       </c>
       <c r="BJ6">
-        <v>-0.00658611686052228</v>
+        <v>-0.0036751396728796951</v>
       </c>
       <c r="BK6">
-        <v>2.6576340856295255</v>
+        <v>0.97684563989955087</v>
       </c>
       <c r="BL6">
-        <v>-0.0045625882984409345</v>
+        <v>-0.0026185285894057848</v>
       </c>
       <c r="BM6">
-        <v>1.0054983718890791</v>
+        <v>0.37026455756454624</v>
       </c>
       <c r="BN6">
-        <v>0.046154263230346423</v>
+        <v>0.025690215535535247</v>
       </c>
       <c r="BO6">
-        <v>0.33010503971278754</v>
+        <v>0.40475917985889931</v>
       </c>
       <c r="BP6">
-        <v>-0.81526995518563139</v>
+        <v>-0.81712554242018487</v>
       </c>
       <c r="BQ6">
-        <v>1.2891558158262801</v>
+        <v>0.93646917847000111</v>
       </c>
       <c r="BR6">
-        <v>-23.413340465000591</v>
+        <v>38.704356699491534</v>
       </c>
       <c r="BS6">
-        <v>-1.05504925299128</v>
+        <v>-0.93472054719949149</v>
       </c>
       <c r="BT6">
-        <v>0.0041479273788182069</v>
+        <v>-0.25599112597994705</v>
       </c>
       <c r="BU6">
-        <v>1.5679039898027645</v>
+        <v>1.8376986104327877</v>
       </c>
       <c r="BV6">
-        <v>14.780025988547106</v>
+        <v>14.776388281862037</v>
       </c>
       <c r="BW6">
-        <v>-2.6069475162805893</v>
+        <v>-2.6274879482919995</v>
       </c>
       <c r="BX6">
-        <v>-0.82941384205334112</v>
+        <v>-0.93172872830883768</v>
       </c>
       <c r="BY6">
-        <v>245.46755055855223</v>
+        <v>67.269949404178675</v>
       </c>
       <c r="BZ6">
-        <v>0.666321096773757</v>
+        <v>0.94688485999117666</v>
       </c>
       <c r="CA6">
-        <v>-421.47596863409643</v>
+        <v>-99.903471427305519</v>
       </c>
       <c r="CB6">
-        <v>5.1691302934734509</v>
+        <v>5.4752150893130587</v>
       </c>
       <c r="CC6">
-        <v>245.49016645968752</v>
+        <v>67.276651892054147</v>
       </c>
       <c r="CD6">
-        <v>38.691228242499555</v>
+        <v>36.528245326905093</v>
       </c>
       <c r="CE6">
-        <v>0.81469658391731314</v>
+        <v>2.9727995430108702</v>
       </c>
     </row>
     <row r="7" spans="1:83">
@@ -8393,28 +8393,28 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>219.96846721960262</v>
+        <v>224.2498532157588</v>
       </c>
       <c r="C7">
-        <v>50.473070239288788</v>
+        <v>33.648713492859187</v>
       </c>
       <c r="D7">
-        <v>0.17784978054738457</v>
+        <v>0.11856652036492309</v>
       </c>
       <c r="E7">
-        <v>3.5236568670027997</v>
+        <v>3.5236568670028006</v>
       </c>
       <c r="F7">
-        <v>50.473070239288788</v>
+        <v>33.648713492859187</v>
       </c>
       <c r="G7">
-        <v>31.406276844739608</v>
+        <v>40.379498800379494</v>
       </c>
       <c r="H7">
-        <v>0.17771043268271886</v>
+        <v>0.11908272942301734</v>
       </c>
       <c r="I7">
-        <v>3.5208960310955506</v>
+        <v>3.53899799016948</v>
       </c>
       <c r="J7">
         <v>1071.939064917214</v>
@@ -8468,31 +8468,31 @@
         <v>11.185847290622426</v>
       </c>
       <c r="AA7">
-        <v>0.541161717425563</v>
+        <v>0.54116171742556307</v>
       </c>
       <c r="AB7">
-        <v>2.0392308795994256</v>
+        <v>2.0392308795994252</v>
       </c>
       <c r="AC7">
-        <v>0.20464476778976717</v>
+        <v>0.20453551970113268</v>
       </c>
       <c r="AD7">
-        <v>1.485634049352915</v>
+        <v>1.4908002543296484</v>
       </c>
       <c r="AE7">
-        <v>7.7439781692803438</v>
+        <v>2.8095472857188177</v>
       </c>
       <c r="AF7">
-        <v>17.522556687718218</v>
+        <v>27.345219685131617</v>
       </c>
       <c r="AG7">
-        <v>6616.0367068352925</v>
+        <v>4410.6911078868889</v>
       </c>
       <c r="AH7">
-        <v>1098.7237543581007</v>
+        <v>1412.6480778117116</v>
       </c>
       <c r="AI7">
-        <v>1098.7237543581007</v>
+        <v>1412.6480778117116</v>
       </c>
       <c r="AJ7">
         <v>16.786709767180497</v>
@@ -8507,136 +8507,136 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>-4.8762125011998023</v>
+        <v>-4.8762115025391264</v>
       </c>
       <c r="AO7">
-        <v>-2.5691393279058059</v>
+        <v>-2.5693172432980176</v>
       </c>
       <c r="AP7">
-        <v>-0.52374860516989774</v>
+        <v>-0.52375790283275381</v>
       </c>
       <c r="AQ7">
-        <v>-1.9732859082343661</v>
+        <v>-1.9730542478908431</v>
       </c>
       <c r="AR7">
-        <v>251.79183835247949</v>
+        <v>167.77177512105632</v>
       </c>
       <c r="AS7">
-        <v>81.274990940706545</v>
+        <v>104.84732719885339</v>
       </c>
       <c r="AT7">
-        <v>-6.4982362390582056</v>
+        <v>-3.5635489052899842</v>
       </c>
       <c r="AU7">
-        <v>-1.4809115723366186</v>
+        <v>-0.44246748197862384</v>
       </c>
       <c r="AV7">
-        <v>-1.9791401060101033</v>
+        <v>-1.0853348968442502</v>
       </c>
       <c r="AW7">
-        <v>1.1312965061795051</v>
+        <v>0.33800932196826677</v>
       </c>
       <c r="AX7">
-        <v>0.0016398430878730858</v>
+        <v>0.00089926879012395037</v>
       </c>
       <c r="AY7">
-        <v>1.4576326960735939</v>
+        <v>0.43551220797320794</v>
       </c>
       <c r="AZ7">
-        <v>-0.0054213555903352487</v>
+        <v>-0.0029730014527644911</v>
       </c>
       <c r="BA7">
-        <v>2.2531933265162518</v>
+        <v>0.6732102012152219</v>
       </c>
       <c r="BB7">
-        <v>-2.0274415448523668</v>
+        <v>-1.6259518855495498</v>
       </c>
       <c r="BC7">
-        <v>-0.80633087974122908</v>
+        <v>-0.64178397461116865</v>
       </c>
       <c r="BD7">
-        <v>-0.0080931103940116034</v>
+        <v>-0.004438114975213671</v>
       </c>
       <c r="BE7">
-        <v>-0.28914220227423348</v>
+        <v>-0.086389132797913382</v>
       </c>
       <c r="BF7">
-        <v>-0.032142068015255459</v>
+        <v>-0.026453287342351438</v>
       </c>
       <c r="BG7">
-        <v>-3.5575790157291389</v>
+        <v>-0.82395169343771435</v>
       </c>
       <c r="BH7">
-        <v>72.861250543826642</v>
+        <v>72.067216045160009</v>
       </c>
       <c r="BI7">
-        <v>35.39466452225733</v>
+        <v>34.795207035050531</v>
       </c>
       <c r="BJ7">
-        <v>-0.0046973746297181915</v>
+        <v>-0.0025516824207559414</v>
       </c>
       <c r="BK7">
-        <v>2.4932969864043488</v>
+        <v>0.7418052465797571</v>
       </c>
       <c r="BL7">
-        <v>-0.0031646253139643995</v>
+        <v>-0.00177097115127149</v>
       </c>
       <c r="BM7">
-        <v>0.99249351680861841</v>
+        <v>0.304315353639418</v>
       </c>
       <c r="BN7">
-        <v>0.045181001782706377</v>
+        <v>0.025330115547251102</v>
       </c>
       <c r="BO7">
-        <v>0.36373025264029107</v>
+        <v>0.45498271846112293</v>
       </c>
       <c r="BP7">
-        <v>-0.81518819406078746</v>
+        <v>-0.817052536734534</v>
       </c>
       <c r="BQ7">
-        <v>1.2934858668934344</v>
+        <v>0.94080804229701676</v>
       </c>
       <c r="BR7">
-        <v>-23.413420593172887</v>
+        <v>38.704241975446706</v>
       </c>
       <c r="BS7">
-        <v>-1.0604524444056203</v>
+        <v>-0.95172440372925426</v>
       </c>
       <c r="BT7">
-        <v>0.007189969559817007</v>
+        <v>-0.25198408115161053</v>
       </c>
       <c r="BU7">
-        <v>1.5895250699950234</v>
+        <v>1.8593875593511464</v>
       </c>
       <c r="BV7">
-        <v>14.773553736317842</v>
+        <v>14.768975248381807</v>
       </c>
       <c r="BW7">
-        <v>-2.70828887055115</v>
+        <v>-2.7331463039705035</v>
       </c>
       <c r="BX7">
-        <v>-0.7849979869695094</v>
+        <v>-0.85478719593133667</v>
       </c>
       <c r="BY7">
-        <v>226.16815181973681</v>
+        <v>50.494669287402559</v>
       </c>
       <c r="BZ7">
-        <v>0.63205441572596255</v>
+        <v>0.8799140181155497</v>
       </c>
       <c r="CA7">
-        <v>-398.70951013849532</v>
+        <v>-77.324767354118748</v>
       </c>
       <c r="CB7">
-        <v>4.1530748279186236</v>
+        <v>4.4189911872934138</v>
       </c>
       <c r="CC7">
-        <v>226.1961300862786</v>
+        <v>50.501391296055147</v>
       </c>
       <c r="CD7">
-        <v>48.157090417808107</v>
+        <v>45.259198654907912</v>
       </c>
       <c r="CE7">
-        <v>0.88418842499079642</v>
+        <v>3.960286932047806</v>
       </c>
     </row>
     <row r="8" spans="1:83">
@@ -8644,28 +8644,28 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>217.49227741305941</v>
+        <v>221.38721110996937</v>
       </c>
       <c r="C8">
-        <v>44.90175169639992</v>
+        <v>29.934501130933274</v>
       </c>
       <c r="D8">
-        <v>0.12015041009985816</v>
+        <v>0.0801002733999054</v>
       </c>
       <c r="E8">
-        <v>2.6758512877681659</v>
+        <v>2.6758512877681655</v>
       </c>
       <c r="F8">
-        <v>44.90175169639992</v>
+        <v>29.934501130933274</v>
       </c>
       <c r="G8">
-        <v>32.589049831481809</v>
+        <v>41.90020692619089</v>
       </c>
       <c r="H8">
-        <v>0.12008969633274533</v>
+        <v>0.0804142362104209</v>
       </c>
       <c r="I8">
-        <v>2.6744991408068768</v>
+        <v>2.6863396139020206</v>
       </c>
       <c r="J8">
         <v>1383.4505275005968</v>
@@ -8722,28 +8722,28 @@
         <v>0.49616056392259061</v>
       </c>
       <c r="AB8">
-        <v>2.0555216676606585</v>
+        <v>2.055521667660658</v>
       </c>
       <c r="AC8">
-        <v>0.19892866514192378</v>
+        <v>0.19882246965761119</v>
       </c>
       <c r="AD8">
-        <v>1.4703225448573825</v>
+        <v>1.4754345042512735</v>
       </c>
       <c r="AE8">
-        <v>6.0681508236565165</v>
+        <v>2.1831379232891024</v>
       </c>
       <c r="AF8">
-        <v>18.613445117226497</v>
+        <v>29.117454579505626</v>
       </c>
       <c r="AG8">
-        <v>5236.0613019879456</v>
+        <v>3490.7075122213723</v>
       </c>
       <c r="AH8">
-        <v>1183.0229487654513</v>
+        <v>1521.0329340330593</v>
       </c>
       <c r="AI8">
-        <v>1183.0229487654513</v>
+        <v>1521.0329340330593</v>
       </c>
       <c r="AJ8">
         <v>15.833151307774594</v>
@@ -8758,136 +8758,136 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-4.5991235066563805</v>
+        <v>-4.59912261662489</v>
       </c>
       <c r="AO8">
-        <v>-2.6159741985822027</v>
+        <v>-2.6161516525076762</v>
       </c>
       <c r="AP8">
-        <v>-0.4801955165676054</v>
+        <v>-0.48020404086215379</v>
       </c>
       <c r="AQ8">
-        <v>-1.9890528816294022</v>
+        <v>-1.98881947512774</v>
       </c>
       <c r="AR8">
-        <v>211.27432780301692</v>
+        <v>140.7744945716581</v>
       </c>
       <c r="AS8">
-        <v>85.909681024916253</v>
+        <v>110.82630827787484</v>
       </c>
       <c r="AT8">
-        <v>-6.9382823462709311</v>
+        <v>-3.9540748855092409</v>
       </c>
       <c r="AU8">
-        <v>-1.6860015647338058</v>
+        <v>-0.30197042950456227</v>
       </c>
       <c r="AV8">
-        <v>-2.0626529999863479</v>
+        <v>-1.1754904193470583</v>
       </c>
       <c r="AW8">
-        <v>1.1755617934270168</v>
+        <v>0.21054838091230152</v>
       </c>
       <c r="AX8">
-        <v>0.001028517024686146</v>
+        <v>0.00058614411084264239</v>
       </c>
       <c r="AY8">
-        <v>1.2634787155734835</v>
+        <v>0.22629469532659405</v>
       </c>
       <c r="AZ8">
-        <v>-0.0034786769171293104</v>
+        <v>-0.0019824717914822946</v>
       </c>
       <c r="BA8">
-        <v>2.1093753876669568</v>
+        <v>0.37779857689557433</v>
       </c>
       <c r="BB8">
-        <v>-2.2732391232311175</v>
+        <v>-1.8959230400539606</v>
       </c>
       <c r="BC8">
-        <v>-0.86503643192491142</v>
+        <v>-0.716413440289425</v>
       </c>
       <c r="BD8">
-        <v>-0.0061788201387205019</v>
+        <v>-0.0035212295702111776</v>
       </c>
       <c r="BE8">
-        <v>-0.28964543688641636</v>
+        <v>-0.051876156295643829</v>
       </c>
       <c r="BF8">
-        <v>-0.029245484782615745</v>
+        <v>-0.025013263808372436</v>
       </c>
       <c r="BG8">
-        <v>-3.3715110268237516</v>
+        <v>-0.46808521461866903</v>
       </c>
       <c r="BH8">
-        <v>73.485479009641963</v>
+        <v>72.77306939643023</v>
       </c>
       <c r="BI8">
-        <v>36.546177783640012</v>
+        <v>32.703860562496374</v>
       </c>
       <c r="BJ8">
-        <v>-0.0030428090350113584</v>
+        <v>-0.0017199459551605826</v>
       </c>
       <c r="BK8">
-        <v>2.2711207361155079</v>
+        <v>0.39454463339787649</v>
       </c>
       <c r="BL8">
-        <v>-0.0019749312748272461</v>
+        <v>-0.0011469722028128152</v>
       </c>
       <c r="BM8">
-        <v>0.94225983294869176</v>
+        <v>0.19564147334911491</v>
       </c>
       <c r="BN8">
-        <v>0.043097441102601927</v>
+        <v>0.023896176242116967</v>
       </c>
       <c r="BO8">
-        <v>0.37400767398921192</v>
+        <v>0.5438625590815781</v>
       </c>
       <c r="BP8">
-        <v>-0.81539170518308923</v>
+        <v>-0.81719513332270477</v>
       </c>
       <c r="BQ8">
-        <v>1.2868797264841811</v>
+        <v>0.93421095118256925</v>
       </c>
       <c r="BR8">
-        <v>-23.413234138885013</v>
+        <v>38.70444688791445</v>
       </c>
       <c r="BS8">
-        <v>-1.0537257780145284</v>
+        <v>-0.92464472246677731</v>
       </c>
       <c r="BT8">
-        <v>0.0068456401821876045</v>
+        <v>-0.249818172140225</v>
       </c>
       <c r="BU8">
-        <v>1.5831695851505148</v>
+        <v>1.853469363228011</v>
       </c>
       <c r="BV8">
-        <v>14.774543258062614</v>
+        <v>14.766279195321026</v>
       </c>
       <c r="BW8">
-        <v>-2.6836489964011059</v>
+        <v>-2.7287541380779454</v>
       </c>
       <c r="BX8">
-        <v>-0.6455995612164982</v>
+        <v>-0.7362698116168892</v>
       </c>
       <c r="BY8">
-        <v>193.1650891130906</v>
+        <v>25.146841354350119</v>
       </c>
       <c r="BZ8">
-        <v>0.51954849491655042</v>
+        <v>0.74118217499376671</v>
       </c>
       <c r="CA8">
-        <v>-339.21330923872767</v>
+        <v>-38.874210512159785</v>
       </c>
       <c r="CB8">
-        <v>3.1941815223387953</v>
+        <v>3.427613058196874</v>
       </c>
       <c r="CC8">
-        <v>193.19451011525203</v>
+        <v>25.151197463918056</v>
       </c>
       <c r="CD8">
-        <v>46.9603868631014</v>
+        <v>43.762232624620935</v>
       </c>
       <c r="CE8">
-        <v>0.77641957791924865</v>
+        <v>5.9639307518137148</v>
       </c>
     </row>
     <row r="9" spans="1:83">
@@ -8895,28 +8895,28 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>215.63047275898356</v>
+        <v>219.2319142121199</v>
       </c>
       <c r="C9">
-        <v>41.41613193467871</v>
+        <v>27.610754623119135</v>
       </c>
       <c r="D9">
-        <v>0.073953981035796354</v>
+        <v>0.049302654023864217</v>
       </c>
       <c r="E9">
-        <v>1.7856322544180645</v>
+        <v>1.7856322544180643</v>
       </c>
       <c r="F9">
-        <v>41.41613193467871</v>
+        <v>27.610754623119135</v>
       </c>
       <c r="G9">
-        <v>36.202163938314875</v>
+        <v>46.545639349261982</v>
       </c>
       <c r="H9">
-        <v>0.073931717080437984</v>
+        <v>0.049447221357027053</v>
       </c>
       <c r="I9">
-        <v>1.7850946871871729</v>
+        <v>1.7908681610470627</v>
       </c>
       <c r="J9">
         <v>1735.796849693681</v>
@@ -8970,31 +8970,31 @@
         <v>12.009582891914787</v>
       </c>
       <c r="AA9">
-        <v>0.40789667438134813</v>
+        <v>0.407896674381348</v>
       </c>
       <c r="AB9">
-        <v>1.8581003974265979</v>
+        <v>1.8582200948224295</v>
       </c>
       <c r="AC9">
-        <v>0.17028937533427294</v>
+        <v>0.17019841723856033</v>
       </c>
       <c r="AD9">
-        <v>1.2657973077624807</v>
+        <v>1.268098251500243</v>
       </c>
       <c r="AE9">
-        <v>4.9277391986541765</v>
+        <v>1.6997974380721614</v>
       </c>
       <c r="AF9">
-        <v>19.047773638292544</v>
+        <v>30.872891560995335</v>
       </c>
       <c r="AG9">
-        <v>4454.6729874187295</v>
+        <v>2969.7819776156821</v>
       </c>
       <c r="AH9">
-        <v>1459.6425752490816</v>
+        <v>1876.683473453279</v>
       </c>
       <c r="AI9">
-        <v>1459.6425752490816</v>
+        <v>1876.683473453279</v>
       </c>
       <c r="AJ9">
         <v>15.206192632496732</v>
@@ -9009,136 +9009,136 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>-4.4165731158029331</v>
+        <v>-4.41657248908978</v>
       </c>
       <c r="AO9">
-        <v>-2.7428652909653217</v>
+        <v>-2.7429401416030594</v>
       </c>
       <c r="AP9">
-        <v>-0.39477189493915416</v>
+        <v>-0.39477890632908719</v>
       </c>
       <c r="AQ9">
-        <v>-1.7979477848030236</v>
+        <v>-1.7979573005852965</v>
       </c>
       <c r="AR9">
-        <v>187.15655681538459</v>
+        <v>124.70450422599954</v>
       </c>
       <c r="AS9">
-        <v>100.59083741462813</v>
+        <v>129.76516335388061</v>
       </c>
       <c r="AT9">
-        <v>-6.1852746281982078</v>
+        <v>-5.28885801541586</v>
       </c>
       <c r="AU9">
-        <v>-1.8001789168724807</v>
+        <v>-0.37854229560402625</v>
       </c>
       <c r="AV9">
-        <v>-1.7918094678191217</v>
+        <v>-1.5321269362511329</v>
       </c>
       <c r="AW9">
-        <v>1.2008092635230179</v>
+        <v>0.25250662083427944</v>
       </c>
       <c r="AX9">
-        <v>0.00040957785864142592</v>
+        <v>0.00035021874869339321</v>
       </c>
       <c r="AY9">
-        <v>1.1179185448677349</v>
+        <v>0.23507632952826207</v>
       </c>
       <c r="AZ9">
-        <v>-0.0014191978509946115</v>
+        <v>-0.0012135170030243777</v>
       </c>
       <c r="BA9">
-        <v>1.9294661795932326</v>
+        <v>0.40572886954063292</v>
       </c>
       <c r="BB9">
-        <v>-2.0736325889438749</v>
+        <v>-2.596602005300523</v>
       </c>
       <c r="BC9">
-        <v>-0.75762520372065179</v>
+        <v>-0.94241917914275042</v>
       </c>
       <c r="BD9">
-        <v>-0.0037124612075371505</v>
+        <v>-0.0031743982840665868</v>
       </c>
       <c r="BE9">
-        <v>-0.27038130352090578</v>
+        <v>-0.056855599606024043</v>
       </c>
       <c r="BF9">
-        <v>-0.019836126880658556</v>
+        <v>-0.025455361887439819</v>
       </c>
       <c r="BG9">
-        <v>-2.6879317288752023</v>
+        <v>-0.43814224200507496</v>
       </c>
       <c r="BH9">
-        <v>74.399689251223563</v>
+        <v>74.248250945411769</v>
       </c>
       <c r="BI9">
-        <v>40.771215503901537</v>
+        <v>37.901577239030409</v>
       </c>
       <c r="BJ9">
-        <v>-0.0012567704311980989</v>
+        <v>-0.0010728719137965228</v>
       </c>
       <c r="BK9">
-        <v>2.1066446981950655</v>
+        <v>0.4347330680553726</v>
       </c>
       <c r="BL9">
-        <v>-0.0007761473093576784</v>
+        <v>-0.00066650022141948311</v>
       </c>
       <c r="BM9">
-        <v>0.73118378450285659</v>
+        <v>0.17573831631822007</v>
       </c>
       <c r="BN9">
-        <v>0.039141967596028837</v>
+        <v>0.020372655382319724</v>
       </c>
       <c r="BO9">
-        <v>0.25950911596155429</v>
+        <v>0.38101870229970208</v>
       </c>
       <c r="BP9">
-        <v>-1.5221144655414456</v>
+        <v>-0.81782743511239753</v>
       </c>
       <c r="BQ9">
-        <v>1.2539192721431882</v>
+        <v>0.90120297764534751</v>
       </c>
       <c r="BR9">
-        <v>-21.294852117695758</v>
+        <v>38.705330392894162</v>
       </c>
       <c r="BS9">
-        <v>-1.0225288045994192</v>
+        <v>-0.791447480985469</v>
       </c>
       <c r="BT9">
-        <v>-0.0042719896789338114</v>
+        <v>-0.26423499476949081</v>
       </c>
       <c r="BU9">
-        <v>1.4967153782046598</v>
+        <v>1.7668194068409666</v>
       </c>
       <c r="BV9">
-        <v>14.797617802809784</v>
+        <v>14.792637017265662</v>
       </c>
       <c r="BW9">
-        <v>-2.2873472826250421</v>
+        <v>-2.31943998271572</v>
       </c>
       <c r="BX9">
-        <v>-0.320064728179762</v>
+        <v>-0.56900153353684935</v>
       </c>
       <c r="BY9">
-        <v>165.53579111028014</v>
+        <v>24.904007823871311</v>
       </c>
       <c r="BZ9">
-        <v>0.25707546207179915</v>
+        <v>0.50822945252221152</v>
       </c>
       <c r="CA9">
-        <v>-260.3885398751703</v>
+        <v>-34.046154343945489</v>
       </c>
       <c r="CB9">
-        <v>2.0422664837023685</v>
+        <v>2.29923852876746</v>
       </c>
       <c r="CC9">
-        <v>165.55761267753712</v>
+        <v>24.907861696975772</v>
       </c>
       <c r="CD9">
-        <v>73.4478096747047</v>
+        <v>65.238990267099283</v>
       </c>
       <c r="CE9">
-        <v>0.90602901053037477</v>
+        <v>6.0221949930857575</v>
       </c>
     </row>
     <row r="10" spans="1:83">
@@ -9146,28 +9146,28 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>214.37176091245323</v>
+        <v>217.7733157987233</v>
       </c>
       <c r="C10">
-        <v>39.98765244367096</v>
+        <v>26.658434962447302</v>
       </c>
       <c r="D10">
-        <v>0.047993398470801682</v>
+        <v>0.031995598980534452</v>
       </c>
       <c r="E10">
         <v>1.20020545188063</v>
       </c>
       <c r="F10">
-        <v>39.98765244367096</v>
+        <v>26.658434962447302</v>
       </c>
       <c r="G10">
-        <v>43.127311408876366</v>
+        <v>55.449400382841034</v>
       </c>
       <c r="H10">
-        <v>0.047984531469516527</v>
+        <v>0.032063833614075068</v>
       </c>
       <c r="I10">
-        <v>1.1999837083987477</v>
+        <v>1.2027650407550983</v>
       </c>
       <c r="J10">
         <v>2091.1827059310322</v>
@@ -9215,37 +9215,37 @@
         <v>40.225256791052963</v>
       </c>
       <c r="Y10">
-        <v>19.280220912219509</v>
+        <v>19.280220912219505</v>
       </c>
       <c r="Z10">
         <v>13.108012627134054</v>
       </c>
       <c r="AA10">
-        <v>0.34933674039182228</v>
+        <v>0.34933674039182205</v>
       </c>
       <c r="AB10">
-        <v>1.7850606373717</v>
+        <v>1.7851759438413937</v>
       </c>
       <c r="AC10">
-        <v>0.14842719828313675</v>
+        <v>0.14834792568639738</v>
       </c>
       <c r="AD10">
-        <v>1.1155471588685226</v>
+        <v>1.1175716522209696</v>
       </c>
       <c r="AE10">
-        <v>4.4483243769022689</v>
+        <v>1.4877635224049202</v>
       </c>
       <c r="AF10">
-        <v>23.464465838368149</v>
+        <v>39.233652591619595</v>
       </c>
       <c r="AG10">
-        <v>4152.6722368081655</v>
+        <v>2768.4481479600695</v>
       </c>
       <c r="AH10">
-        <v>2071.2655925345794</v>
+        <v>2663.0559384489129</v>
       </c>
       <c r="AI10">
-        <v>2071.2655925345794</v>
+        <v>2663.0559384489129</v>
       </c>
       <c r="AJ10">
         <v>14.9416539703337</v>
@@ -9260,136 +9260,136 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>-4.3394573549611541</v>
+        <v>-4.3394568871777883</v>
       </c>
       <c r="AO10">
-        <v>-2.9838483172862023</v>
+        <v>-2.98391159678344</v>
       </c>
       <c r="AP10">
-        <v>-0.33809633521454507</v>
+        <v>-0.3381023391477726</v>
       </c>
       <c r="AQ10">
-        <v>-1.7272962490983193</v>
+        <v>-1.7273061010366044</v>
       </c>
       <c r="AR10">
-        <v>177.55740721643829</v>
+        <v>118.30848573184662</v>
       </c>
       <c r="AS10">
-        <v>130.79263511265259</v>
+        <v>168.72784701355838</v>
       </c>
       <c r="AT10">
-        <v>-6.5547049692931125</v>
+        <v>-6.8020523266249269</v>
       </c>
       <c r="AU10">
-        <v>-1.9984907636066205</v>
+        <v>-0.45269680280591956</v>
       </c>
       <c r="AV10">
-        <v>-1.8634119795596538</v>
+        <v>-1.933729412750584</v>
       </c>
       <c r="AW10">
-        <v>1.2706653329585342</v>
+        <v>0.2878302687917122</v>
       </c>
       <c r="AX10">
-        <v>0.00019631581063329648</v>
+        <v>0.00020372395443077931</v>
       </c>
       <c r="AY10">
-        <v>1.0653339563498276</v>
+        <v>0.24131874149360741</v>
       </c>
       <c r="AZ10">
-        <v>-0.00069236226283028843</v>
+        <v>-0.000718489140672941</v>
       </c>
       <c r="BA10">
-        <v>1.9144088012545486</v>
+        <v>0.43365061243887559</v>
       </c>
       <c r="BB10">
-        <v>-2.1799117211648422</v>
+        <v>-3.3144368655268539</v>
       </c>
       <c r="BC10">
-        <v>-0.77405647583826909</v>
+        <v>-1.1694036386768334</v>
       </c>
       <c r="BD10">
-        <v>-0.0027005739162064006</v>
+        <v>-0.0028024635565684773</v>
       </c>
       <c r="BE10">
-        <v>-0.28216494673320847</v>
+        <v>-0.0639154460057688</v>
       </c>
       <c r="BF10">
-        <v>-0.015209581839153939</v>
+        <v>-0.023687764569317805</v>
       </c>
       <c r="BG10">
-        <v>-2.1573458359499971</v>
+        <v>-0.378807927304571</v>
       </c>
       <c r="BH10">
-        <v>75.327949036391075</v>
+        <v>75.3481654679783</v>
       </c>
       <c r="BI10">
-        <v>44.203363171244355</v>
+        <v>41.571048467152742</v>
       </c>
       <c r="BJ10">
-        <v>-0.00062006125179452423</v>
+        <v>-0.00064359349976721386</v>
       </c>
       <c r="BK10">
-        <v>2.0984451843233325</v>
+        <v>0.46828674092441819</v>
       </c>
       <c r="BL10">
-        <v>-0.00036527995362337269</v>
+        <v>-0.0003788370387531355</v>
       </c>
       <c r="BM10">
-        <v>0.62962314543151154</v>
+        <v>0.16430190789840896</v>
       </c>
       <c r="BN10">
-        <v>0.036156186314377357</v>
+        <v>0.018124286328452206</v>
       </c>
       <c r="BO10">
-        <v>0.19475064142787044</v>
+        <v>0.29616106478003362</v>
       </c>
       <c r="BP10">
-        <v>-1.522736322732096</v>
+        <v>-0.81827862469964674</v>
       </c>
       <c r="BQ10">
-        <v>1.2289846760020931</v>
+        <v>0.8760053509800575</v>
       </c>
       <c r="BR10">
-        <v>-19.882579205751345</v>
+        <v>-24.822535736834098</v>
       </c>
       <c r="BS10">
-        <v>-1.0052169397776574</v>
+        <v>-0.73040636649257384</v>
       </c>
       <c r="BT10">
-        <v>-0.0113469155291452</v>
+        <v>-0.27303516056394067</v>
       </c>
       <c r="BU10">
-        <v>1.432928807213947</v>
+        <v>1.7031598258344791</v>
       </c>
       <c r="BV10">
-        <v>14.811282527091459</v>
+        <v>14.807635977806648</v>
       </c>
       <c r="BW10">
-        <v>-2.0050969435195389</v>
+        <v>-2.0319397470625966</v>
       </c>
       <c r="BX10">
-        <v>-0.1714446919491277</v>
+        <v>-0.37906423434390629</v>
       </c>
       <c r="BY10">
-        <v>128.15137195679867</v>
+        <v>20.345494678635397</v>
       </c>
       <c r="BZ10">
-        <v>0.13837037076334632</v>
+        <v>0.31257067282934103</v>
       </c>
       <c r="CA10">
-        <v>-183.81969063085546</v>
+        <v>-25.166498090349595</v>
       </c>
       <c r="CB10">
-        <v>1.3384405002051971</v>
+        <v>1.5155208461300533</v>
       </c>
       <c r="CC10">
-        <v>128.16952943451753</v>
+        <v>20.349020840427926</v>
       </c>
       <c r="CD10">
-        <v>112.07072707154589</v>
+        <v>98.975873794828587</v>
       </c>
       <c r="CE10">
-        <v>1.1703249646136507</v>
+        <v>7.3713620510914764</v>
       </c>
     </row>
     <row r="11" spans="1:83">
@@ -9397,28 +9397,28 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>213.29647024618566</v>
+        <v>216.52630919808175</v>
       </c>
       <c r="C11">
-        <v>39.1596734538681</v>
+        <v>26.1064489692454</v>
       </c>
       <c r="D11">
-        <v>0.13339709275082937</v>
+        <v>0.088931395167219568</v>
       </c>
       <c r="E11">
         <v>3.40649144860662</v>
       </c>
       <c r="F11">
-        <v>39.1596734538681</v>
+        <v>26.1064489692454</v>
       </c>
       <c r="G11">
-        <v>51.594007590389843</v>
+        <v>66.335152616215524</v>
       </c>
       <c r="H11">
-        <v>0.1333769030499955</v>
+        <v>0.089285878981590072</v>
       </c>
       <c r="I11">
-        <v>3.4059758748274453</v>
+        <v>3.4200698489010497</v>
       </c>
       <c r="J11">
         <v>2448.1835606991444</v>
@@ -9469,34 +9469,34 @@
         <v>19.079569977012866</v>
       </c>
       <c r="Z11">
-        <v>14.337066192263846</v>
+        <v>14.337066192263842</v>
       </c>
       <c r="AA11">
         <v>0.33805783428013331</v>
       </c>
       <c r="AB11">
-        <v>1.8276441207359193</v>
+        <v>1.82776231475923</v>
       </c>
       <c r="AC11">
-        <v>0.14514598943110932</v>
+        <v>0.14506847036667978</v>
       </c>
       <c r="AD11">
-        <v>1.0448029503606693</v>
+        <v>1.0466977190041245</v>
       </c>
       <c r="AE11">
-        <v>4.2467460001130908</v>
+        <v>1.4139554126233485</v>
       </c>
       <c r="AF11">
-        <v>31.388063983466676</v>
+        <v>53.333832605502089</v>
       </c>
       <c r="AG11">
-        <v>3982.4821036149096</v>
+        <v>2654.9880599865096</v>
       </c>
       <c r="AH11">
-        <v>2964.214740867742</v>
+        <v>3811.13345869231</v>
       </c>
       <c r="AI11">
-        <v>2964.214740867742</v>
+        <v>3811.13345869231</v>
       </c>
       <c r="AJ11">
         <v>14.786154878475196</v>
@@ -9511,136 +9511,136 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>-4.2942577147663323</v>
+        <v>-4.2942572720995136</v>
       </c>
       <c r="AO11">
-        <v>-3.2590138372093072</v>
+        <v>-3.2590744791361508</v>
       </c>
       <c r="AP11">
-        <v>-0.32718035827239689</v>
+        <v>-0.32718616824350016</v>
       </c>
       <c r="AQ11">
-        <v>-1.7685125058834885</v>
+        <v>-1.7685229037886052</v>
       </c>
       <c r="AR11">
-        <v>172.07128874621429</v>
+        <v>114.65302393512636</v>
       </c>
       <c r="AS11">
-        <v>171.13942984621221</v>
+        <v>220.7776883883835</v>
       </c>
       <c r="AT11">
-        <v>-6.5680080035944854</v>
+        <v>-7.3722538815856469</v>
       </c>
       <c r="AU11">
-        <v>-2.3014667588674231</v>
+        <v>-0.70375429816607138</v>
       </c>
       <c r="AV11">
-        <v>-1.8117776078088019</v>
+        <v>-2.0336279271323288</v>
       </c>
       <c r="AW11">
-        <v>1.4473773485812063</v>
+        <v>0.44258646196284818</v>
       </c>
       <c r="AX11">
-        <v>0.00050860623701856514</v>
+        <v>0.00057088455175553234</v>
       </c>
       <c r="AY11">
-        <v>1.0785310291904897</v>
+        <v>0.32979874446320756</v>
       </c>
       <c r="AZ11">
-        <v>-0.0018519058882454163</v>
+        <v>-0.0020786698745611813</v>
       </c>
       <c r="BA11">
-        <v>1.9465309718755137</v>
+        <v>0.59522021454044638</v>
       </c>
       <c r="BB11">
-        <v>-1.2135508497277612</v>
+        <v>-1.9958093233619179</v>
       </c>
       <c r="BC11">
-        <v>-0.41362373906476363</v>
+        <v>-0.67618154874624226</v>
       </c>
       <c r="BD11">
-        <v>-0.0042350801054896886</v>
+        <v>-0.0047536296121234375</v>
       </c>
       <c r="BE11">
-        <v>-0.321573992777328</v>
+        <v>-0.098331954039918013</v>
       </c>
       <c r="BF11">
-        <v>-0.024612357682378686</v>
+        <v>-0.041461005117607405</v>
       </c>
       <c r="BG11">
-        <v>-1.8790175535018314</v>
+        <v>-0.44538900084385458</v>
       </c>
       <c r="BH11">
-        <v>75.834569291221086</v>
+        <v>75.885657927339679</v>
       </c>
       <c r="BI11">
-        <v>45.954730862334728</v>
+        <v>44.831165517933115</v>
       </c>
       <c r="BJ11">
-        <v>-0.0016711279642339109</v>
+        <v>-0.0018767022793145559</v>
       </c>
       <c r="BK11">
-        <v>2.148971770450447</v>
+        <v>0.6535312958198205</v>
       </c>
       <c r="BL11">
-        <v>-0.00094634404441918145</v>
+        <v>-0.0010605499392564513</v>
       </c>
       <c r="BM11">
-        <v>0.57804181094830831</v>
+        <v>0.18960791394651549</v>
       </c>
       <c r="BN11">
-        <v>0.034599066372861954</v>
+        <v>0.01724374149711665</v>
       </c>
       <c r="BO11">
-        <v>0.16319425536793861</v>
+        <v>0.23262637487167365</v>
       </c>
       <c r="BP11">
-        <v>-1.5228515293848681</v>
+        <v>-0.81835279396350236</v>
       </c>
       <c r="BQ11">
-        <v>1.2252124128607111</v>
+        <v>0.872215315920957</v>
       </c>
       <c r="BR11">
-        <v>-19.882483846973482</v>
+        <v>-24.822463550671205</v>
       </c>
       <c r="BS11">
-        <v>-1.0035799873844364</v>
+        <v>-0.7254702489335223</v>
       </c>
       <c r="BT11">
-        <v>-0.014543292463706586</v>
+        <v>-0.27769260457250272</v>
       </c>
       <c r="BU11">
-        <v>1.4026535963037978</v>
+        <v>1.6728353204128588</v>
       </c>
       <c r="BV11">
-        <v>14.817083686486766</v>
+        <v>14.814739276594352</v>
       </c>
       <c r="BW11">
-        <v>-1.8721970124587302</v>
+        <v>-1.8907420041052641</v>
       </c>
       <c r="BX11">
-        <v>-0.48249259454178778</v>
+        <v>-1.1579931535857893</v>
       </c>
       <c r="BY11">
-        <v>96.0349769124192</v>
+        <v>20.512065508498534</v>
       </c>
       <c r="BZ11">
-        <v>0.39019201230766609</v>
+        <v>0.95298028573966409</v>
       </c>
       <c r="CA11">
-        <v>-131.06868187102995</v>
+        <v>-23.905439635259146</v>
       </c>
       <c r="CB11">
-        <v>3.7962476730933328</v>
+        <v>4.3732466766724389</v>
       </c>
       <c r="CC11">
-        <v>96.053357554721913</v>
+        <v>20.516900418606316</v>
       </c>
       <c r="CD11">
-        <v>32.40041498656349</v>
+        <v>28.125557301878409</v>
       </c>
       <c r="CE11">
-        <v>1.2805382667641418</v>
+        <v>5.9950576105762092</v>
       </c>
     </row>
   </sheetData>

--- a/src/nodes/HPC/compressor_blade_strength.xlsx
+++ b/src/nodes/HPC/compressor_blade_strength.xlsx
@@ -1,23 +1,313 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\projects\gte\src\nodes\HPC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="210" windowWidth="15135" windowHeight="6720"/>
+    <workbookView xWindow="600" yWindow="216" windowWidth="15132" windowHeight="6720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="T" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="92">
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>R0.rotor</t>
+  </si>
+  <si>
+    <t>area0.rotor</t>
+  </si>
+  <si>
+    <t>N0.rotor</t>
+  </si>
+  <si>
+    <t>σ0_z.rotor</t>
+  </si>
+  <si>
+    <t>area.rotor</t>
+  </si>
+  <si>
+    <t>area.stator</t>
+  </si>
+  <si>
+    <t>N.rotor</t>
+  </si>
+  <si>
+    <t>σ_z.rotor</t>
+  </si>
+  <si>
+    <t>P.1</t>
+  </si>
+  <si>
+    <t>P.2</t>
+  </si>
+  <si>
+    <t>P.3</t>
+  </si>
+  <si>
+    <t>ρ.1</t>
+  </si>
+  <si>
+    <t>ρ.2</t>
+  </si>
+  <si>
+    <t>ρ.3</t>
+  </si>
+  <si>
+    <t>c.a1</t>
+  </si>
+  <si>
+    <t>c.a2</t>
+  </si>
+  <si>
+    <t>c.a3</t>
+  </si>
+  <si>
+    <t>c.u1</t>
+  </si>
+  <si>
+    <t>c.u2</t>
+  </si>
+  <si>
+    <t>c.u3</t>
+  </si>
+  <si>
+    <t>x0.rotor</t>
+  </si>
+  <si>
+    <t>x0.stator</t>
+  </si>
+  <si>
+    <t>y0.rotor</t>
+  </si>
+  <si>
+    <t>y0.stator</t>
+  </si>
+  <si>
+    <t>α_major.rotor</t>
+  </si>
+  <si>
+    <t>α_major.stator</t>
+  </si>
+  <si>
+    <t>Ju.rotor</t>
+  </si>
+  <si>
+    <t>Ju.stator</t>
+  </si>
+  <si>
+    <t>Jv.rotor</t>
+  </si>
+  <si>
+    <t>Jv.stator</t>
+  </si>
+  <si>
+    <t>CPx.rotor</t>
+  </si>
+  <si>
+    <t>CPx.stator</t>
+  </si>
+  <si>
+    <t>CPy.rotor</t>
+  </si>
+  <si>
+    <t>CPy.stator</t>
+  </si>
+  <si>
+    <t>CPx.rotor.axis</t>
+  </si>
+  <si>
+    <t>CPx.stator.axis</t>
+  </si>
+  <si>
+    <t>CPy.rotor.axis</t>
+  </si>
+  <si>
+    <t>CPy.stator.axis</t>
+  </si>
+  <si>
+    <t>Wp.rotor</t>
+  </si>
+  <si>
+    <t>Wp.stator</t>
+  </si>
+  <si>
+    <t>qx.rotor</t>
+  </si>
+  <si>
+    <t>qx.stator</t>
+  </si>
+  <si>
+    <t>qy.rotor</t>
+  </si>
+  <si>
+    <t>qy.stator</t>
+  </si>
+  <si>
+    <t>Mx.rotor</t>
+  </si>
+  <si>
+    <t>Mx.stator</t>
+  </si>
+  <si>
+    <t>My.rotor</t>
+  </si>
+  <si>
+    <t>My.stator</t>
+  </si>
+  <si>
+    <t>shift_x.rotor</t>
+  </si>
+  <si>
+    <t>shift_y.rotor</t>
+  </si>
+  <si>
+    <t>Mτ.rotor</t>
+  </si>
+  <si>
+    <t>Mτ.stator</t>
+  </si>
+  <si>
+    <t>τ.rotor</t>
+  </si>
+  <si>
+    <t>τ.stator</t>
+  </si>
+  <si>
+    <t>φ_uv.rotor</t>
+  </si>
+  <si>
+    <t>φ_uv.stator</t>
+  </si>
+  <si>
+    <t>Mu.rotor</t>
+  </si>
+  <si>
+    <t>Mu.stator</t>
+  </si>
+  <si>
+    <t>Mv.rotor</t>
+  </si>
+  <si>
+    <t>Mv.stator</t>
+  </si>
+  <si>
+    <t>φ_neutral.rotor</t>
+  </si>
+  <si>
+    <t>φ_neutral.stator</t>
+  </si>
+  <si>
+    <t>u_u.rotor</t>
+  </si>
+  <si>
+    <t>v_u.rotor</t>
+  </si>
+  <si>
+    <t>u_l.rotor</t>
+  </si>
+  <si>
+    <t>v_l.rotor</t>
+  </si>
+  <si>
+    <t>u_u.stator</t>
+  </si>
+  <si>
+    <t>v_u.stator</t>
+  </si>
+  <si>
+    <t>u_l.stator</t>
+  </si>
+  <si>
+    <t>v_l.stator</t>
+  </si>
+  <si>
+    <t>σ_p.rotor</t>
+  </si>
+  <si>
+    <t>σ_p.stator</t>
+  </si>
+  <si>
+    <t>σ_n.rotor</t>
+  </si>
+  <si>
+    <t>σ_n.stator</t>
+  </si>
+  <si>
+    <t>σ.rotor</t>
+  </si>
+  <si>
+    <t>σ.stator</t>
+  </si>
+  <si>
+    <t>safety.rotor</t>
+  </si>
+  <si>
+    <t>safety.stator</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
+    <t>мм^2</t>
+  </si>
+  <si>
+    <t>кН</t>
+  </si>
+  <si>
+    <t>МПа</t>
+  </si>
+  <si>
+    <t>кПа</t>
+  </si>
+  <si>
+    <t>кг/м^3</t>
+  </si>
+  <si>
+    <t>м/с</t>
+  </si>
+  <si>
+    <t>град</t>
+  </si>
+  <si>
+    <t>мм^4</t>
+  </si>
+  <si>
+    <t>мм^3</t>
+  </si>
+  <si>
+    <t>кН/м</t>
+  </si>
+  <si>
+    <t>Н*м</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -45,21 +335,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -97,9 +396,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -131,9 +430,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -165,9 +465,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -340,845 +641,513 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CE11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:83">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>R0.rotor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>area0.rotor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>N0.rotor</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>σ0_z.rotor</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>area.rotor</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>area.stator</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>N.rotor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>σ_z.rotor</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>P.2</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>P.3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ρ.1</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ρ.2</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ρ.3</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ρ.1</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ρ.2</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ρ.3</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>c.a1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>c.a2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>c.a3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>c.u1</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>c.u2</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>c.u3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>x0.rotor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>x0.stator</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>y0.rotor</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>y0.stator</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>α_major.rotor</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>α_major.stator</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Ju.rotor</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Ju.stator</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Jv.rotor</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Jv.stator</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Jv.stator</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>CPx.rotor</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>CPx.stator</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>CPy.rotor</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>CPy.stator</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>CPx.rotor.axis</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>CPx.stator.axis</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>CPy.rotor.axis</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>CPy.stator.axis</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Wp.rotor</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Wp.stator</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>qx.rotor</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>qx.stator</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>qy.rotor</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>qy.stator</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Mx.rotor</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Mx.stator</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>My.rotor</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>My.stator</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>shift_x.rotor</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>shift_y.rotor</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Mτ.rotor</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Mτ.stator</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>τ.rotor</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>τ.stator</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>φ_uv.rotor</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>φ_uv.stator</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>Mu.rotor</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>Mu.stator</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>Mv.rotor</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>Mv.stator</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>φ_neutral.rotor</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>φ_neutral.stator</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>u_u.rotor</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>v_u.rotor</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>u_l.rotor</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>v_l.rotor</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>u_u.stator</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>v_u.stator</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>u_l.stator</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>v_l.stator</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>σ_p.rotor</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>σ_p.stator</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>σ_n.rotor</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>σ_n.stator</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>σ.rotor</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>σ.stator</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>safety.rotor</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>safety.stator</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:83">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>кН</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>кН</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>мм^3</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>мм^3</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:83">
+    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>79</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1267,7 +1236,7 @@
         <v>1.0420027363837927</v>
       </c>
       <c r="AD3">
-        <v>1.1692051981276797</v>
+        <v>1.1692051981276796</v>
       </c>
       <c r="AE3">
         <v>756.40196267309841</v>
@@ -1330,25 +1299,25 @@
         <v>4.659685765198982</v>
       </c>
       <c r="AY3">
-        <v>0.0011426149378461264</v>
+        <v>1.1426149378461264E-3</v>
       </c>
       <c r="AZ3">
         <v>-11.362976052056272</v>
       </c>
       <c r="BA3">
-        <v>0.0014305195632442697</v>
+        <v>1.4305195632442697E-3</v>
       </c>
       <c r="BB3">
-        <v>-0.019335200224522855</v>
+        <v>-1.9335200224522855E-2</v>
       </c>
       <c r="BC3">
-        <v>-0.011597797617609373</v>
+        <v>-1.1597797617609373E-2</v>
       </c>
       <c r="BD3">
         <v>-0.46192118681762528</v>
       </c>
       <c r="BE3">
-        <v>0.0040573887286063292</v>
+        <v>4.0573887286063292E-3</v>
       </c>
       <c r="BF3">
         <v>-0.33443347452048428</v>
@@ -1363,22 +1332,22 @@
         <v>38.895699801144687</v>
       </c>
       <c r="BJ3">
-        <v>-4.50655524166095</v>
+        <v>-4.5065552416609496</v>
       </c>
       <c r="BK3">
-        <v>0.0017875159769749876</v>
+        <v>1.7875159769749876E-3</v>
       </c>
       <c r="BL3">
         <v>-11.424572466567867</v>
       </c>
       <c r="BM3">
-        <v>0.00039590623772913641</v>
+        <v>3.9590623772913641E-4</v>
       </c>
       <c r="BN3">
         <v>2.7046860185524357</v>
       </c>
       <c r="BO3">
-        <v>0.097865931250574148</v>
+        <v>9.7865931250574148E-2</v>
       </c>
       <c r="BP3">
         <v>-2.5469371287826226</v>
@@ -1429,7 +1398,7 @@
         <v>352.11492627237953</v>
       </c>
     </row>
-    <row r="4" spans="1:83">
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1446,7 +1415,7 @@
         <v>89.46921287755346</v>
       </c>
       <c r="F4">
-        <v>196.21544539296986</v>
+        <v>196.21544539296985</v>
       </c>
       <c r="G4">
         <v>10.99029793601327</v>
@@ -1581,31 +1550,31 @@
         <v>3.2059138493943506</v>
       </c>
       <c r="AY4">
-        <v>0.00066531327344706182</v>
+        <v>6.6531327344706182E-4</v>
       </c>
       <c r="AZ4">
-        <v>-8.17473484373679</v>
+        <v>-8.1747348437367897</v>
       </c>
       <c r="BA4">
-        <v>0.000992081616465926</v>
+        <v>9.9208161646592596E-4</v>
       </c>
       <c r="BB4">
-        <v>-0.018664052750750705</v>
+        <v>-1.8664052750750705E-2</v>
       </c>
       <c r="BC4">
-        <v>-0.010029318791238301</v>
+        <v>-1.0029318791238301E-2</v>
       </c>
       <c r="BD4">
         <v>-0.28014511626728472</v>
       </c>
       <c r="BE4">
-        <v>0.0034324429098657977</v>
+        <v>3.4324429098657977E-3</v>
       </c>
       <c r="BF4">
         <v>-0.27695669911034249</v>
       </c>
       <c r="BG4">
-        <v>0.13413679185833941</v>
+        <v>0.1341367918583394</v>
       </c>
       <c r="BH4">
         <v>49.810404176997409</v>
@@ -1617,13 +1586,13 @@
         <v>-4.1759509802967028</v>
       </c>
       <c r="BK4">
-        <v>0.001155445846783711</v>
+        <v>1.155445846783711E-3</v>
       </c>
       <c r="BL4">
         <v>-7.7243515446477371</v>
       </c>
       <c r="BM4">
-        <v>0.000303005908696122</v>
+        <v>3.03005908696122E-4</v>
       </c>
       <c r="BN4">
         <v>1.825065847400887</v>
@@ -1680,7 +1649,7 @@
         <v>562.92853639079169</v>
       </c>
     </row>
-    <row r="5" spans="1:83">
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1688,7 +1657,7 @@
         <v>232.5503088636367</v>
       </c>
       <c r="C5">
-        <v>154.13191914197302</v>
+        <v>154.13191914197301</v>
       </c>
       <c r="D5">
         <v>11.736983989613789</v>
@@ -1787,7 +1756,7 @@
         <v>260.89987793611488</v>
       </c>
       <c r="AJ5">
-        <v>15.182162276327365</v>
+        <v>15.182162276327364</v>
       </c>
       <c r="AK5">
         <v>7.4794004512165557</v>
@@ -1811,13 +1780,13 @@
         <v>-1.6704281981530393</v>
       </c>
       <c r="AR5">
-        <v>704.218381138802</v>
+        <v>704.21838113880199</v>
       </c>
       <c r="AS5">
         <v>22.275422424764045</v>
       </c>
       <c r="AT5">
-        <v>-1.62503942904441</v>
+        <v>-1.6250394290444099</v>
       </c>
       <c r="AU5">
         <v>-0.51647672518654286</v>
@@ -1847,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="BD5">
-        <v>-0.17959682165339611</v>
+        <v>-0.1795968216533961</v>
       </c>
       <c r="BE5">
         <v>0</v>
@@ -1895,7 +1864,7 @@
         <v>-3.6968475768887976</v>
       </c>
       <c r="BT5">
-        <v>-1.5638802210273644</v>
+        <v>-1.5638802210273643</v>
       </c>
       <c r="BU5">
         <v>10.23704747429775</v>
@@ -1928,10 +1897,10 @@
         <v>1.4470706940182541</v>
       </c>
       <c r="CE5">
-        <v>1E+307</v>
-      </c>
-    </row>
-    <row r="6" spans="1:83">
+        <v>9.9999999999999999E+306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1963,7 +1932,7 @@
         <v>807.93911464931659</v>
       </c>
       <c r="K6">
-        <v>940.540688691768</v>
+        <v>940.54068869176797</v>
       </c>
       <c r="L6">
         <v>1070.8013292006924</v>
@@ -2008,7 +1977,7 @@
         <v>17.898039585561644</v>
       </c>
       <c r="Z6">
-        <v>9.35538912409344</v>
+        <v>9.3553891240934401</v>
       </c>
       <c r="AA6">
         <v>1.6006930222828686</v>
@@ -2080,7 +2049,7 @@
         <v>0.35883141687050391</v>
       </c>
       <c r="AX6">
-        <v>1.7565005026210268</v>
+        <v>1.7565005026210267</v>
       </c>
       <c r="AY6">
         <v>0</v>
@@ -2146,7 +2115,7 @@
         <v>-3.2284041426901791</v>
       </c>
       <c r="BT6">
-        <v>-1.570421558155559</v>
+        <v>-1.5704215581555589</v>
       </c>
       <c r="BU6">
         <v>10.237404551945254</v>
@@ -2158,7 +2127,7 @@
         <v>-12.32703842153494</v>
       </c>
       <c r="BX6">
-        <v>-62.6286119138999</v>
+        <v>-62.628611913899903</v>
       </c>
       <c r="BY6">
         <v>0</v>
@@ -2179,10 +2148,10 @@
         <v>1.4570064945931158</v>
       </c>
       <c r="CE6">
-        <v>1E+307</v>
-      </c>
-    </row>
-    <row r="7" spans="1:83">
+        <v>9.9999999999999999E+306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2244,7 +2213,7 @@
         <v>74.41206790978012</v>
       </c>
       <c r="U7">
-        <v>71.9567859143798</v>
+        <v>71.956785914379793</v>
       </c>
       <c r="V7">
         <v>31.174308841948445</v>
@@ -2262,7 +2231,7 @@
         <v>9.3215394088520238</v>
       </c>
       <c r="AA7">
-        <v>1.3718023362564789</v>
+        <v>1.3718023362564788</v>
       </c>
       <c r="AB7">
         <v>1.7245067896635398</v>
@@ -2313,7 +2282,7 @@
         <v>-1.6688733081955107</v>
       </c>
       <c r="AR7">
-        <v>433.275897428434</v>
+        <v>433.27589742843401</v>
       </c>
       <c r="AS7">
         <v>20.069786171461484</v>
@@ -2430,10 +2399,10 @@
         <v>1.438216029712009</v>
       </c>
       <c r="CE7">
-        <v>1E+307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:83">
+        <v>9.9999999999999999E+306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2444,13 +2413,13 @@
         <v>99.191246351021576</v>
       </c>
       <c r="D8">
-        <v>5.20812659911914</v>
+        <v>5.2081265991191401</v>
       </c>
       <c r="E8">
         <v>52.505909449795929</v>
       </c>
       <c r="F8">
-        <v>99.1912463510215</v>
+        <v>99.191246351021505</v>
       </c>
       <c r="G8">
         <v>9.6991219736553038</v>
@@ -2489,7 +2458,7 @@
         <v>8.4720536189877187</v>
       </c>
       <c r="S8">
-        <v>71.9567859143798</v>
+        <v>71.956785914379793</v>
       </c>
       <c r="T8">
         <v>69.683684330696934</v>
@@ -2501,13 +2470,13 @@
         <v>30.955372728026859</v>
       </c>
       <c r="W8">
-        <v>203.636566984424</v>
+        <v>203.63656698442401</v>
       </c>
       <c r="X8">
         <v>38.990724275466178</v>
       </c>
       <c r="Y8">
-        <v>15.715830675392486</v>
+        <v>15.715830675392485</v>
       </c>
       <c r="Z8">
         <v>9.4954436717952113</v>
@@ -2606,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="BF8">
-        <v>-0.334853828786104</v>
+        <v>-0.33485382878610398</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2636,7 +2605,7 @@
         <v>90</v>
       </c>
       <c r="BP8">
-        <v>-1.6206879724752104</v>
+        <v>-1.6206879724752103</v>
       </c>
       <c r="BQ8">
         <v>3.5863620095457702</v>
@@ -2681,10 +2650,10 @@
         <v>1.0484335110225078</v>
       </c>
       <c r="CE8">
-        <v>1E+307</v>
-      </c>
-    </row>
-    <row r="9" spans="1:83">
+        <v>9.9999999999999999E+306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2743,7 +2712,7 @@
         <v>67.4504075580288</v>
       </c>
       <c r="T9">
-        <v>65.410451982381</v>
+        <v>65.410451982381005</v>
       </c>
       <c r="U9">
         <v>63.394673707930707</v>
@@ -2932,10 +2901,10 @@
         <v>0.9591370212469057</v>
       </c>
       <c r="CE9">
-        <v>1E+307</v>
-      </c>
-    </row>
-    <row r="10" spans="1:83">
+        <v>9.9999999999999999E+306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2952,7 +2921,7 @@
         <v>45.151974839257782</v>
       </c>
       <c r="F10">
-        <v>88.3356424791153</v>
+        <v>88.335642479115293</v>
       </c>
       <c r="G10">
         <v>12.835509347879874</v>
@@ -2970,7 +2939,7 @@
         <v>2281.0335685375717</v>
       </c>
       <c r="L10">
-        <v>2444.19558326151</v>
+        <v>2444.1955832615099</v>
       </c>
       <c r="M10">
         <v>9.6505326084551832</v>
@@ -3054,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>-3.34216549952355</v>
+        <v>-3.3421654995235501</v>
       </c>
       <c r="AO10">
         <v>-2.4843431793879445</v>
@@ -3072,10 +3041,10 @@
         <v>32.296292736522858</v>
       </c>
       <c r="AT10">
-        <v>-4.4143057421039194</v>
+        <v>-4.4143057421039193</v>
       </c>
       <c r="AU10">
-        <v>-0.545764715523972</v>
+        <v>-0.54576471552397199</v>
       </c>
       <c r="AV10">
         <v>-1.936597289945974</v>
@@ -3108,13 +3077,13 @@
         <v>0</v>
       </c>
       <c r="BF10">
-        <v>-0.655396307327547</v>
+        <v>-0.65539630732754695</v>
       </c>
       <c r="BG10">
         <v>0</v>
       </c>
       <c r="BH10">
-        <v>66.7844761499119</v>
+        <v>66.784476149911896</v>
       </c>
       <c r="BI10">
         <v>45.847999102542111</v>
@@ -3132,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="BN10">
-        <v>0.704182009239085</v>
+        <v>0.70418200923908503</v>
       </c>
       <c r="BO10">
         <v>90</v>
@@ -3153,7 +3122,7 @@
         <v>-1.1456216295590764</v>
       </c>
       <c r="BU10">
-        <v>10.217222828931361</v>
+        <v>10.21722282893136</v>
       </c>
       <c r="BV10">
         <v>-1.5669669917393649</v>
@@ -3162,7 +3131,7 @@
         <v>-12.350618387356004</v>
       </c>
       <c r="BX10">
-        <v>-184.442903715739</v>
+        <v>-184.44290371573899</v>
       </c>
       <c r="BY10">
         <v>0</v>
@@ -3183,10 +3152,10 @@
         <v>0.78677418898965024</v>
       </c>
       <c r="CE10">
-        <v>1E+307</v>
-      </c>
-    </row>
-    <row r="11" spans="1:83">
+        <v>9.9999999999999999E+306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3215,7 +3184,7 @@
         <v>82.406049098642484</v>
       </c>
       <c r="J11">
-        <v>2444.19558326151</v>
+        <v>2444.1955832615099</v>
       </c>
       <c r="K11">
         <v>2640.2670904993774</v>
@@ -3434,7 +3403,7 @@
         <v>0.52607153720938138</v>
       </c>
       <c r="CE11">
-        <v>1E+307</v>
+        <v>9.9999999999999999E+306</v>
       </c>
     </row>
   </sheetData>
@@ -3443,845 +3412,513 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CE11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:83">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>R0.rotor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>area0.rotor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>N0.rotor</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>σ0_z.rotor</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>area.rotor</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>area.stator</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>N.rotor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>σ_z.rotor</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>P.2</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>P.3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ρ.1</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ρ.2</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ρ.3</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ρ.1</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ρ.2</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ρ.3</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>c.a1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>c.a2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>c.a3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>c.u1</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>c.u2</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>c.u3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>x0.rotor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>x0.stator</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>y0.rotor</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>y0.stator</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>α_major.rotor</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>α_major.stator</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Ju.rotor</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Ju.stator</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Jv.rotor</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Jv.stator</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Jv.stator</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>CPx.rotor</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>CPx.stator</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>CPy.rotor</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>CPy.stator</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>CPx.rotor.axis</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>CPx.stator.axis</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>CPy.rotor.axis</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>CPy.stator.axis</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Wp.rotor</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Wp.stator</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>qx.rotor</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>qx.stator</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>qy.rotor</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>qy.stator</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Mx.rotor</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Mx.stator</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>My.rotor</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>My.stator</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>shift_x.rotor</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>shift_y.rotor</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Mτ.rotor</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Mτ.stator</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>τ.rotor</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>τ.stator</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>φ_uv.rotor</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>φ_uv.stator</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>Mu.rotor</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>Mu.stator</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>Mv.rotor</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>Mv.stator</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>φ_neutral.rotor</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>φ_neutral.stator</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>u_u.rotor</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>v_u.rotor</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>u_l.rotor</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>v_l.rotor</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>u_u.stator</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>v_u.stator</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>u_l.stator</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>v_l.stator</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>σ_p.rotor</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>σ_p.stator</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>σ_n.rotor</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>σ_n.stator</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>σ.rotor</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>σ.stator</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>safety.rotor</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>safety.stator</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:83">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>кН</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>кН</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>мм^3</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>мм^3</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:83">
+    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>79</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4289,7 +3926,7 @@
         <v>235.63216491241906</v>
       </c>
       <c r="C3">
-        <v>78.7380092777086</v>
+        <v>78.738009277708599</v>
       </c>
       <c r="D3">
         <v>8.1994120021517425</v>
@@ -4349,7 +3986,7 @@
         <v>41.59087659848727</v>
       </c>
       <c r="W3">
-        <v>175.93877646002756</v>
+        <v>175.93877646002755</v>
       </c>
       <c r="X3">
         <v>35.946915467752305</v>
@@ -4403,7 +4040,7 @@
         <v>-6.4318894171960626</v>
       </c>
       <c r="AO3">
-        <v>-2.57630029548506</v>
+        <v>-2.5763002954850598</v>
       </c>
       <c r="AP3">
         <v>-1.0444123660715117</v>
@@ -4448,10 +4085,10 @@
         <v>-0.29135826813007082</v>
       </c>
       <c r="BD3">
-        <v>-0.310942316137982</v>
+        <v>-0.31094231613798201</v>
       </c>
       <c r="BE3">
-        <v>-0.081841629186138617</v>
+        <v>-8.1841629186138617E-2</v>
       </c>
       <c r="BF3">
         <v>-0.44641803095182231</v>
@@ -4496,7 +4133,7 @@
         <v>-1.3308330628627341</v>
       </c>
       <c r="BT3">
-        <v>-0.014050038681906673</v>
+        <v>-1.4050038681906673E-2</v>
       </c>
       <c r="BU3">
         <v>1.2096431137820558</v>
@@ -4517,7 +4154,7 @@
         <v>63.679293447196471</v>
       </c>
       <c r="CA3">
-        <v>-132.36404522829506</v>
+        <v>-132.36404522829505</v>
       </c>
       <c r="CB3">
         <v>153.13036292516296</v>
@@ -4532,7 +4169,7 @@
         <v>2.3822344818651349</v>
       </c>
     </row>
-    <row r="4" spans="1:83">
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4603,7 +4240,7 @@
         <v>181.58273759076252</v>
       </c>
       <c r="X4">
-        <v>31.4243636924555</v>
+        <v>31.424363692455501</v>
       </c>
       <c r="Y4">
         <v>25.688610072706247</v>
@@ -4642,7 +4279,7 @@
         <v>19.907983649810767</v>
       </c>
       <c r="AK4">
-        <v>8.6801495776545</v>
+        <v>8.6801495776545003</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -4666,7 +4303,7 @@
         <v>507.0034136370092</v>
       </c>
       <c r="AS4">
-        <v>69.8366802950334</v>
+        <v>69.836680295033403</v>
       </c>
       <c r="AT4">
         <v>-2.6061037513318377</v>
@@ -4675,7 +4312,7 @@
         <v>-0.51875892193421691</v>
       </c>
       <c r="AV4">
-        <v>-1.1164410018521243</v>
+        <v>-1.1164410018521242</v>
       </c>
       <c r="AW4">
         <v>0.42757057651865243</v>
@@ -4702,7 +4339,7 @@
         <v>-0.16394909511116848</v>
       </c>
       <c r="BE4">
-        <v>-0.0750023175139001</v>
+        <v>-7.5002317513900102E-2</v>
       </c>
       <c r="BF4">
         <v>-0.32336881902840275</v>
@@ -4747,7 +4384,7 @@
         <v>-1.3881560141651013</v>
       </c>
       <c r="BT4">
-        <v>-0.0087942181642024757</v>
+        <v>-8.7942181642024757E-3</v>
       </c>
       <c r="BU4">
         <v>1.2580571617601084</v>
@@ -4774,7 +4411,7 @@
         <v>150.11480397157607</v>
       </c>
       <c r="CC4">
-        <v>58.7397876237791</v>
+        <v>58.739787623779101</v>
       </c>
       <c r="CD4">
         <v>1.3323136340228616</v>
@@ -4783,7 +4420,7 @@
         <v>3.4048471758354775</v>
       </c>
     </row>
-    <row r="5" spans="1:83">
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4797,7 +4434,7 @@
         <v>4.0696096399767185</v>
       </c>
       <c r="E5">
-        <v>76.1631574404607</v>
+        <v>76.163157440460694</v>
       </c>
       <c r="F5">
         <v>67.101286460966847</v>
@@ -4848,7 +4485,7 @@
         <v>82.437663453318592</v>
       </c>
       <c r="V5">
-        <v>31.4243636924555</v>
+        <v>31.424363692455501</v>
       </c>
       <c r="W5">
         <v>187.38855254816909</v>
@@ -4902,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>-5.12205758986098</v>
+        <v>-5.1220575898609804</v>
       </c>
       <c r="AO5">
         <v>-2.4508890424366023</v>
@@ -4953,7 +4590,7 @@
         <v>-0.10920825205466581</v>
       </c>
       <c r="BE5">
-        <v>-0.055355368796494137</v>
+        <v>-5.5355368796494137E-2</v>
       </c>
       <c r="BF5">
         <v>-0.31067207521713663</v>
@@ -4995,16 +4632,16 @@
         <v>34.663802677939785</v>
       </c>
       <c r="BS5">
-        <v>-1.4872539078788321</v>
+        <v>-1.487253907878832</v>
       </c>
       <c r="BT5">
-        <v>-0.00063402022975030548</v>
+        <v>-6.3402022975030548E-4</v>
       </c>
       <c r="BU5">
         <v>1.3275448414918467</v>
       </c>
       <c r="BV5">
-        <v>13.668811448342837</v>
+        <v>13.668811448342836</v>
       </c>
       <c r="BW5">
         <v>-2.4112622869746776</v>
@@ -5034,7 +4671,7 @@
         <v>5.0172433418088884</v>
       </c>
     </row>
-    <row r="6" spans="1:83">
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5159,7 +4796,7 @@
         <v>-2.3751950278922935</v>
       </c>
       <c r="AP6">
-        <v>-0.825442984658271</v>
+        <v>-0.82544298465827104</v>
       </c>
       <c r="AQ6">
         <v>-1.7853848861607584</v>
@@ -5201,10 +4838,10 @@
         <v>-0.27530687086336963</v>
       </c>
       <c r="BD6">
-        <v>-0.088638217291158047</v>
+        <v>-8.8638217291158047E-2</v>
       </c>
       <c r="BE6">
-        <v>-0.052818985609339252</v>
+        <v>-5.2818985609339252E-2</v>
       </c>
       <c r="BF6">
         <v>-0.3315520400060592</v>
@@ -5231,7 +4868,7 @@
         <v>0.10351251425140223</v>
       </c>
       <c r="BN6">
-        <v>0.0986097454977269</v>
+        <v>9.86097454977269E-2</v>
       </c>
       <c r="BO6">
         <v>0.29413250983602468</v>
@@ -5249,7 +4886,7 @@
         <v>-1.4370140090341916</v>
       </c>
       <c r="BT6">
-        <v>-0.00013069558149072952</v>
+        <v>-1.3069558149072952E-4</v>
       </c>
       <c r="BU6">
         <v>1.332969419953727</v>
@@ -5285,7 +4922,7 @@
         <v>5.1348821991063218</v>
       </c>
     </row>
-    <row r="7" spans="1:83">
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5347,7 +4984,7 @@
         <v>74.41206790978012</v>
       </c>
       <c r="U7">
-        <v>71.9567859143798</v>
+        <v>71.956785914379793</v>
       </c>
       <c r="V7">
         <v>27.181807144137792</v>
@@ -5446,16 +5083,16 @@
         <v>0.19529936801422532</v>
       </c>
       <c r="BB7">
-        <v>-0.732479405490545</v>
+        <v>-0.73247940549054502</v>
       </c>
       <c r="BC7">
         <v>-0.30145454218793333</v>
       </c>
       <c r="BD7">
-        <v>-0.076852641041575964</v>
+        <v>-7.6852641041575964E-2</v>
       </c>
       <c r="BE7">
-        <v>-0.045016782728534849</v>
+        <v>-4.5016782728534849E-2</v>
       </c>
       <c r="BF7">
         <v>-0.35705959676152077</v>
@@ -5467,7 +5104,7 @@
         <v>67.909197176703884</v>
       </c>
       <c r="BI7">
-        <v>36.5669278818605</v>
+        <v>36.566927881860501</v>
       </c>
       <c r="BJ7">
         <v>-0.87424588677630433</v>
@@ -5479,10 +5116,10 @@
         <v>-0.73281778134692188</v>
       </c>
       <c r="BM7">
-        <v>0.084576672131348216</v>
+        <v>8.4576672131348216E-2</v>
       </c>
       <c r="BN7">
-        <v>0.093698777946565948</v>
+        <v>9.3698777946565948E-2</v>
       </c>
       <c r="BO7">
         <v>0.33524414562265459</v>
@@ -5491,7 +5128,7 @@
         <v>-0.72426677110367765</v>
       </c>
       <c r="BQ7">
-        <v>1.4861771882513915</v>
+        <v>1.4861771882513914</v>
       </c>
       <c r="BR7">
         <v>34.664931748870806</v>
@@ -5500,7 +5137,7 @@
         <v>-1.4154527741111582</v>
       </c>
       <c r="BT7">
-        <v>0.0025113328450566681</v>
+        <v>2.5113328450566681E-3</v>
       </c>
       <c r="BU7">
         <v>1.3511562674065769</v>
@@ -5536,7 +5173,7 @@
         <v>6.9503737338289691</v>
       </c>
     </row>
-    <row r="8" spans="1:83">
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5592,7 +5229,7 @@
         <v>8.4767755254350519</v>
       </c>
       <c r="S8">
-        <v>71.9567859143798</v>
+        <v>71.956785914379793</v>
       </c>
       <c r="T8">
         <v>69.683684330696934</v>
@@ -5613,7 +5250,7 @@
         <v>18.199372375093496</v>
       </c>
       <c r="Z8">
-        <v>10.4958078185444</v>
+        <v>10.495807818544399</v>
       </c>
       <c r="AA8">
         <v>0.69688353407589643</v>
@@ -5658,7 +5295,7 @@
         <v>-4.0991015600451757</v>
       </c>
       <c r="AO8">
-        <v>-2.4101473089448</v>
+        <v>-2.4101473089447998</v>
       </c>
       <c r="AP8">
         <v>-0.67444815497151633</v>
@@ -5688,7 +5325,7 @@
         <v>0.313610922927891</v>
       </c>
       <c r="AY8">
-        <v>0.062553177317515307</v>
+        <v>6.2553177317515307E-2</v>
       </c>
       <c r="AZ8">
         <v>-0.99833980334742445</v>
@@ -5703,10 +5340,10 @@
         <v>-0.33432340512302849</v>
       </c>
       <c r="BD8">
-        <v>-0.0717129460925606</v>
+        <v>-7.1712946092560598E-2</v>
       </c>
       <c r="BE8">
-        <v>-0.026853463227403632</v>
+        <v>-2.6853463227403632E-2</v>
       </c>
       <c r="BF8">
         <v>-0.39777726990710721</v>
@@ -5718,7 +5355,7 @@
         <v>69.045147369312048</v>
       </c>
       <c r="BI8">
-        <v>34.3720048053326</v>
+        <v>34.372004805332601</v>
       </c>
       <c r="BJ8">
         <v>-0.82015475868312537</v>
@@ -5730,10 +5367,10 @@
         <v>-0.64990795174153848</v>
       </c>
       <c r="BM8">
-        <v>0.054136918391996726</v>
+        <v>5.4136918391996726E-2</v>
       </c>
       <c r="BN8">
-        <v>0.085875146001744548</v>
+        <v>8.5875146001744548E-2</v>
       </c>
       <c r="BO8">
         <v>0.39776931665591003</v>
@@ -5745,13 +5382,13 @@
         <v>1.4671370287762635</v>
       </c>
       <c r="BR8">
-        <v>34.6660247102103</v>
+        <v>34.666024710210301</v>
       </c>
       <c r="BS8">
         <v>-1.3353143494810154</v>
       </c>
       <c r="BT8">
-        <v>0.0031575821234480113</v>
+        <v>3.1575821234480113E-3</v>
       </c>
       <c r="BU8">
         <v>1.3423676842734591</v>
@@ -5784,10 +5421,10 @@
         <v>0.76191056032997018</v>
       </c>
       <c r="CE8">
-        <v>10.453787957916696</v>
-      </c>
-    </row>
-    <row r="9" spans="1:83">
+        <v>10.453787957916695</v>
+      </c>
+    </row>
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5846,7 +5483,7 @@
         <v>67.4504075580288</v>
       </c>
       <c r="T9">
-        <v>65.410451982381</v>
+        <v>65.410451982381005</v>
       </c>
       <c r="U9">
         <v>63.394673707930707</v>
@@ -5939,7 +5576,7 @@
         <v>0.34704929153019021</v>
       </c>
       <c r="AY9">
-        <v>0.06462256634108049</v>
+        <v>6.462256634108049E-2</v>
       </c>
       <c r="AZ9">
         <v>-1.1352240068066988</v>
@@ -5954,10 +5591,10 @@
         <v>-0.43743127447951363</v>
       </c>
       <c r="BD9">
-        <v>-0.0893675982664041</v>
+        <v>-8.93675982664041E-2</v>
       </c>
       <c r="BE9">
-        <v>-0.029165009203172085</v>
+        <v>-2.9165009203172085E-2</v>
       </c>
       <c r="BF9">
         <v>-0.56032381252929975</v>
@@ -5978,13 +5615,13 @@
         <v>0.12350955898703425</v>
       </c>
       <c r="BL9">
-        <v>-0.698216979167988</v>
+        <v>-0.69821697916798797</v>
       </c>
       <c r="BM9">
-        <v>0.047398847532632946</v>
+        <v>4.7398847532632946E-2</v>
       </c>
       <c r="BN9">
-        <v>0.072544499337529919</v>
+        <v>7.2544499337529919E-2</v>
       </c>
       <c r="BO9">
         <v>0.25459222707044449</v>
@@ -5999,10 +5636,10 @@
         <v>-21.60889400966844</v>
       </c>
       <c r="BS9">
-        <v>-1.15822334150383</v>
+        <v>-1.1582233415038301</v>
       </c>
       <c r="BT9">
-        <v>-0.0076449967207965893</v>
+        <v>-7.6449967207965893E-3</v>
       </c>
       <c r="BU9">
         <v>1.2566048553852336</v>
@@ -6038,7 +5675,7 @@
         <v>10.06059390994043</v>
       </c>
     </row>
-    <row r="10" spans="1:83">
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6118,7 +5755,7 @@
         <v>12.06787739838461</v>
       </c>
       <c r="AA10">
-        <v>0.46916425536893</v>
+        <v>0.46916425536893003</v>
       </c>
       <c r="AB10">
         <v>1.6203243026796821</v>
@@ -6139,10 +5776,10 @@
         <v>3145.7989808905731</v>
       </c>
       <c r="AH10">
-        <v>1275.22965670274</v>
+        <v>1275.2296567027399</v>
       </c>
       <c r="AI10">
-        <v>1275.22965670274</v>
+        <v>1275.2296567027399</v>
       </c>
       <c r="AJ10">
         <v>13.30000317232177</v>
@@ -6178,7 +5815,7 @@
         <v>-5.6947770717507726</v>
       </c>
       <c r="AU10">
-        <v>-0.492757713497473</v>
+        <v>-0.49275771349747299</v>
       </c>
       <c r="AV10">
         <v>-1.9349147845579429</v>
@@ -6190,7 +5827,7 @@
         <v>0.38851021679770703</v>
       </c>
       <c r="AY10">
-        <v>0.06607665245855128</v>
+        <v>6.607665245855128E-2</v>
       </c>
       <c r="AZ10">
         <v>-1.2957973168376629</v>
@@ -6208,7 +5845,7 @@
         <v>-0.11058461956632087</v>
       </c>
       <c r="BE10">
-        <v>-0.032579122621533452</v>
+        <v>-3.2579122621533452E-2</v>
       </c>
       <c r="BF10">
         <v>-0.73150351797389834</v>
@@ -6229,13 +5866,13 @@
         <v>0.13237506107537972</v>
       </c>
       <c r="BL10">
-        <v>-0.762662937001009</v>
+        <v>-0.76266293700100896</v>
       </c>
       <c r="BM10">
-        <v>0.043467173211797737</v>
+        <v>4.3467173211797737E-2</v>
       </c>
       <c r="BN10">
-        <v>0.064525248609714883</v>
+        <v>6.4525248609714883E-2</v>
       </c>
       <c r="BO10">
         <v>0.18395853882250032</v>
@@ -6253,7 +5890,7 @@
         <v>-1.1166524150741448</v>
       </c>
       <c r="BT10">
-        <v>-0.014062087951013122</v>
+        <v>-1.4062087951013122E-2</v>
       </c>
       <c r="BU10">
         <v>1.194282980961257</v>
@@ -6289,7 +5926,7 @@
         <v>11.82512097861412</v>
       </c>
     </row>
-    <row r="11" spans="1:83">
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -6309,7 +5946,7 @@
         <v>37.415132842530141</v>
       </c>
       <c r="G11">
-        <v>37.4663505551951</v>
+        <v>37.466350555195099</v>
       </c>
       <c r="H11">
         <v>2.4269421278472274</v>
@@ -6390,10 +6027,10 @@
         <v>3012.9096282555111</v>
       </c>
       <c r="AH11">
-        <v>1823.3249365599143</v>
+        <v>1823.3249365599142</v>
       </c>
       <c r="AI11">
-        <v>1823.3249365599143</v>
+        <v>1823.3249365599142</v>
       </c>
       <c r="AJ11">
         <v>13.157267607845068</v>
@@ -6441,7 +6078,7 @@
         <v>0.37644095918460263</v>
       </c>
       <c r="AY11">
-        <v>0.089936457971006328</v>
+        <v>8.9936457971006328E-2</v>
       </c>
       <c r="AZ11">
         <v>-1.2983001099660498</v>
@@ -6459,10 +6096,10 @@
         <v>-0.11096365665206903</v>
       </c>
       <c r="BE11">
-        <v>-0.049945623403468552</v>
+        <v>-4.9945623403468552E-2</v>
       </c>
       <c r="BF11">
-        <v>-0.758160148865506</v>
+        <v>-0.75816014886550598</v>
       </c>
       <c r="BG11">
         <v>-0.43730005307162484</v>
@@ -6483,10 +6120,10 @@
         <v>-0.73655007250203419</v>
       </c>
       <c r="BM11">
-        <v>0.049253258598634053</v>
+        <v>4.9253258598634053E-2</v>
       </c>
       <c r="BN11">
-        <v>0.060433681358118933</v>
+        <v>6.0433681358118933E-2</v>
       </c>
       <c r="BO11">
         <v>0.13900407719143568</v>
@@ -6504,7 +6141,7 @@
         <v>-1.1061469816705212</v>
       </c>
       <c r="BT11">
-        <v>-0.017062436718488679</v>
+        <v>-1.7062436718488679E-2</v>
       </c>
       <c r="BU11">
         <v>1.1659665222264919</v>
@@ -6546,845 +6183,513 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CE11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:83">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>R0.rotor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>area0.rotor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>N0.rotor</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>σ0_z.rotor</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>area.rotor</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>area.stator</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>N.rotor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>σ_z.rotor</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>P.1</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>P.2</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>P.3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ρ.1</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ρ.2</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ρ.3</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ρ.1</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ρ.2</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ρ.3</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>c.a1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>c.a2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>c.a3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>c.u1</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>c.u2</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>c.u3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>x0.rotor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>x0.stator</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>y0.rotor</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>y0.stator</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>α_major.rotor</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>α_major.stator</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Ju.rotor</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Ju.stator</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Jv.rotor</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Jv.stator</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Jv.stator</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>CPx.rotor</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>CPx.stator</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>CPy.rotor</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>CPy.stator</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>CPx.rotor.axis</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>CPx.stator.axis</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>CPy.rotor.axis</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>CPy.stator.axis</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Wp.rotor</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Wp.stator</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>qx.rotor</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>qx.stator</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>qy.rotor</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>qy.stator</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Mx.rotor</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Mx.stator</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>My.rotor</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>My.stator</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>shift_x.rotor</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>shift_y.rotor</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Mτ.rotor</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Mτ.stator</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>τ.rotor</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>τ.stator</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>φ_uv.rotor</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>φ_uv.stator</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>Mu.rotor</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>Mu.stator</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>Mv.rotor</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>Mv.stator</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>φ_neutral.rotor</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>φ_neutral.stator</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>u_u.rotor</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>v_u.rotor</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>u_l.rotor</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>v_l.rotor</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>u_u.stator</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>v_u.stator</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>u_l.stator</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>v_l.stator</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>σ_p.rotor</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>σ_p.stator</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>σ_n.rotor</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>σ_n.stator</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>σ.rotor</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>σ.stator</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>safety.rotor</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>safety.stator</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:83">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>кН</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>мм^2</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>кН</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>кПа</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>кг/м^3</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>м/с</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>мм^4</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>мм^3</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>мм^3</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>кН/м</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>Н*м</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>град</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>МПа</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:83">
+    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>79</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7410,7 +6715,7 @@
         <v>0.34222056481212354</v>
       </c>
       <c r="I3">
-        <v>4.90187493041852</v>
+        <v>4.9018749304185203</v>
       </c>
       <c r="J3">
         <v>301.22432772946655</v>
@@ -7527,19 +6832,19 @@
         <v>-0.4190974619128866</v>
       </c>
       <c r="AV3">
-        <v>-1.1233655035168118</v>
+        <v>-1.1233655035168117</v>
       </c>
       <c r="AW3">
         <v>0.39644467258741839</v>
       </c>
       <c r="AX3">
-        <v>0.0014766150957015358</v>
+        <v>1.4766150957015358E-3</v>
       </c>
       <c r="AY3">
         <v>1.555458278481423</v>
       </c>
       <c r="AZ3">
-        <v>-0.0045273849518804483</v>
+        <v>-4.5273849518804483E-3</v>
       </c>
       <c r="BA3">
         <v>1.8408651058480874</v>
@@ -7551,13 +6856,13 @@
         <v>-0.58016811240683219</v>
       </c>
       <c r="BD3">
-        <v>-0.016703754245654335</v>
+        <v>-1.6703754245654335E-2</v>
       </c>
       <c r="BE3">
         <v>-0.15266429921633087</v>
       </c>
       <c r="BF3">
-        <v>-0.031099453862768085</v>
+        <v>-3.1099453862768085E-2</v>
       </c>
       <c r="BG3">
         <v>-1.1132079915613942</v>
@@ -7569,25 +6874,25 @@
         <v>37.26449528592012</v>
       </c>
       <c r="BJ3">
-        <v>-0.0038719363743517</v>
+        <v>-3.8719363743517001E-3</v>
       </c>
       <c r="BK3">
         <v>2.3525449327798649</v>
       </c>
       <c r="BL3">
-        <v>-0.0027723122761224789</v>
+        <v>-2.7723122761224789E-3</v>
       </c>
       <c r="BM3">
         <v>0.52322761134831619</v>
       </c>
       <c r="BN3">
-        <v>0.020688087853250131</v>
+        <v>2.0688087853250131E-2</v>
       </c>
       <c r="BO3">
         <v>0.18779893398767233</v>
       </c>
       <c r="BP3">
-        <v>0.000305264002156285</v>
+        <v>3.0526400215628499E-4</v>
       </c>
       <c r="BQ3">
         <v>0.84543039089892924</v>
@@ -7608,7 +6913,7 @@
         <v>14.811421642263355</v>
       </c>
       <c r="BW3">
-        <v>-2.00471469946858</v>
+        <v>-2.0047146994685798</v>
       </c>
       <c r="BX3">
         <v>-0.34256501177293674</v>
@@ -7635,7 +6940,7 @@
         <v>1.4853919774665976</v>
       </c>
     </row>
-    <row r="4" spans="1:83">
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7736,16 +7041,16 @@
         <v>13659.411851170204</v>
       </c>
       <c r="AH4">
-        <v>1952.5793194635558</v>
+        <v>1952.5793194635557</v>
       </c>
       <c r="AI4">
-        <v>1952.5793194635558</v>
+        <v>1952.5793194635557</v>
       </c>
       <c r="AJ4">
         <v>22.268824042909408</v>
       </c>
       <c r="AK4">
-        <v>9.39986679101518</v>
+        <v>9.3998667910151799</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -7784,13 +7089,13 @@
         <v>0.43360690941802477</v>
       </c>
       <c r="AX4">
-        <v>0.00098127632608621348</v>
+        <v>9.8127632608621348E-4</v>
       </c>
       <c r="AY4">
         <v>1.1214196563545891</v>
       </c>
       <c r="AZ4">
-        <v>-0.0030397597000474748</v>
+        <v>-3.0397597000474748E-3</v>
       </c>
       <c r="BA4">
         <v>1.4754974270219841</v>
@@ -7802,13 +7107,13 @@
         <v>-0.5567355985078406</v>
       </c>
       <c r="BD4">
-        <v>-0.0068652966641230967</v>
+        <v>-6.8652966641230967E-3</v>
       </c>
       <c r="BE4">
         <v>-0.1427698652202781</v>
       </c>
       <c r="BF4">
-        <v>-0.017528573094319457</v>
+        <v>-1.7528573094319457E-2</v>
       </c>
       <c r="BG4">
         <v>-1.0679622263067667</v>
@@ -7820,19 +7125,19 @@
         <v>35.233143630950188</v>
       </c>
       <c r="BJ4">
-        <v>-0.0025725097294631068</v>
+        <v>-2.5725097294631068E-3</v>
       </c>
       <c r="BK4">
         <v>1.7672099747399308</v>
       </c>
       <c r="BL4">
-        <v>-0.0018934719311327597</v>
+        <v>-1.8934719311327597E-3</v>
       </c>
       <c r="BM4">
         <v>0.55825048856819848</v>
       </c>
       <c r="BN4">
-        <v>0.024536740931889157</v>
+        <v>2.4536740931889157E-2</v>
       </c>
       <c r="BO4">
         <v>0.29054963268952588</v>
@@ -7877,7 +7182,7 @@
         <v>4.2070475128634977</v>
       </c>
       <c r="CC4">
-        <v>98.8847928249226</v>
+        <v>98.884792824922599</v>
       </c>
       <c r="CD4">
         <v>47.539277697358678</v>
@@ -7886,7 +7191,7 @@
         <v>2.0225556861316765</v>
       </c>
     </row>
-    <row r="5" spans="1:83">
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7900,7 +7205,7 @@
         <v>0.28080100460805724</v>
       </c>
       <c r="E5">
-        <v>6.03680842047547</v>
+        <v>6.0368084204754702</v>
       </c>
       <c r="F5">
         <v>46.514811312488327</v>
@@ -7984,13 +7289,13 @@
         <v>29.770302994238737</v>
       </c>
       <c r="AG5">
-        <v>8428.53251951291</v>
+        <v>8428.5325195129099</v>
       </c>
       <c r="AH5">
-        <v>1623.2153325420291</v>
+        <v>1623.215332542029</v>
       </c>
       <c r="AI5">
-        <v>1623.2153325420291</v>
+        <v>1623.215332542029</v>
       </c>
       <c r="AJ5">
         <v>19.736810959225576</v>
@@ -8020,7 +7325,7 @@
         <v>272.67973276673973</v>
       </c>
       <c r="AS5">
-        <v>116.37134164603774</v>
+        <v>116.37134164603773</v>
       </c>
       <c r="AT5">
         <v>-3.1503199088032381</v>
@@ -8035,13 +7340,13 @@
         <v>0.34081907370103781</v>
       </c>
       <c r="AX5">
-        <v>0.0021940872827694987</v>
+        <v>2.1940872827694987E-3</v>
       </c>
       <c r="AY5">
         <v>0.68335116946965391</v>
       </c>
       <c r="AZ5">
-        <v>-0.0069657643349382891</v>
+        <v>-6.9657643349382891E-3</v>
       </c>
       <c r="BA5">
         <v>0.96998227777096979</v>
@@ -8053,37 +7358,37 @@
         <v>-0.53252015054369561</v>
       </c>
       <c r="BD5">
-        <v>-0.00813351089304566</v>
+        <v>-8.13351089304566E-3</v>
       </c>
       <c r="BE5">
         <v>-0.10449387142979144</v>
       </c>
       <c r="BF5">
-        <v>-0.029828072700963673</v>
+        <v>-2.9828072700963673E-2</v>
       </c>
       <c r="BG5">
         <v>-0.89793474881149393</v>
       </c>
       <c r="BH5">
-        <v>71.2118646520448</v>
+        <v>71.211864652044795</v>
       </c>
       <c r="BI5">
         <v>33.846528798966268</v>
       </c>
       <c r="BJ5">
-        <v>-0.0058879514224398008</v>
+        <v>-5.8879514224398008E-3</v>
       </c>
       <c r="BK5">
         <v>1.1077965930053031</v>
       </c>
       <c r="BL5">
-        <v>-0.0043206388209729163</v>
+        <v>-4.3206388209729163E-3</v>
       </c>
       <c r="BM5">
         <v>0.42499546883601635</v>
       </c>
       <c r="BN5">
-        <v>0.02634094097192918</v>
+        <v>2.634094097192918E-2</v>
       </c>
       <c r="BO5">
         <v>0.40313161544974274</v>
@@ -8131,13 +7436,13 @@
         <v>68.1173195597665</v>
       </c>
       <c r="CD5">
-        <v>28.0880727698555</v>
+        <v>28.088072769855501</v>
       </c>
       <c r="CE5">
         <v>2.9361108348445644</v>
       </c>
     </row>
-    <row r="6" spans="1:83">
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -8247,7 +7552,7 @@
         <v>18.031650679111152</v>
       </c>
       <c r="AK6">
-        <v>8.70021070939704</v>
+        <v>8.7002107093970409</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -8256,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>-5.23776788092174</v>
+        <v>-5.2377678809217398</v>
       </c>
       <c r="AO6">
         <v>-2.575015103892389</v>
@@ -8286,55 +7591,55 @@
         <v>0.37146783733691241</v>
       </c>
       <c r="AX6">
-        <v>0.001326657354963343</v>
+        <v>1.326657354963343E-3</v>
       </c>
       <c r="AY6">
         <v>0.58910177299105038</v>
       </c>
       <c r="AZ6">
-        <v>-0.0043131570631303687</v>
+        <v>-4.3131570631303687E-3</v>
       </c>
       <c r="BA6">
         <v>0.86271800018200229</v>
       </c>
       <c r="BB6">
-        <v>-1.4127335813501663</v>
+        <v>-1.4127335813501662</v>
       </c>
       <c r="BC6">
         <v>-0.58158986810411661</v>
       </c>
       <c r="BD6">
-        <v>-0.0057426478589016608</v>
+        <v>-5.7426478589016608E-3</v>
       </c>
       <c r="BE6">
         <v>-0.10065669968928685</v>
       </c>
       <c r="BF6">
-        <v>-0.027617461083226075</v>
+        <v>-2.7617461083226075E-2</v>
       </c>
       <c r="BG6">
         <v>-0.94962990889817334</v>
       </c>
       <c r="BH6">
-        <v>71.6272658323713</v>
+        <v>71.627265832371293</v>
       </c>
       <c r="BI6">
         <v>34.914258266381218</v>
       </c>
       <c r="BJ6">
-        <v>-0.0036751396728796951</v>
+        <v>-3.6751396728796951E-3</v>
       </c>
       <c r="BK6">
         <v>0.97684563989955087</v>
       </c>
       <c r="BL6">
-        <v>-0.0026185285894057848</v>
+        <v>-2.6185285894057848E-3</v>
       </c>
       <c r="BM6">
         <v>0.37026455756454624</v>
       </c>
       <c r="BN6">
-        <v>0.025690215535535247</v>
+        <v>2.5690215535535247E-2</v>
       </c>
       <c r="BO6">
         <v>0.40475917985889931</v>
@@ -8388,7 +7693,7 @@
         <v>2.9727995430108702</v>
       </c>
     </row>
-    <row r="7" spans="1:83">
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -8414,7 +7719,7 @@
         <v>0.11908272942301734</v>
       </c>
       <c r="I7">
-        <v>3.53899799016948</v>
+        <v>3.5389979901694799</v>
       </c>
       <c r="J7">
         <v>1071.939064917214</v>
@@ -8450,13 +7755,13 @@
         <v>74.41206790978012</v>
       </c>
       <c r="U7">
-        <v>71.9567859143798</v>
+        <v>71.956785914379793</v>
       </c>
       <c r="V7">
         <v>24.412557488178578</v>
       </c>
       <c r="W7">
-        <v>165.24759189589256</v>
+        <v>165.24759189589255</v>
       </c>
       <c r="X7">
         <v>24.748378339014465</v>
@@ -8516,7 +7821,7 @@
         <v>-0.52375790283275381</v>
       </c>
       <c r="AQ7">
-        <v>-1.9730542478908431</v>
+        <v>-1.973054247890843</v>
       </c>
       <c r="AR7">
         <v>167.77177512105632</v>
@@ -8537,13 +7842,13 @@
         <v>0.33800932196826677</v>
       </c>
       <c r="AX7">
-        <v>0.00089926879012395037</v>
+        <v>8.9926879012395037E-4</v>
       </c>
       <c r="AY7">
         <v>0.43551220797320794</v>
       </c>
       <c r="AZ7">
-        <v>-0.0029730014527644911</v>
+        <v>-2.9730014527644911E-3</v>
       </c>
       <c r="BA7">
         <v>0.6732102012152219</v>
@@ -8555,13 +7860,13 @@
         <v>-0.64178397461116865</v>
       </c>
       <c r="BD7">
-        <v>-0.004438114975213671</v>
+        <v>-4.438114975213671E-3</v>
       </c>
       <c r="BE7">
-        <v>-0.086389132797913382</v>
+        <v>-8.6389132797913382E-2</v>
       </c>
       <c r="BF7">
-        <v>-0.026453287342351438</v>
+        <v>-2.6453287342351438E-2</v>
       </c>
       <c r="BG7">
         <v>-0.82395169343771435</v>
@@ -8573,25 +7878,25 @@
         <v>34.795207035050531</v>
       </c>
       <c r="BJ7">
-        <v>-0.0025516824207559414</v>
+        <v>-2.5516824207559414E-3</v>
       </c>
       <c r="BK7">
         <v>0.7418052465797571</v>
       </c>
       <c r="BL7">
-        <v>-0.00177097115127149</v>
+        <v>-1.77097115127149E-3</v>
       </c>
       <c r="BM7">
-        <v>0.304315353639418</v>
+        <v>0.30431535363941797</v>
       </c>
       <c r="BN7">
-        <v>0.025330115547251102</v>
+        <v>2.5330115547251102E-2</v>
       </c>
       <c r="BO7">
         <v>0.45498271846112293</v>
       </c>
       <c r="BP7">
-        <v>-0.817052536734534</v>
+        <v>-0.81705253673453404</v>
       </c>
       <c r="BQ7">
         <v>0.94080804229701676</v>
@@ -8639,7 +7944,7 @@
         <v>3.960286932047806</v>
       </c>
     </row>
-    <row r="8" spans="1:83">
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -8650,7 +7955,7 @@
         <v>29.934501130933274</v>
       </c>
       <c r="D8">
-        <v>0.0801002733999054</v>
+        <v>8.01002733999054E-2</v>
       </c>
       <c r="E8">
         <v>2.6758512877681655</v>
@@ -8662,7 +7967,7 @@
         <v>41.90020692619089</v>
       </c>
       <c r="H8">
-        <v>0.0804142362104209</v>
+        <v>8.0414236210420903E-2</v>
       </c>
       <c r="I8">
         <v>2.6863396139020206</v>
@@ -8683,7 +7988,7 @@
         <v>8.0888958750395368</v>
       </c>
       <c r="O8">
-        <v>8.47989529704594</v>
+        <v>8.4798952970459407</v>
       </c>
       <c r="P8">
         <v>7.2351127254385705</v>
@@ -8692,10 +7997,10 @@
         <v>8.0888958750395368</v>
       </c>
       <c r="R8">
-        <v>8.47989529704594</v>
+        <v>8.4798952970459407</v>
       </c>
       <c r="S8">
-        <v>71.9567859143798</v>
+        <v>71.956785914379793</v>
       </c>
       <c r="T8">
         <v>69.683684330696934</v>
@@ -8758,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-4.59912261662489</v>
+        <v>-4.5991226166248902</v>
       </c>
       <c r="AO8">
         <v>-2.6161516525076762</v>
@@ -8767,7 +8072,7 @@
         <v>-0.48020404086215379</v>
       </c>
       <c r="AQ8">
-        <v>-1.98881947512774</v>
+        <v>-1.9888194751277399</v>
       </c>
       <c r="AR8">
         <v>140.7744945716581</v>
@@ -8788,13 +8093,13 @@
         <v>0.21054838091230152</v>
       </c>
       <c r="AX8">
-        <v>0.00058614411084264239</v>
+        <v>5.8614411084264239E-4</v>
       </c>
       <c r="AY8">
         <v>0.22629469532659405</v>
       </c>
       <c r="AZ8">
-        <v>-0.0019824717914822946</v>
+        <v>-1.9824717914822946E-3</v>
       </c>
       <c r="BA8">
         <v>0.37779857689557433</v>
@@ -8806,13 +8111,13 @@
         <v>-0.716413440289425</v>
       </c>
       <c r="BD8">
-        <v>-0.0035212295702111776</v>
+        <v>-3.5212295702111776E-3</v>
       </c>
       <c r="BE8">
-        <v>-0.051876156295643829</v>
+        <v>-5.1876156295643829E-2</v>
       </c>
       <c r="BF8">
-        <v>-0.025013263808372436</v>
+        <v>-2.5013263808372436E-2</v>
       </c>
       <c r="BG8">
         <v>-0.46808521461866903</v>
@@ -8824,19 +8129,19 @@
         <v>32.703860562496374</v>
       </c>
       <c r="BJ8">
-        <v>-0.0017199459551605826</v>
+        <v>-1.7199459551605826E-3</v>
       </c>
       <c r="BK8">
         <v>0.39454463339787649</v>
       </c>
       <c r="BL8">
-        <v>-0.0011469722028128152</v>
+        <v>-1.1469722028128152E-3</v>
       </c>
       <c r="BM8">
         <v>0.19564147334911491</v>
       </c>
       <c r="BN8">
-        <v>0.023896176242116967</v>
+        <v>2.3896176242116967E-2</v>
       </c>
       <c r="BO8">
         <v>0.5438625590815781</v>
@@ -8890,7 +8195,7 @@
         <v>5.9639307518137148</v>
       </c>
     </row>
-    <row r="9" spans="1:83">
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -8901,7 +8206,7 @@
         <v>27.610754623119135</v>
       </c>
       <c r="D9">
-        <v>0.049302654023864217</v>
+        <v>4.9302654023864217E-2</v>
       </c>
       <c r="E9">
         <v>1.7856322544180643</v>
@@ -8913,7 +8218,7 @@
         <v>46.545639349261982</v>
       </c>
       <c r="H9">
-        <v>0.049447221357027053</v>
+        <v>4.9447221357027053E-2</v>
       </c>
       <c r="I9">
         <v>1.7908681610470627</v>
@@ -8928,7 +8233,7 @@
         <v>2091.1827059310322</v>
       </c>
       <c r="M9">
-        <v>8.47989529704594</v>
+        <v>8.4798952970459407</v>
       </c>
       <c r="N9">
         <v>9.2854243076886576</v>
@@ -8937,7 +8242,7 @@
         <v>9.6611571391019062</v>
       </c>
       <c r="P9">
-        <v>8.47989529704594</v>
+        <v>8.4798952970459407</v>
       </c>
       <c r="Q9">
         <v>9.2854243076886576</v>
@@ -8949,7 +8254,7 @@
         <v>67.4504075580288</v>
       </c>
       <c r="T9">
-        <v>65.410451982381</v>
+        <v>65.410451982381005</v>
       </c>
       <c r="U9">
         <v>63.394673707930707</v>
@@ -8970,10 +8275,10 @@
         <v>12.009582891914787</v>
       </c>
       <c r="AA9">
-        <v>0.407896674381348</v>
+        <v>0.40789667438134802</v>
       </c>
       <c r="AB9">
-        <v>1.8582200948224295</v>
+        <v>1.8582200948224294</v>
       </c>
       <c r="AC9">
         <v>0.17019841723856033</v>
@@ -9009,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>-4.41657248908978</v>
+        <v>-4.4165724890897797</v>
       </c>
       <c r="AO9">
         <v>-2.7429401416030594</v>
@@ -9039,13 +8344,13 @@
         <v>0.25250662083427944</v>
       </c>
       <c r="AX9">
-        <v>0.00035021874869339321</v>
+        <v>3.5021874869339321E-4</v>
       </c>
       <c r="AY9">
         <v>0.23507632952826207</v>
       </c>
       <c r="AZ9">
-        <v>-0.0012135170030243777</v>
+        <v>-1.2135170030243777E-3</v>
       </c>
       <c r="BA9">
         <v>0.40572886954063292</v>
@@ -9057,13 +8362,13 @@
         <v>-0.94241917914275042</v>
       </c>
       <c r="BD9">
-        <v>-0.0031743982840665868</v>
+        <v>-3.1743982840665868E-3</v>
       </c>
       <c r="BE9">
-        <v>-0.056855599606024043</v>
+        <v>-5.6855599606024043E-2</v>
       </c>
       <c r="BF9">
-        <v>-0.025455361887439819</v>
+        <v>-2.5455361887439819E-2</v>
       </c>
       <c r="BG9">
         <v>-0.43814224200507496</v>
@@ -9075,19 +8380,19 @@
         <v>37.901577239030409</v>
       </c>
       <c r="BJ9">
-        <v>-0.0010728719137965228</v>
+        <v>-1.0728719137965228E-3</v>
       </c>
       <c r="BK9">
         <v>0.4347330680553726</v>
       </c>
       <c r="BL9">
-        <v>-0.00066650022141948311</v>
+        <v>-6.6650022141948311E-4</v>
       </c>
       <c r="BM9">
         <v>0.17573831631822007</v>
       </c>
       <c r="BN9">
-        <v>0.020372655382319724</v>
+        <v>2.0372655382319724E-2</v>
       </c>
       <c r="BO9">
         <v>0.38101870229970208</v>
@@ -9102,7 +8407,7 @@
         <v>38.705330392894162</v>
       </c>
       <c r="BS9">
-        <v>-0.791447480985469</v>
+        <v>-0.79144748098546902</v>
       </c>
       <c r="BT9">
         <v>-0.26423499476949081</v>
@@ -9114,7 +8419,7 @@
         <v>14.792637017265662</v>
       </c>
       <c r="BW9">
-        <v>-2.31943998271572</v>
+        <v>-2.3194399827157199</v>
       </c>
       <c r="BX9">
         <v>-0.56900153353684935</v>
@@ -9129,7 +8434,7 @@
         <v>-34.046154343945489</v>
       </c>
       <c r="CB9">
-        <v>2.29923852876746</v>
+        <v>2.2992385287674599</v>
       </c>
       <c r="CC9">
         <v>24.907861696975772</v>
@@ -9141,7 +8446,7 @@
         <v>6.0221949930857575</v>
       </c>
     </row>
-    <row r="10" spans="1:83">
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -9152,7 +8457,7 @@
         <v>26.658434962447302</v>
       </c>
       <c r="D10">
-        <v>0.031995598980534452</v>
+        <v>3.1995598980534452E-2</v>
       </c>
       <c r="E10">
         <v>1.20020545188063</v>
@@ -9164,7 +8469,7 @@
         <v>55.449400382841034</v>
       </c>
       <c r="H10">
-        <v>0.032063833614075068</v>
+        <v>3.2063833614075068E-2</v>
       </c>
       <c r="I10">
         <v>1.2027650407550983</v>
@@ -9227,10 +8532,10 @@
         <v>1.7851759438413937</v>
       </c>
       <c r="AC10">
-        <v>0.14834792568639738</v>
+        <v>0.14834792568639737</v>
       </c>
       <c r="AD10">
-        <v>1.1175716522209696</v>
+        <v>1.1175716522209695</v>
       </c>
       <c r="AE10">
         <v>1.4877635224049202</v>
@@ -9275,7 +8580,7 @@
         <v>118.30848573184662</v>
       </c>
       <c r="AS10">
-        <v>168.72784701355838</v>
+        <v>168.72784701355837</v>
       </c>
       <c r="AT10">
         <v>-6.8020523266249269</v>
@@ -9290,13 +8595,13 @@
         <v>0.2878302687917122</v>
       </c>
       <c r="AX10">
-        <v>0.00020372395443077931</v>
+        <v>2.0372395443077931E-4</v>
       </c>
       <c r="AY10">
         <v>0.24131874149360741</v>
       </c>
       <c r="AZ10">
-        <v>-0.000718489140672941</v>
+        <v>-7.1848914067294096E-4</v>
       </c>
       <c r="BA10">
         <v>0.43365061243887559</v>
@@ -9308,37 +8613,37 @@
         <v>-1.1694036386768334</v>
       </c>
       <c r="BD10">
-        <v>-0.0028024635565684773</v>
+        <v>-2.8024635565684773E-3</v>
       </c>
       <c r="BE10">
-        <v>-0.0639154460057688</v>
+        <v>-6.3915446005768803E-2</v>
       </c>
       <c r="BF10">
-        <v>-0.023687764569317805</v>
+        <v>-2.3687764569317805E-2</v>
       </c>
       <c r="BG10">
-        <v>-0.378807927304571</v>
+        <v>-0.37880792730457102</v>
       </c>
       <c r="BH10">
-        <v>75.3481654679783</v>
+        <v>75.348165467978305</v>
       </c>
       <c r="BI10">
         <v>41.571048467152742</v>
       </c>
       <c r="BJ10">
-        <v>-0.00064359349976721386</v>
+        <v>-6.4359349976721386E-4</v>
       </c>
       <c r="BK10">
         <v>0.46828674092441819</v>
       </c>
       <c r="BL10">
-        <v>-0.0003788370387531355</v>
+        <v>-3.788370387531355E-4</v>
       </c>
       <c r="BM10">
         <v>0.16430190789840896</v>
       </c>
       <c r="BN10">
-        <v>0.018124286328452206</v>
+        <v>1.8124286328452206E-2</v>
       </c>
       <c r="BO10">
         <v>0.29616106478003362</v>
@@ -9392,7 +8697,7 @@
         <v>7.3713620510914764</v>
       </c>
     </row>
-    <row r="11" spans="1:83">
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -9400,22 +8705,22 @@
         <v>216.52630919808175</v>
       </c>
       <c r="C11">
-        <v>26.1064489692454</v>
+        <v>26.106448969245399</v>
       </c>
       <c r="D11">
-        <v>0.088931395167219568</v>
+        <v>8.8931395167219568E-2</v>
       </c>
       <c r="E11">
-        <v>3.40649144860662</v>
+        <v>3.4064914486066198</v>
       </c>
       <c r="F11">
-        <v>26.1064489692454</v>
+        <v>26.106448969245399</v>
       </c>
       <c r="G11">
         <v>66.335152616215524</v>
       </c>
       <c r="H11">
-        <v>0.089285878981590072</v>
+        <v>8.9285878981590072E-2</v>
       </c>
       <c r="I11">
         <v>3.4200698489010497</v>
@@ -9475,13 +8780,13 @@
         <v>0.33805783428013331</v>
       </c>
       <c r="AB11">
-        <v>1.82776231475923</v>
+        <v>1.8277623147592299</v>
       </c>
       <c r="AC11">
-        <v>0.14506847036667978</v>
+        <v>0.14506847036667977</v>
       </c>
       <c r="AD11">
-        <v>1.0466977190041245</v>
+        <v>1.0466977190041244</v>
       </c>
       <c r="AE11">
         <v>1.4139554126233485</v>
@@ -9493,10 +8798,10 @@
         <v>2654.9880599865096</v>
       </c>
       <c r="AH11">
-        <v>3811.13345869231</v>
+        <v>3811.1334586923099</v>
       </c>
       <c r="AI11">
-        <v>3811.13345869231</v>
+        <v>3811.1334586923099</v>
       </c>
       <c r="AJ11">
         <v>14.786154878475196</v>
@@ -9541,13 +8846,13 @@
         <v>0.44258646196284818</v>
       </c>
       <c r="AX11">
-        <v>0.00057088455175553234</v>
+        <v>5.7088455175553234E-4</v>
       </c>
       <c r="AY11">
         <v>0.32979874446320756</v>
       </c>
       <c r="AZ11">
-        <v>-0.0020786698745611813</v>
+        <v>-2.0786698745611813E-3</v>
       </c>
       <c r="BA11">
         <v>0.59522021454044638</v>
@@ -9559,13 +8864,13 @@
         <v>-0.67618154874624226</v>
       </c>
       <c r="BD11">
-        <v>-0.0047536296121234375</v>
+        <v>-4.7536296121234375E-3</v>
       </c>
       <c r="BE11">
-        <v>-0.098331954039918013</v>
+        <v>-9.8331954039918013E-2</v>
       </c>
       <c r="BF11">
-        <v>-0.041461005117607405</v>
+        <v>-4.1461005117607405E-2</v>
       </c>
       <c r="BG11">
         <v>-0.44538900084385458</v>
@@ -9577,19 +8882,19 @@
         <v>44.831165517933115</v>
       </c>
       <c r="BJ11">
-        <v>-0.0018767022793145559</v>
+        <v>-1.8767022793145559E-3</v>
       </c>
       <c r="BK11">
         <v>0.6535312958198205</v>
       </c>
       <c r="BL11">
-        <v>-0.0010605499392564513</v>
+        <v>-1.0605499392564513E-3</v>
       </c>
       <c r="BM11">
         <v>0.18960791394651549</v>
       </c>
       <c r="BN11">
-        <v>0.01724374149711665</v>
+        <v>1.724374149711665E-2</v>
       </c>
       <c r="BO11">
         <v>0.23262637487167365</v>
@@ -9598,7 +8903,7 @@
         <v>-0.81835279396350236</v>
       </c>
       <c r="BQ11">
-        <v>0.872215315920957</v>
+        <v>0.87221531592095702</v>
       </c>
       <c r="BR11">
         <v>-24.822463550671205</v>
@@ -9619,7 +8924,7 @@
         <v>-1.8907420041052641</v>
       </c>
       <c r="BX11">
-        <v>-1.1579931535857893</v>
+        <v>-1.1579931535857892</v>
       </c>
       <c r="BY11">
         <v>20.512065508498534</v>
@@ -9646,4 +8951,1415 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F83"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="1">
+        <v>235.63216491241906</v>
+      </c>
+      <c r="E2" s="1">
+        <v>235.63216491241906</v>
+      </c>
+      <c r="F2" s="1">
+        <v>235.63216491241906</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="1">
+        <v>230.28755476505043</v>
+      </c>
+      <c r="E3" s="1">
+        <v>78.738009277708599</v>
+      </c>
+      <c r="F3" s="1">
+        <v>69.814217961473943</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="1">
+        <v>23.982338871449944</v>
+      </c>
+      <c r="E4" s="1">
+        <v>8.1994120021517425</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.34231753143004695</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="1">
+        <v>104.14083772750023</v>
+      </c>
+      <c r="E5" s="1">
+        <v>104.13537346661197</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4.9032638540612217</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="1">
+        <v>241.50206305446437</v>
+      </c>
+      <c r="E6" s="1">
+        <v>105.85772424362537</v>
+      </c>
+      <c r="F6" s="1">
+        <v>69.814217961473943</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="1">
+        <v>11.178822012033388</v>
+      </c>
+      <c r="E7" s="1">
+        <v>27.531737975863223</v>
+      </c>
+      <c r="F7" s="1">
+        <v>48.292511091984224</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="1">
+        <v>27.643139880282742</v>
+      </c>
+      <c r="E8" s="1">
+        <v>9.4690177625296688</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.34222056481212354</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="1">
+        <v>114.46336950773197</v>
+      </c>
+      <c r="E9" s="1">
+        <v>89.45041875959167</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4.9018749304185203</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="1">
+        <v>299.26418287761362</v>
+      </c>
+      <c r="E10" s="1">
+        <v>300.50920160679021</v>
+      </c>
+      <c r="F10" s="1">
+        <v>301.22432772946655</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="1">
+        <v>349.78808651740758</v>
+      </c>
+      <c r="E11" s="1">
+        <v>376.44730091103872</v>
+      </c>
+      <c r="F11" s="1">
+        <v>389.67107140859684</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="1">
+        <v>421.73524183129689</v>
+      </c>
+      <c r="E12" s="1">
+        <v>422.81391004163669</v>
+      </c>
+      <c r="F12" s="1">
+        <v>423.3462934690229</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2.5299367044947672</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2.5374835411800185</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.5418143722930324</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2.7883401465980904</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2.9396949042568554</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3.0136499218883235</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3.1901206909973827</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3.19599052645327</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3.1988860727554957</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.5299367044947672</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2.5374835411800185</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2.5418143722930324</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.7883401465980904</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2.9396949042568554</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3.0136499218883235</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3.1901206909973827</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3.19599052645327</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3.1988860727554957</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="1">
+        <v>103.47185073308697</v>
+      </c>
+      <c r="E19" s="1">
+        <v>99.88510196737468</v>
+      </c>
+      <c r="F19" s="1">
+        <v>97.968643364307269</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="1">
+        <v>111.30193915669611</v>
+      </c>
+      <c r="E20" s="1">
+        <v>97.284769469570548</v>
+      </c>
+      <c r="F20" s="1">
+        <v>89.559409142252335</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="1">
+        <v>94.39606954466818</v>
+      </c>
+      <c r="E21" s="1">
+        <v>94.278083563082717</v>
+      </c>
+      <c r="F21" s="1">
+        <v>94.220111232685639</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="1">
+        <v>44.532847557170811</v>
+      </c>
+      <c r="E22" s="1">
+        <v>41.59087659848727</v>
+      </c>
+      <c r="F22" s="1">
+        <v>39.31679256168686</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="1">
+        <v>215.98601679739394</v>
+      </c>
+      <c r="E23" s="1">
+        <v>175.93877646002755</v>
+      </c>
+      <c r="F23" s="1">
+        <v>153.3384414350669</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="1">
+        <v>44.108432098047047</v>
+      </c>
+      <c r="E24" s="1">
+        <v>35.946915467752305</v>
+      </c>
+      <c r="F24" s="1">
+        <v>31.146463255638665</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="1">
+        <v>24.522293718412932</v>
+      </c>
+      <c r="E25" s="1">
+        <v>28.557268840417873</v>
+      </c>
+      <c r="F25" s="1">
+        <v>35.29336527669517</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="1">
+        <v>10.194057339256814</v>
+      </c>
+      <c r="E26" s="1">
+        <v>11.312298784599481</v>
+      </c>
+      <c r="F26" s="1">
+        <v>12.232868807108176</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3.0970335177708219</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1.0791544037582392</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0.50105290867266339</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1.4617331174998134</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1.5731425907814125</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1.6666594422619077</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1.0420027363837927</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.30962217086022292</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1.1692051981276796</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.1375564628100969</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1.1180165935167421</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="1">
+        <v>756.40196267309841</v>
+      </c>
+      <c r="E31" s="1">
+        <v>45.308055881979115</v>
+      </c>
+      <c r="F31" s="1">
+        <v>9.5557110131730649</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2.5038677557644964</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10.042586514942441</v>
+      </c>
+      <c r="F32" s="1">
+        <v>29.769093119297569</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="1">
+        <v>40591.109554649549</v>
+      </c>
+      <c r="E33" s="1">
+        <v>24118.115726380929</v>
+      </c>
+      <c r="F33" s="1">
+        <v>18948.690614068757</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="1">
+        <v>324.67173109056989</v>
+      </c>
+      <c r="E34" s="1">
+        <v>984.64491511324263</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2019.9763563475462</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="1">
+        <v>324.67173109056989</v>
+      </c>
+      <c r="E35" s="1">
+        <v>984.64491511324263</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2019.9763563475462</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="1">
+        <v>19.004119764374312</v>
+      </c>
+      <c r="E36" s="1">
+        <v>22.131117236363469</v>
+      </c>
+      <c r="F36" s="1">
+        <v>24.705355693686609</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="1">
+        <v>7.9001209586960881</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8.7667280794167013</v>
+      </c>
+      <c r="F37" s="1">
+        <v>9.4801451504353054</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="1">
+        <v>-5.5735821459542736</v>
+      </c>
+      <c r="E40" s="1">
+        <v>-6.4318894171960626</v>
+      </c>
+      <c r="F40" s="1">
+        <v>-10.588009583008557</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="1">
+        <v>-2.3232855294726575</v>
+      </c>
+      <c r="E41" s="1">
+        <v>-2.5763002954850598</v>
+      </c>
+      <c r="F41" s="1">
+        <v>-2.7847191895336247</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="1">
+        <v>-2.9961713000971559</v>
+      </c>
+      <c r="E42" s="1">
+        <v>-1.0444123660715117</v>
+      </c>
+      <c r="F42" s="1">
+        <v>-0.50105290867266339</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="1">
+        <v>-1.4146208585337339</v>
+      </c>
+      <c r="E43" s="1">
+        <v>-1.5222958363927817</v>
+      </c>
+      <c r="F43" s="1">
+        <v>-1.6126314712079848</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1381.2049989312068</v>
+      </c>
+      <c r="E44" s="1">
+        <v>696.52723362228858</v>
+      </c>
+      <c r="F44" s="1">
+        <v>537.10763923259378</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="1">
+        <v>26.250217892143027</v>
+      </c>
+      <c r="E45" s="1">
+        <v>71.946958196113656</v>
+      </c>
+      <c r="F45" s="1">
+        <v>137.13906149937242</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="1">
+        <v>-1.3984763476286868</v>
+      </c>
+      <c r="E46" s="1">
+        <v>-2.5388189779966437</v>
+      </c>
+      <c r="F46" s="1">
+        <v>-3.4180744619002827</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="1">
+        <v>-0.53666232106699019</v>
+      </c>
+      <c r="E47" s="1">
+        <v>-0.46474370902606166</v>
+      </c>
+      <c r="F47" s="1">
+        <v>-0.4190974619128866</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="1">
+        <v>-1.1928028506862294</v>
+      </c>
+      <c r="E48" s="1">
+        <v>-1.1483983772568915</v>
+      </c>
+      <c r="F48" s="1">
+        <v>-1.1233655035168117</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.42764734353111244</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.40887235601121957</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0.39644467258741839</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4.659685765198982</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.98111987348717145</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1.4766150957015358E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1.1426149378461264E-3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.45350507292479275</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1.555458278481423</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="1">
+        <v>-11.362976052056272</v>
+      </c>
+      <c r="E52" s="1">
+        <v>-2.7359277064587375</v>
+      </c>
+      <c r="F52" s="1">
+        <v>-4.5273849518804483E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1.4305195632442697E-3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.55119818477610738</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1.8408651058480874</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="1">
+        <v>-1.9335200224522855E-2</v>
+      </c>
+      <c r="E54" s="1">
+        <v>-0.5297204520242812</v>
+      </c>
+      <c r="F54" s="1">
+        <v>-1.1317624713645493</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" s="1">
+        <v>-1.1597797617609373E-2</v>
+      </c>
+      <c r="E55" s="1">
+        <v>-0.29135826813007082</v>
+      </c>
+      <c r="F55" s="1">
+        <v>-0.58016811240683219</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="1">
+        <v>-0.46192118681762528</v>
+      </c>
+      <c r="E56" s="1">
+        <v>-0.31094231613798201</v>
+      </c>
+      <c r="F56" s="1">
+        <v>-1.6703754245654335E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4.0573887286063292E-3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>-8.1841629186138617E-2</v>
+      </c>
+      <c r="F57" s="1">
+        <v>-0.15266429921633087</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="1">
+        <v>-0.33443347452048428</v>
+      </c>
+      <c r="E58" s="1">
+        <v>-0.44641803095182231</v>
+      </c>
+      <c r="F58" s="1">
+        <v>-3.1099453862768085E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0.1545659066632262</v>
+      </c>
+      <c r="E59" s="1">
+        <v>-1.1375273011967229</v>
+      </c>
+      <c r="F59" s="1">
+        <v>-1.1132079915613942</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" s="1">
+        <v>43.824696406366066</v>
+      </c>
+      <c r="E60" s="1">
+        <v>65.085792298812379</v>
+      </c>
+      <c r="F60" s="1">
+        <v>72.461113406556407</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="1">
+        <v>38.895699801144687</v>
+      </c>
+      <c r="E61" s="1">
+        <v>38.074464850833088</v>
+      </c>
+      <c r="F61" s="1">
+        <v>37.26449528592012</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="1">
+        <v>-4.5065552416609496</v>
+      </c>
+      <c r="E62" s="1">
+        <v>-2.0680138640895183</v>
+      </c>
+      <c r="F62" s="1">
+        <v>-3.8719363743517001E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1.7875159769749876E-3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.69691940804436814</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2.3525449327798649</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="1">
+        <v>-11.424572466567867</v>
+      </c>
+      <c r="E64" s="1">
+        <v>-2.04235532634593</v>
+      </c>
+      <c r="F64" s="1">
+        <v>-2.7723122761224789E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3.9590623772913641E-4</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.15423886916106733</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0.52322761134831619</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2.7046860185524357</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.10629970107469862</v>
+      </c>
+      <c r="F66" s="1">
+        <v>2.0688087853250131E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67" s="1">
+        <v>9.7865931250574148E-2</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.12932994935416645</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0.18779893398767233</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" s="1">
+        <v>-2.5469371287826226</v>
+      </c>
+      <c r="E68" s="1">
+        <v>-0.72469066125427206</v>
+      </c>
+      <c r="F68" s="1">
+        <v>3.0526400215628499E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" t="s">
+        <v>80</v>
+      </c>
+      <c r="D69" s="1">
+        <v>4.0064931143670748</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1.4631644443707086</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0.84543039089892924</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" t="s">
+        <v>80</v>
+      </c>
+      <c r="D70" s="1">
+        <v>29.509175764571651</v>
+      </c>
+      <c r="E70" s="1">
+        <v>34.665747355781754</v>
+      </c>
+      <c r="F70" s="1">
+        <v>23.293412314639106</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" s="1">
+        <v>-5.036087827531901</v>
+      </c>
+      <c r="E71" s="1">
+        <v>-1.3308330628627341</v>
+      </c>
+      <c r="F71" s="1">
+        <v>-0.5823894827299132</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.20594638147026464</v>
+      </c>
+      <c r="E72" s="1">
+        <v>-1.4050038681906673E-2</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-0.27623835607432828</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0.7659489704818645</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1.2096431137820558</v>
+      </c>
+      <c r="F73" s="1">
+        <v>1.7028284307059776</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" s="1">
+        <v>12.34236731200504</v>
+      </c>
+      <c r="E74" s="1">
+        <v>13.697356690149816</v>
+      </c>
+      <c r="F74" s="1">
+        <v>14.811421642263355</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" s="1">
+        <v>-1.7350811875955339</v>
+      </c>
+      <c r="E75" s="1">
+        <v>-1.8764434998649049</v>
+      </c>
+      <c r="F75" s="1">
+        <v>-2.0047146994685798</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" s="1">
+        <v>-24.587070000457388</v>
+      </c>
+      <c r="E76" s="1">
+        <v>-66.845172528390563</v>
+      </c>
+      <c r="F76" s="1">
+        <v>-0.34256501177293674</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0.54656130214851961</v>
+      </c>
+      <c r="E77" s="1">
+        <v>83.947085129763849</v>
+      </c>
+      <c r="F77" s="1">
+        <v>134.63999223521878</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" s="1">
+        <v>38.309934014229214</v>
+      </c>
+      <c r="E78" s="1">
+        <v>63.679293447196471</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0.23938989130145416</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79" s="1">
+        <v>-1.2537281172451249</v>
+      </c>
+      <c r="E79" s="1">
+        <v>-132.36404522829505</v>
+      </c>
+      <c r="F79" s="1">
+        <v>-162.26198321617792</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80" s="1">
+        <v>152.77366957287552</v>
+      </c>
+      <c r="E80" s="1">
+        <v>153.13036292516296</v>
+      </c>
+      <c r="F80" s="1">
+        <v>5.1413588809852477</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0.56799637015469606</v>
+      </c>
+      <c r="E81" s="1">
+        <v>83.954791823604609</v>
+      </c>
+      <c r="F81" s="1">
+        <v>134.64459417716051</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1.3091261115816606</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1.3060767060138354</v>
+      </c>
+      <c r="F82" s="1">
+        <v>38.900221639784391</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>78</v>
+      </c>
+      <c r="C83" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83" s="1">
+        <v>352.11492627237953</v>
+      </c>
+      <c r="E83" s="1">
+        <v>2.3822344818651349</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1.4853919774665976</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>